--- a/admin_testy/reporty_google_testy/google_data/Pobočky/Prosek/Databaze Prosek 2026.xlsx
+++ b/admin_testy/reporty_google_testy/google_data/Pobočky/Prosek/Databaze Prosek 2026.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2899" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3054" uniqueCount="367">
   <si>
     <t>Datum</t>
   </si>
@@ -261,27 +261,84 @@
     <t>10 min 34 s</t>
   </si>
   <si>
+    <t>05.05.2026</t>
+  </si>
+  <si>
+    <t>Úterý</t>
+  </si>
+  <si>
+    <t>02:00</t>
+  </si>
+  <si>
+    <t>9 min 01 s</t>
+  </si>
+  <si>
+    <t>06.05.2026</t>
+  </si>
+  <si>
+    <t>Středa</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>14 min 37 s</t>
+  </si>
+  <si>
+    <t>07.05.2026</t>
+  </si>
+  <si>
+    <t>Čtvrtek</t>
+  </si>
+  <si>
+    <t>11 min 25 s</t>
+  </si>
+  <si>
+    <t>08.05.2026</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>11 min 00 s</t>
+  </si>
+  <si>
+    <t>09.05.2026</t>
+  </si>
+  <si>
+    <t>Kopic Jakub</t>
+  </si>
+  <si>
+    <t>10 min 48 s</t>
+  </si>
+  <si>
+    <t>10.05.2026</t>
+  </si>
+  <si>
+    <t>14 min 25 s</t>
+  </si>
+  <si>
+    <t>11.05.2026</t>
+  </si>
+  <si>
+    <t>01:30</t>
+  </si>
+  <si>
+    <t>08:30</t>
+  </si>
+  <si>
+    <t>14 min 17 s</t>
+  </si>
+  <si>
     <t>01.04.2026</t>
   </si>
   <si>
-    <t>Středa</t>
-  </si>
-  <si>
-    <t>08:00</t>
-  </si>
-  <si>
     <t>10 min 50 s</t>
   </si>
   <si>
     <t>02.04.2026</t>
   </si>
   <si>
-    <t>Čtvrtek</t>
-  </si>
-  <si>
-    <t>15:00</t>
-  </si>
-  <si>
     <t>10 min 06 s</t>
   </si>
   <si>
@@ -324,9 +381,6 @@
     <t>07.04.2026</t>
   </si>
   <si>
-    <t>Úterý</t>
-  </si>
-  <si>
     <t>9 min 10 s</t>
   </si>
   <si>
@@ -357,9 +411,6 @@
     <t>18:30</t>
   </si>
   <si>
-    <t>08:30</t>
-  </si>
-  <si>
     <t>Pešová Hana</t>
   </si>
   <si>
@@ -498,12 +549,6 @@
     <t>30.04.2026</t>
   </si>
   <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>01:30</t>
-  </si>
-  <si>
     <t>12 min 48 s</t>
   </si>
   <si>
@@ -549,9 +594,6 @@
     <t>07.03.2026</t>
   </si>
   <si>
-    <t>Kopic Jakub</t>
-  </si>
-  <si>
     <t>Kináč Jozef</t>
   </si>
   <si>
@@ -850,9 +892,6 @@
   </si>
   <si>
     <t>19.02.2026</t>
-  </si>
-  <si>
-    <t>9 min 01 s</t>
   </si>
   <si>
     <t>20.02.2026</t>
@@ -2098,6 +2137,1138 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="M17" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="N17" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O17" s="3">
+        <v>270.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="P18" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Q18" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="R18" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="S18" s="3">
+        <v>7055.0</v>
+      </c>
+      <c r="T18" s="3">
+        <v>5869.0</v>
+      </c>
+      <c r="U18" s="3">
+        <v>5233.0</v>
+      </c>
+      <c r="V18" s="3">
+        <v>3517.0</v>
+      </c>
+      <c r="W18" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X18" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>1962.0</v>
+      </c>
+      <c r="AA18" s="3">
+        <v>1024.0</v>
+      </c>
+      <c r="AB18" s="3">
+        <v>24930.0</v>
+      </c>
+      <c r="AC18" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AD18" s="3">
+        <v>0.39369336035091795</v>
+      </c>
+      <c r="AI18" s="3">
+        <v>270.0</v>
+      </c>
+      <c r="AJ18" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AK18" s="3">
+        <v>394.0</v>
+      </c>
+      <c r="AL18" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AM18" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AN18" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AO18" s="3">
+        <v>65.0</v>
+      </c>
+      <c r="AP18" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AQ18" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AR18" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS18" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AT18" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU18" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AV18" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="M21" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="N21" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O21" s="3">
+        <v>240.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="P22" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="S22" s="3">
+        <v>17136.0</v>
+      </c>
+      <c r="T22" s="3">
+        <v>3182.0</v>
+      </c>
+      <c r="U22" s="3">
+        <v>8977.0</v>
+      </c>
+      <c r="V22" s="3">
+        <v>2752.0</v>
+      </c>
+      <c r="W22" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X22" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>1565.0</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>1126.0</v>
+      </c>
+      <c r="AB22" s="3">
+        <v>35008.0</v>
+      </c>
+      <c r="AC22" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AD22" s="3">
+        <v>0.3434363926402076</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="AI22" s="3">
+        <v>240.0</v>
+      </c>
+      <c r="AJ22" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="AK22" s="3">
+        <v>1286.0</v>
+      </c>
+      <c r="AL22" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AM22" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="AN22" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AO22" s="3">
+        <v>74.0</v>
+      </c>
+      <c r="AP22" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AQ22" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AR22" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS22" s="3">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="AT22" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU22" s="3">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AV22" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="M25" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="N25" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O25" s="3">
+        <v>270.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="P26" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="Q26" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="R26" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="S26" s="3">
+        <v>12640.0</v>
+      </c>
+      <c r="T26" s="3">
+        <v>6766.0</v>
+      </c>
+      <c r="U26" s="3">
+        <v>6371.0</v>
+      </c>
+      <c r="V26" s="3">
+        <v>3620.0</v>
+      </c>
+      <c r="W26" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X26" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Y26" s="3">
+        <v>1545.0</v>
+      </c>
+      <c r="AA26" s="3">
+        <v>220.0</v>
+      </c>
+      <c r="AB26" s="3">
+        <v>32429.0</v>
+      </c>
+      <c r="AC26" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="AD26" s="3">
+        <v>0.30704047221771835</v>
+      </c>
+      <c r="AE26" s="3">
+        <v>1000.0</v>
+      </c>
+      <c r="AI26" s="3">
+        <v>270.0</v>
+      </c>
+      <c r="AJ26" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK26" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL26" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AM26" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="AN26" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AO26" s="3">
+        <v>81.0</v>
+      </c>
+      <c r="AP26" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="AQ26" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AR26" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS26" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AT26" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU26" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AV26" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="M29" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N29" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O29" s="3">
+        <v>160.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="P30" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="Q30" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="R30" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="S30" s="3">
+        <v>16333.0</v>
+      </c>
+      <c r="T30" s="3">
+        <v>10895.0</v>
+      </c>
+      <c r="U30" s="3">
+        <v>7497.0</v>
+      </c>
+      <c r="V30" s="3">
+        <v>4057.0</v>
+      </c>
+      <c r="W30" s="3">
+        <v>612.0</v>
+      </c>
+      <c r="X30" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>10103.0</v>
+      </c>
+      <c r="AA30" s="3">
+        <v>1941.0</v>
+      </c>
+      <c r="AB30" s="3">
+        <v>52317.5</v>
+      </c>
+      <c r="AC30" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="AD30" s="3">
+        <v>0.16406365811723392</v>
+      </c>
+      <c r="AE30" s="3">
+        <v>700.0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>20.0</v>
+      </c>
+      <c r="AI30" s="3">
+        <v>160.0</v>
+      </c>
+      <c r="AJ30" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="AK30" s="3">
+        <v>1145.0</v>
+      </c>
+      <c r="AL30" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AM30" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN30" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AO30" s="3">
+        <v>120.0</v>
+      </c>
+      <c r="AP30" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="AQ30" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AR30" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS30" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AT30" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU30" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AV30" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="M34" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N34" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O34" s="3">
+        <v>90.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="P35" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="Q35" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R35" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="S35" s="3">
+        <v>13311.0</v>
+      </c>
+      <c r="T35" s="3">
+        <v>4031.0</v>
+      </c>
+      <c r="U35" s="3">
+        <v>4934.0</v>
+      </c>
+      <c r="V35" s="3">
+        <v>3280.0</v>
+      </c>
+      <c r="W35" s="3">
+        <v>1546.0</v>
+      </c>
+      <c r="X35" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Y35" s="3">
+        <v>448.0</v>
+      </c>
+      <c r="AA35" s="3">
+        <v>1935.0</v>
+      </c>
+      <c r="AB35" s="3">
+        <v>30339.0</v>
+      </c>
+      <c r="AC35" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AD35" s="3">
+        <v>0.40949311557890467</v>
+      </c>
+      <c r="AH35" s="3">
+        <v>764.0</v>
+      </c>
+      <c r="AI35" s="3">
+        <v>90.0</v>
+      </c>
+      <c r="AJ35" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AK35" s="3">
+        <v>249.0</v>
+      </c>
+      <c r="AL35" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AM35" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="AN35" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AO35" s="3">
+        <v>66.0</v>
+      </c>
+      <c r="AP35" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="AQ35" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AR35" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS35" s="3">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="AT35" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU35" s="3">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="AV35" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="M38" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N38" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O38" s="3">
+        <v>90.0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="P39" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="Q39" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R39" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="S39" s="3">
+        <v>9027.0</v>
+      </c>
+      <c r="T39" s="3">
+        <v>5048.0</v>
+      </c>
+      <c r="U39" s="3">
+        <v>5214.0</v>
+      </c>
+      <c r="V39" s="3">
+        <v>3921.0</v>
+      </c>
+      <c r="W39" s="3">
+        <v>920.0</v>
+      </c>
+      <c r="X39" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Y39" s="3">
+        <v>2724.0</v>
+      </c>
+      <c r="AA39" s="3">
+        <v>1064.0</v>
+      </c>
+      <c r="AB39" s="3">
+        <v>28079.0</v>
+      </c>
+      <c r="AC39" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AD39" s="3">
+        <v>0.37349000012637157</v>
+      </c>
+      <c r="AG39" s="3">
+        <v>71.0</v>
+      </c>
+      <c r="AI39" s="3">
+        <v>90.0</v>
+      </c>
+      <c r="AJ39" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AK39" s="3">
+        <v>388.0</v>
+      </c>
+      <c r="AL39" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AM39" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="AN39" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AO39" s="3">
+        <v>71.0</v>
+      </c>
+      <c r="AP39" s="3">
+        <v>11.0</v>
+      </c>
+      <c r="AQ39" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="AR39" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS39" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AT39" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU39" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AV39" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="P42" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="Q42" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="R42" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="S42" s="3">
+        <v>11900.0</v>
+      </c>
+      <c r="T42" s="3">
+        <v>3393.0</v>
+      </c>
+      <c r="U42" s="3">
+        <v>4332.0</v>
+      </c>
+      <c r="V42" s="3">
+        <v>2441.0</v>
+      </c>
+      <c r="W42" s="3">
+        <v>518.0</v>
+      </c>
+      <c r="X42" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Y42" s="3">
+        <v>1191.0</v>
+      </c>
+      <c r="AA42" s="3">
+        <v>-200.0</v>
+      </c>
+      <c r="AB42" s="3">
+        <v>23575.0</v>
+      </c>
+      <c r="AC42" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AD42" s="3">
+        <v>0.3743179857284576</v>
+      </c>
+      <c r="AI42" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ42" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK42" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL42" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AM42" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="AN42" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO42" s="3">
+        <v>56.0</v>
+      </c>
+      <c r="AP42" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AQ42" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AR42" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AS42" s="3">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AT42" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU42" s="3">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AV42" s="3">
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -2258,10 +3429,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>50</v>
@@ -2273,15 +3444,15 @@
         <v>77</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>54</v>
@@ -2298,10 +3469,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>57</v>
@@ -2327,10 +3498,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="P5" s="3">
         <v>2.0</v>
@@ -2393,7 +3564,7 @@
         <v>1.0</v>
       </c>
       <c r="AM5" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="AN5" s="3">
         <v>1.0</v>
@@ -2425,10 +3596,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>63</v>
@@ -2440,15 +3611,15 @@
         <v>58</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>57</v>
@@ -2474,10 +3645,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="P8" s="3">
         <v>0.0</v>
@@ -2537,7 +3708,7 @@
         <v>0.0</v>
       </c>
       <c r="AM8" s="1" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="AN8" s="3">
         <v>1.0</v>
@@ -2569,7 +3740,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>49</v>
@@ -2589,7 +3760,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>49</v>
@@ -2599,16 +3770,16 @@
       <c r="E10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>64</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="N10" s="1" t="b">
         <v>1</v>
@@ -2616,7 +3787,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>49</v>
@@ -2683,7 +3854,7 @@
         <v>3.0</v>
       </c>
       <c r="AM11" s="1" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="AN11" s="3">
         <v>0.0</v>
@@ -2715,7 +3886,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>62</v>
@@ -2735,13 +3906,13 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>53</v>
@@ -2764,7 +3935,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>62</v>
@@ -2827,7 +3998,7 @@
         <v>2.0</v>
       </c>
       <c r="AM14" s="1" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="AN14" s="3">
         <v>1.0</v>
@@ -2859,7 +4030,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>69</v>
@@ -2879,13 +4050,13 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>53</v>
@@ -2894,7 +4065,7 @@
         <v>71</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="M16" s="3">
         <v>8.0</v>
@@ -2908,7 +4079,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>69</v>
@@ -2968,7 +4139,7 @@
         <v>0.0</v>
       </c>
       <c r="AM17" s="1" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="AN17" s="3">
         <v>1.0</v>
@@ -3000,7 +4171,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>76</v>
@@ -3020,7 +4191,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>76</v>
@@ -3035,12 +4206,12 @@
         <v>58</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>76</v>
@@ -3069,7 +4240,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>76</v>
@@ -3132,7 +4303,7 @@
         <v>3.0</v>
       </c>
       <c r="AM21" s="1" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="AN21" s="3">
         <v>1.0</v>
@@ -3164,10 +4335,10 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>50</v>
@@ -3184,10 +4355,10 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>63</v>
@@ -3199,15 +4370,15 @@
         <v>58</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>57</v>
@@ -3233,10 +4404,10 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="P25" s="3">
         <v>0.0</v>
@@ -3296,7 +4467,7 @@
         <v>0.0</v>
       </c>
       <c r="AM25" s="1" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="AN25" s="3">
         <v>1.0</v>
@@ -3328,10 +4499,10 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>50</v>
@@ -3348,10 +4519,10 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>54</v>
@@ -3363,15 +4534,15 @@
         <v>58</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>57</v>
@@ -3397,10 +4568,10 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="P29" s="3">
         <v>1.0</v>
@@ -3457,7 +4628,7 @@
         <v>1.0</v>
       </c>
       <c r="AM29" s="1" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="AN29" s="3">
         <v>1.0</v>
@@ -3489,10 +4660,10 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>63</v>
@@ -3509,10 +4680,10 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>54</v>
@@ -3524,15 +4695,15 @@
         <v>58</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>57</v>
@@ -3558,10 +4729,10 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="P33" s="3">
         <v>0.0</v>
@@ -3618,7 +4789,7 @@
         <v>2.0</v>
       </c>
       <c r="AM33" s="1" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="AN33" s="3">
         <v>1.0</v>
@@ -3650,7 +4821,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>49</v>
@@ -3670,13 +4841,13 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>77</v>
@@ -3690,7 +4861,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>49</v>
@@ -3719,7 +4890,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>49</v>
@@ -3782,7 +4953,7 @@
         <v>0.0</v>
       </c>
       <c r="AM37" s="1" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="AN37" s="3">
         <v>1.0</v>
@@ -3814,7 +4985,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>62</v>
@@ -3826,47 +4997,47 @@
         <v>51</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>55</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>77</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>66</v>
@@ -3874,7 +5045,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>62</v>
@@ -3890,7 +5061,7 @@
         <v>50</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="S41" s="3">
         <v>17084.0</v>
@@ -3938,7 +5109,7 @@
         <v>2.0</v>
       </c>
       <c r="AM41" s="1" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="AN41" s="3">
         <v>0.0</v>
@@ -3970,19 +5141,19 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>66</v>
@@ -3990,7 +5161,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>69</v>
@@ -3999,7 +5170,7 @@
         <v>54</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>71</v>
@@ -4010,13 +5181,13 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>55</v>
@@ -4030,7 +5201,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>69</v>
@@ -4040,7 +5211,7 @@
       <c r="E45" s="1"/>
       <c r="G45" s="1"/>
       <c r="H45" s="1" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>55</v>
@@ -4057,7 +5228,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>69</v>
@@ -4070,7 +5241,7 @@
         <v>2.0</v>
       </c>
       <c r="Q46" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="R46" s="1" t="s">
         <v>54</v>
@@ -4127,7 +5298,7 @@
         <v>1.0</v>
       </c>
       <c r="AM46" s="1" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="AN46" s="3">
         <v>0.0</v>
@@ -4159,7 +5330,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>76</v>
@@ -4179,7 +5350,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>76</v>
@@ -4194,12 +5365,12 @@
         <v>58</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>76</v>
@@ -4228,7 +5399,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>76</v>
@@ -4288,7 +5459,7 @@
         <v>0.0</v>
       </c>
       <c r="AM50" s="1" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="AN50" s="3">
         <v>1.0</v>
@@ -4320,10 +5491,10 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>50</v>
@@ -4340,10 +5511,10 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>54</v>
@@ -4360,10 +5531,10 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>57</v>
@@ -4389,10 +5560,10 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="P54" s="3">
         <v>1.0</v>
@@ -4458,7 +5629,7 @@
         <v>1.0</v>
       </c>
       <c r="AM54" s="1" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="AN54" s="3">
         <v>1.0</v>
@@ -4490,10 +5661,10 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>50</v>
@@ -4502,18 +5673,18 @@
         <v>51</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>54</v>
@@ -4525,15 +5696,15 @@
         <v>58</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>57</v>
@@ -4542,10 +5713,10 @@
         <v>51</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="M57" s="3">
         <v>1.0</v>
@@ -4559,22 +5730,22 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>58</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="M58" s="3">
         <v>3.0</v>
@@ -4588,10 +5759,10 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="P59" s="3">
         <v>0.0</v>
@@ -4648,7 +5819,7 @@
         <v>0.0</v>
       </c>
       <c r="AM59" s="1" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="AN59" s="3">
         <v>2.0</v>
@@ -4680,10 +5851,10 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>63</v>
@@ -4695,15 +5866,15 @@
         <v>58</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H61" s="1" t="s">
         <v>57</v>
@@ -4729,10 +5900,10 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="P62" s="3">
         <v>0.0</v>
@@ -4789,7 +5960,7 @@
         <v>1.0</v>
       </c>
       <c r="AM62" s="1" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="AN62" s="3">
         <v>1.0</v>
@@ -4821,7 +5992,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>49</v>
@@ -4841,13 +6012,13 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>55</v>
@@ -4861,7 +6032,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>49</v>
@@ -4871,7 +6042,7 @@
       <c r="E65" s="1"/>
       <c r="G65" s="1"/>
       <c r="H65" s="1" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>53</v>
@@ -4894,7 +6065,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>49</v>
@@ -4961,7 +6132,7 @@
         <v>0.0</v>
       </c>
       <c r="AM66" s="1" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="AN66" s="3">
         <v>1.0</v>
@@ -4993,7 +6164,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>62</v>
@@ -5013,7 +6184,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>62</v>
@@ -5033,7 +6204,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>62</v>
@@ -5045,15 +6216,15 @@
         <v>55</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>62</v>
@@ -5082,7 +6253,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>62</v>
@@ -5142,7 +6313,7 @@
         <v>2.0</v>
       </c>
       <c r="AM71" s="1" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="AN71" s="3">
         <v>1.0</v>
@@ -5174,7 +6345,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>69</v>
@@ -5194,13 +6365,13 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>55</v>
@@ -5214,7 +6385,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>69</v>
@@ -5277,7 +6448,7 @@
         <v>2.0</v>
       </c>
       <c r="AM74" s="1" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="AN74" s="3">
         <v>0.0</v>
@@ -5309,7 +6480,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>76</v>
@@ -5321,15 +6492,15 @@
         <v>51</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>76</v>
@@ -5338,7 +6509,7 @@
         <v>54</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>58</v>
@@ -5349,7 +6520,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>76</v>
@@ -5378,7 +6549,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>76</v>
@@ -5441,7 +6612,7 @@
         <v>0.0</v>
       </c>
       <c r="AM78" s="1" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="AN78" s="3">
         <v>1.0</v>
@@ -5473,10 +6644,10 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>54</v>
@@ -5488,15 +6659,15 @@
         <v>58</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="H80" s="1" t="s">
         <v>57</v>
@@ -5522,10 +6693,10 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="P81" s="3">
         <v>0.0</v>
@@ -5585,7 +6756,7 @@
         <v>1.0</v>
       </c>
       <c r="AM81" s="1" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="AN81" s="3">
         <v>1.0</v>
@@ -5617,10 +6788,10 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>50</v>
@@ -5637,10 +6808,10 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>63</v>
@@ -5652,15 +6823,15 @@
         <v>58</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H84" s="1" t="s">
         <v>57</v>
@@ -5669,7 +6840,7 @@
         <v>53</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="L84" s="2" t="s">
         <v>56</v>
@@ -5686,10 +6857,10 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="P85" s="3">
         <v>8.0</v>
@@ -5746,7 +6917,7 @@
         <v>1.0</v>
       </c>
       <c r="AM85" s="1" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="AN85" s="3">
         <v>1.0</v>
@@ -5778,10 +6949,10 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>63</v>
@@ -5793,15 +6964,15 @@
         <v>58</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H87" s="1" t="s">
         <v>57</v>
@@ -5827,10 +6998,10 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="P88" s="3">
         <v>3.0</v>
@@ -5887,7 +7058,7 @@
         <v>1.0</v>
       </c>
       <c r="AM88" s="1" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="AN88" s="3">
         <v>1.0</v>
@@ -5919,7 +7090,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>49</v>
@@ -5939,13 +7110,13 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="I90" s="2" t="s">
         <v>53</v>
@@ -5968,7 +7139,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>49</v>
@@ -6028,7 +7199,7 @@
         <v>2.0</v>
       </c>
       <c r="AM91" s="1" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="AN91" s="3">
         <v>1.0</v>
@@ -6060,7 +7231,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>62</v>
@@ -6080,7 +7251,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>62</v>
@@ -6109,13 +7280,13 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="I94" s="2" t="s">
         <v>55</v>
@@ -6138,7 +7309,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>62</v>
@@ -6198,7 +7369,7 @@
         <v>0.0</v>
       </c>
       <c r="AM95" s="1" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="AN95" s="3">
         <v>2.0</v>
@@ -6230,7 +7401,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>69</v>
@@ -6250,7 +7421,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>69</v>
@@ -6310,7 +7481,7 @@
         <v>0.0</v>
       </c>
       <c r="AM97" s="1" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="AN97" s="3">
         <v>0.0</v>
@@ -6342,7 +7513,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>76</v>
@@ -6357,12 +7528,12 @@
         <v>58</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>76</v>
@@ -6374,7 +7545,7 @@
         <v>53</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="L99" s="2" t="s">
         <v>56</v>
@@ -6385,7 +7556,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>76</v>
@@ -6445,7 +7616,7 @@
         <v>0.0</v>
       </c>
       <c r="AM100" s="1" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="AN100" s="3">
         <v>0.0</v>
@@ -6477,10 +7648,10 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>63</v>
@@ -6492,15 +7663,15 @@
         <v>58</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="H102" s="1" t="s">
         <v>57</v>
@@ -6517,10 +7688,10 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="P103" s="3">
         <v>0.0</v>
@@ -6609,10 +7780,10 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>54</v>
@@ -6624,27 +7795,27 @@
         <v>58</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H105" s="1" t="s">
         <v>57</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="J105" s="2" t="s">
         <v>58</v>
       </c>
       <c r="L105" s="2" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="M105" s="3">
         <v>8.0</v>
@@ -6652,10 +7823,10 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="P106" s="3">
         <v>1.0</v>
@@ -6718,7 +7889,7 @@
         <v>2.0</v>
       </c>
       <c r="AM106" s="1" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="AN106" s="3">
         <v>0.0</v>
@@ -6750,10 +7921,10 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>54</v>
@@ -6762,7 +7933,7 @@
         <v>51</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>160</v>
+        <v>83</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>78</v>
@@ -6770,10 +7941,10 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H108" s="1" t="s">
         <v>57</v>
@@ -6782,10 +7953,10 @@
         <v>53</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>161</v>
+        <v>101</v>
       </c>
       <c r="L108" s="2" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="M108" s="3">
         <v>9.0</v>
@@ -6793,10 +7964,10 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="P109" s="3">
         <v>1.0</v>
@@ -6853,7 +8024,7 @@
         <v>2.0</v>
       </c>
       <c r="AM109" s="1" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="AN109" s="3">
         <v>0.0</v>
@@ -7043,7 +8214,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>69</v>
@@ -7055,7 +8226,7 @@
         <v>51</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>64</v>
@@ -7063,7 +8234,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>69</v>
@@ -7072,7 +8243,7 @@
         <v>63</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>71</v>
@@ -7083,13 +8254,13 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>53</v>
@@ -7098,7 +8269,7 @@
         <v>71</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="M4" s="3">
         <v>15.0</v>
@@ -7112,7 +8283,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>69</v>
@@ -7175,7 +8346,7 @@
         <v>5.0</v>
       </c>
       <c r="AM5" s="1" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="AN5" s="3">
         <v>1.0</v>
@@ -7207,7 +8378,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>76</v>
@@ -7227,7 +8398,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>76</v>
@@ -7242,12 +8413,12 @@
         <v>58</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>76</v>
@@ -7267,7 +8438,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>76</v>
@@ -7296,7 +8467,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>76</v>
@@ -7356,7 +8527,7 @@
         <v>0.0</v>
       </c>
       <c r="AM10" s="1" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="AN10" s="3">
         <v>1.0</v>
@@ -7388,10 +8559,10 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>63</v>
@@ -7403,18 +8574,18 @@
         <v>58</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>53</v>
@@ -7423,7 +8594,7 @@
         <v>71</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="M12" s="3">
         <v>8.0</v>
@@ -7437,10 +8608,10 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="P13" s="3">
         <v>1.0</v>
@@ -7500,7 +8671,7 @@
         <v>3.0</v>
       </c>
       <c r="AM13" s="1" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="AN13" s="3">
         <v>1.0</v>
@@ -7532,10 +8703,10 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>63</v>
@@ -7552,19 +8723,19 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>70</v>
@@ -7572,10 +8743,10 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>54</v>
@@ -7587,15 +8758,15 @@
         <v>58</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>57</v>
@@ -7615,10 +8786,10 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="P18" s="3">
         <v>2.0</v>
@@ -7678,7 +8849,7 @@
         <v>0.0</v>
       </c>
       <c r="AM18" s="1" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="AN18" s="3">
         <v>0.0</v>
@@ -7710,10 +8881,10 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>54</v>
@@ -7730,10 +8901,10 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>63</v>
@@ -7745,15 +8916,15 @@
         <v>77</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>57</v>
@@ -7773,10 +8944,10 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="P22" s="3">
         <v>0.0</v>
@@ -7839,7 +9010,7 @@
         <v>2.0</v>
       </c>
       <c r="AM22" s="1" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="AN22" s="3">
         <v>0.0</v>
@@ -7871,7 +9042,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>49</v>
@@ -7891,7 +9062,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>49</v>
@@ -7901,7 +9072,7 @@
       <c r="E24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>51</v>
@@ -7924,7 +9095,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>49</v>
@@ -7988,7 +9159,7 @@
         <v>3.0</v>
       </c>
       <c r="AM25" s="1" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="AN25" s="3">
         <v>1.0</v>
@@ -8020,7 +9191,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>62</v>
@@ -8035,32 +9206,32 @@
         <v>65</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>177</v>
+        <v>96</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>64</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>62</v>
@@ -8070,7 +9241,7 @@
       <c r="E28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>53</v>
@@ -8093,7 +9264,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>62</v>
@@ -8109,7 +9280,7 @@
         <v>50</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>177</v>
+        <v>96</v>
       </c>
       <c r="S29" s="3">
         <v>13413.0</v>
@@ -8157,7 +9328,7 @@
         <v>7.0</v>
       </c>
       <c r="AM29" s="1" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="AN29" s="3">
         <v>1.0</v>
@@ -8189,7 +9360,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>69</v>
@@ -8209,7 +9380,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>69</v>
@@ -8219,7 +9390,7 @@
       <c r="E31" s="1"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>53</v>
@@ -8228,7 +9399,7 @@
         <v>71</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="M31" s="3">
         <v>12.0</v>
@@ -8242,7 +9413,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>69</v>
@@ -8258,7 +9429,7 @@
         <v>50</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="S32" s="3">
         <v>12040.0</v>
@@ -8309,7 +9480,7 @@
         <v>9.0</v>
       </c>
       <c r="AM32" s="1" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="AN32" s="3">
         <v>1.0</v>
@@ -8341,7 +9512,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>76</v>
@@ -8356,12 +9527,12 @@
         <v>58</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>76</v>
@@ -8390,7 +9561,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>76</v>
@@ -8450,7 +9621,7 @@
         <v>0.0</v>
       </c>
       <c r="AM35" s="1" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="AN35" s="3">
         <v>1.0</v>
@@ -8482,10 +9653,10 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>63</v>
@@ -8497,15 +9668,15 @@
         <v>58</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>57</v>
@@ -8531,10 +9702,10 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="P38" s="3">
         <v>0.0</v>
@@ -8591,7 +9762,7 @@
         <v>0.0</v>
       </c>
       <c r="AM38" s="1" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="AN38" s="3">
         <v>1.0</v>
@@ -8623,10 +9794,10 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>50</v>
@@ -8643,16 +9814,16 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>58</v>
@@ -8663,19 +9834,19 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>78</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>56</v>
@@ -8683,13 +9854,13 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>51</v>
@@ -8703,10 +9874,10 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>57</v>
@@ -8732,10 +9903,10 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="P44" s="3">
         <v>0.0</v>
@@ -8792,7 +9963,7 @@
         <v>1.0</v>
       </c>
       <c r="AM44" s="1" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="AN44" s="3">
         <v>1.0</v>
@@ -8824,10 +9995,10 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>50</v>
@@ -8839,15 +10010,15 @@
         <v>77</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>54</v>
@@ -8864,13 +10035,13 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>55</v>
@@ -8884,17 +10055,17 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>53</v>
@@ -8908,10 +10079,10 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
@@ -8941,10 +10112,10 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
@@ -9008,7 +10179,7 @@
         <v>1.0</v>
       </c>
       <c r="AM50" s="1" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="AN50" s="3">
         <v>1.0</v>
@@ -9040,7 +10211,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>49</v>
@@ -9052,15 +10223,15 @@
         <v>51</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>49</v>
@@ -9080,13 +10251,13 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>53</v>
@@ -9103,7 +10274,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>49</v>
@@ -9166,7 +10337,7 @@
         <v>3.0</v>
       </c>
       <c r="AM54" s="1" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="AN54" s="3">
         <v>0.0</v>
@@ -9198,7 +10369,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>62</v>
@@ -9218,7 +10389,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>62</v>
@@ -9230,30 +10401,30 @@
         <v>55</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>53</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="M57" s="3">
         <v>13.0</v>
@@ -9261,7 +10432,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>62</v>
@@ -9324,7 +10495,7 @@
         <v>5.0</v>
       </c>
       <c r="AM58" s="1" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="AN58" s="3">
         <v>0.0</v>
@@ -9356,7 +10527,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>69</v>
@@ -9376,13 +10547,13 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>53</v>
@@ -9391,7 +10562,7 @@
         <v>71</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="M60" s="3">
         <v>9.0</v>
@@ -9399,7 +10570,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>69</v>
@@ -9459,7 +10630,7 @@
         <v>6.0</v>
       </c>
       <c r="AM61" s="1" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="AN61" s="3">
         <v>0.0</v>
@@ -9491,7 +10662,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>76</v>
@@ -9511,7 +10682,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>76</v>
@@ -9526,12 +10697,12 @@
         <v>58</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>76</v>
@@ -9543,10 +10714,10 @@
         <v>53</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="M64" s="3">
         <v>6.0</v>
@@ -9560,7 +10731,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>76</v>
@@ -9620,7 +10791,7 @@
         <v>2.0</v>
       </c>
       <c r="AM65" s="1" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="AN65" s="3">
         <v>1.0</v>
@@ -9652,10 +10823,10 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>63</v>
@@ -9667,15 +10838,15 @@
         <v>58</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="H67" s="1" t="s">
         <v>57</v>
@@ -9701,10 +10872,10 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="P68" s="3">
         <v>0.0</v>
@@ -9761,7 +10932,7 @@
         <v>0.0</v>
       </c>
       <c r="AM68" s="1" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="AN68" s="3">
         <v>1.0</v>
@@ -9793,10 +10964,10 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>63</v>
@@ -9813,10 +10984,10 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H70" s="1" t="s">
         <v>57</v>
@@ -9842,10 +11013,10 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="P71" s="3">
         <v>0.0</v>
@@ -9902,7 +11073,7 @@
         <v>0.0</v>
       </c>
       <c r="AM71" s="1" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="AN71" s="3">
         <v>1.0</v>
@@ -9934,10 +11105,10 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>50</v>
@@ -9954,10 +11125,10 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>54</v>
@@ -9969,18 +11140,18 @@
         <v>58</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>77</v>
@@ -9994,10 +11165,10 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H75" s="1" t="s">
         <v>57</v>
@@ -10023,10 +11194,10 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="P76" s="3">
         <v>2.0</v>
@@ -10086,7 +11257,7 @@
         <v>0.0</v>
       </c>
       <c r="AM76" s="1" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="AN76" s="3">
         <v>1.0</v>
@@ -10118,7 +11289,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>49</v>
@@ -10138,13 +11309,13 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>55</v>
@@ -10153,12 +11324,12 @@
         <v>58</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>49</v>
@@ -10218,7 +11389,7 @@
         <v>4.0</v>
       </c>
       <c r="AM79" s="1" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="AN79" s="3">
         <v>0.0</v>
@@ -10250,7 +11421,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>62</v>
@@ -10262,15 +11433,15 @@
         <v>51</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>62</v>
@@ -10290,7 +11461,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>62</v>
@@ -10302,15 +11473,15 @@
         <v>78</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>62</v>
@@ -10370,7 +11541,7 @@
         <v>5.0</v>
       </c>
       <c r="AM83" s="1" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="AN83" s="3">
         <v>0.0</v>
@@ -10402,7 +11573,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>69</v>
@@ -10422,7 +11593,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>69</v>
@@ -10482,7 +11653,7 @@
         <v>2.0</v>
       </c>
       <c r="AM85" s="1" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="AN85" s="3">
         <v>0.0</v>
@@ -10514,7 +11685,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>76</v>
@@ -10529,12 +11700,12 @@
         <v>58</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>76</v>
@@ -10546,7 +11717,7 @@
         <v>51</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>64</v>
@@ -10554,7 +11725,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>76</v>
@@ -10583,7 +11754,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>76</v>
@@ -10643,7 +11814,7 @@
         <v>0.0</v>
       </c>
       <c r="AM89" s="1" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="AN89" s="3">
         <v>1.0</v>
@@ -10675,10 +11846,10 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>50</v>
@@ -10687,18 +11858,18 @@
         <v>51</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>54</v>
@@ -10710,15 +11881,15 @@
         <v>58</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="H92" s="1" t="s">
         <v>57</v>
@@ -10744,10 +11915,10 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="P93" s="3">
         <v>2.0</v>
@@ -10807,7 +11978,7 @@
         <v>0.0</v>
       </c>
       <c r="AM93" s="1" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="AN93" s="3">
         <v>1.0</v>
@@ -10839,10 +12010,10 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>50</v>
@@ -10851,18 +12022,18 @@
         <v>51</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>54</v>
@@ -10874,15 +12045,15 @@
         <v>58</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H96" s="1" t="s">
         <v>57</v>
@@ -10908,10 +12079,10 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="P97" s="3">
         <v>2.0</v>
@@ -10971,7 +12142,7 @@
         <v>1.0</v>
       </c>
       <c r="AM97" s="1" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="AN97" s="3">
         <v>1.0</v>
@@ -11003,10 +12174,10 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>63</v>
@@ -11018,15 +12189,15 @@
         <v>58</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H99" s="1" t="s">
         <v>57</v>
@@ -11052,10 +12223,10 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="P100" s="3">
         <v>0.0</v>
@@ -11115,7 +12286,7 @@
         <v>2.0</v>
       </c>
       <c r="AM100" s="1" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="AN100" s="3">
         <v>1.0</v>
@@ -11147,7 +12318,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>49</v>
@@ -11167,16 +12338,16 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>65</v>
@@ -11187,7 +12358,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>49</v>
@@ -11247,7 +12418,7 @@
         <v>4.0</v>
       </c>
       <c r="AM103" s="1" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="AN103" s="3">
         <v>0.0</v>
@@ -11279,7 +12450,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>62</v>
@@ -11291,15 +12462,15 @@
         <v>51</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>62</v>
@@ -11319,42 +12490,42 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>77</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="J107" s="2" t="s">
         <v>64</v>
       </c>
       <c r="L107" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="M107" s="3">
         <v>11.0</v>
@@ -11368,13 +12539,13 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="I108" s="2" t="s">
         <v>53</v>
@@ -11391,7 +12562,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>62</v>
@@ -11454,7 +12625,7 @@
         <v>1.0</v>
       </c>
       <c r="AM109" s="1" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="AN109" s="3">
         <v>1.0</v>
@@ -11486,7 +12657,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>69</v>
@@ -11506,13 +12677,13 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>55</v>
@@ -11526,7 +12697,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>69</v>
@@ -11546,7 +12717,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>69</v>
@@ -11610,7 +12781,7 @@
         <v>3.0</v>
       </c>
       <c r="AM113" s="1" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="AN113" s="3">
         <v>0.0</v>
@@ -11642,7 +12813,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>76</v>
@@ -11662,7 +12833,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>76</v>
@@ -11682,7 +12853,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>76</v>
@@ -11702,7 +12873,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>76</v>
@@ -11731,7 +12902,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>76</v>
@@ -11794,7 +12965,7 @@
         <v>0.0</v>
       </c>
       <c r="AM118" s="1" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="AN118" s="3">
         <v>1.0</v>
@@ -11826,10 +12997,10 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>50</v>
@@ -11846,10 +13017,10 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>54</v>
@@ -11861,18 +13032,18 @@
         <v>58</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="I121" s="2" t="s">
         <v>51</v>
@@ -11889,10 +13060,10 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="H122" s="1" t="s">
         <v>57</v>
@@ -11918,10 +13089,10 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="P123" s="3">
         <v>0.0</v>
@@ -11984,7 +13155,7 @@
         <v>0.0</v>
       </c>
       <c r="AM123" s="1" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="AN123" s="3">
         <v>1.0</v>
@@ -12174,13 +13345,13 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>51</v>
@@ -12194,13 +13365,13 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>53</v>
@@ -12209,7 +13380,7 @@
         <v>71</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="M3" s="3">
         <v>10.0</v>
@@ -12223,7 +13394,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>69</v>
@@ -12277,7 +13448,7 @@
         <v>0.0</v>
       </c>
       <c r="AM4" s="1" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="AN4" s="3">
         <v>1.0</v>
@@ -12309,7 +13480,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>76</v>
@@ -12324,12 +13495,12 @@
         <v>58</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>76</v>
@@ -12358,7 +13529,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>76</v>
@@ -12418,7 +13589,7 @@
         <v>1.0</v>
       </c>
       <c r="AM7" s="1" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="AN7" s="3">
         <v>1.0</v>
@@ -12450,10 +13621,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>63</v>
@@ -12465,18 +13636,18 @@
         <v>58</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>53</v>
@@ -12499,13 +13670,13 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>51</v>
@@ -12522,10 +13693,10 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="P11" s="3">
         <v>0.0</v>
@@ -12579,7 +13750,7 @@
         <v>0.0</v>
       </c>
       <c r="AM11" s="1" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="AN11" s="3">
         <v>1.0</v>
@@ -12611,13 +13782,13 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>51</v>
@@ -12626,18 +13797,18 @@
         <v>58</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>53</v>
@@ -12660,19 +13831,19 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="P14" s="3">
         <v>0.0</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="S14" s="3">
         <v>15925.179999999997</v>
@@ -12720,7 +13891,7 @@
         <v>0.0</v>
       </c>
       <c r="AM14" s="1" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="AN14" s="3">
         <v>1.0</v>
@@ -12752,10 +13923,10 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>63</v>
@@ -12767,18 +13938,18 @@
         <v>58</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>51</v>
@@ -12795,10 +13966,10 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>57</v>
@@ -12824,10 +13995,10 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="P18" s="3">
         <v>0.0</v>
@@ -12881,7 +14052,7 @@
         <v>0.0</v>
       </c>
       <c r="AM18" s="1" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="AN18" s="3">
         <v>1.0</v>
@@ -12913,13 +14084,13 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>51</v>
@@ -12933,13 +14104,13 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>55</v>
@@ -12953,7 +14124,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>49</v>
@@ -12982,7 +14153,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>49</v>
@@ -13036,7 +14207,7 @@
         <v>0.0</v>
       </c>
       <c r="AM22" s="1" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="AN22" s="3">
         <v>1.0</v>
@@ -13068,13 +14239,13 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>51</v>
@@ -13088,22 +14259,22 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>53</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="M24" s="3">
         <v>10.0</v>
@@ -13117,13 +14288,13 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>55</v>
@@ -13140,13 +14311,13 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>53</v>
@@ -13169,7 +14340,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>62</v>
@@ -13223,7 +14394,7 @@
         <v>1.0</v>
       </c>
       <c r="AM27" s="1" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="AN27" s="3">
         <v>2.0</v>
@@ -13255,13 +14426,13 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>51</v>
@@ -13275,16 +14446,16 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>71</v>
@@ -13304,19 +14475,19 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>53</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>56</v>
@@ -13333,16 +14504,16 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>71</v>
@@ -13362,7 +14533,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>69</v>
@@ -13371,10 +14542,10 @@
         <v>0.0</v>
       </c>
       <c r="Q32" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="S32" s="3">
         <v>9567.0</v>
@@ -13422,7 +14593,7 @@
         <v>0.0</v>
       </c>
       <c r="AM32" s="1" t="s">
-        <v>260</v>
+        <v>274</v>
       </c>
       <c r="AN32" s="3">
         <v>3.0</v>
@@ -13454,13 +14625,13 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>76</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>51</v>
@@ -13474,7 +14645,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>76</v>
@@ -13489,18 +14660,18 @@
         <v>58</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>53</v>
@@ -13523,16 +14694,16 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>58</v>
@@ -13552,7 +14723,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>76</v>
@@ -13561,7 +14732,7 @@
         <v>1.0</v>
       </c>
       <c r="Q37" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="R37" s="1" t="s">
         <v>63</v>
@@ -13612,7 +14783,7 @@
         <v>0.0</v>
       </c>
       <c r="AM37" s="1" t="s">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="AN37" s="3">
         <v>2.0</v>
@@ -13644,13 +14815,13 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>51</v>
@@ -13659,18 +14830,18 @@
         <v>58</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>53</v>
@@ -13693,13 +14864,13 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>55</v>
@@ -13708,7 +14879,7 @@
         <v>58</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="M40" s="3">
         <v>6.0</v>
@@ -13722,19 +14893,19 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="P41" s="3">
         <v>0.0</v>
       </c>
       <c r="Q41" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="S41" s="3">
         <v>6459.0</v>
@@ -13782,7 +14953,7 @@
         <v>0.0</v>
       </c>
       <c r="AM41" s="1" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="AN41" s="3">
         <v>2.0</v>
@@ -13814,10 +14985,10 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>63</v>
@@ -13829,15 +15000,15 @@
         <v>58</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>57</v>
@@ -13863,10 +15034,10 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="P44" s="3">
         <v>0.0</v>
@@ -13923,7 +15094,7 @@
         <v>0.0</v>
       </c>
       <c r="AM44" s="1" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="AN44" s="3">
         <v>1.0</v>
@@ -13955,10 +15126,10 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>63</v>
@@ -13970,18 +15141,18 @@
         <v>58</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>51</v>
@@ -13998,10 +15169,10 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>57</v>
@@ -14027,10 +15198,10 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="P48" s="3">
         <v>1.0</v>
@@ -14119,13 +15290,13 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>51</v>
@@ -14139,13 +15310,13 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>55</v>
@@ -14159,7 +15330,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>49</v>
@@ -14171,10 +15342,10 @@
         <v>53</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>160</v>
+        <v>83</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="M51" s="3">
         <v>13.0</v>
@@ -14188,7 +15359,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>49</v>
@@ -14197,10 +15368,10 @@
         <v>1.0</v>
       </c>
       <c r="Q52" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="R52" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="S52" s="3">
         <v>23294.0</v>
@@ -14245,7 +15416,7 @@
         <v>4.0</v>
       </c>
       <c r="AM52" s="1" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="AN52" s="3">
         <v>1.0</v>
@@ -14277,13 +15448,13 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>70</v>
@@ -14297,13 +15468,13 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>55</v>
@@ -14317,13 +15488,13 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>53</v>
@@ -14346,7 +15517,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>62</v>
@@ -14400,7 +15571,7 @@
         <v>0.0</v>
       </c>
       <c r="AM56" s="1" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="AN56" s="3">
         <v>1.0</v>
@@ -14432,7 +15603,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>69</v>
@@ -14452,7 +15623,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>69</v>
@@ -14472,7 +15643,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>69</v>
@@ -14535,7 +15706,7 @@
         <v>0.0</v>
       </c>
       <c r="AM59" s="1" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="AN59" s="3">
         <v>0.0</v>
@@ -14567,13 +15738,13 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>51</v>
@@ -14582,7 +15753,7 @@
         <v>58</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="N60" s="1" t="b">
         <v>1</v>
@@ -14590,7 +15761,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>76</v>
@@ -14619,7 +15790,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>76</v>
@@ -14673,7 +15844,7 @@
         <v>1.0</v>
       </c>
       <c r="AM62" s="1" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="AN62" s="3">
         <v>1.0</v>
@@ -14705,10 +15876,10 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>63</v>
@@ -14720,18 +15891,18 @@
         <v>58</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>51</v>
@@ -14748,10 +15919,10 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="H65" s="1" t="s">
         <v>57</v>
@@ -14777,10 +15948,10 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="P66" s="3">
         <v>0.0</v>
@@ -14834,7 +16005,7 @@
         <v>1.0</v>
       </c>
       <c r="AM66" s="1" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="AN66" s="3">
         <v>1.0</v>
@@ -14866,10 +16037,10 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>63</v>
@@ -14881,15 +16052,15 @@
         <v>58</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H68" s="1" t="s">
         <v>57</v>
@@ -14915,10 +16086,10 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="P69" s="3">
         <v>0.0</v>
@@ -14975,7 +16146,7 @@
         <v>0.0</v>
       </c>
       <c r="AM69" s="1" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="AN69" s="3">
         <v>1.0</v>
@@ -15007,10 +16178,10 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>63</v>
@@ -15022,15 +16193,15 @@
         <v>58</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H71" s="1" t="s">
         <v>57</v>
@@ -15056,10 +16227,10 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="P72" s="3">
         <v>0.0</v>
@@ -15116,7 +16287,7 @@
         <v>0.0</v>
       </c>
       <c r="AM72" s="1" t="s">
-        <v>278</v>
+        <v>84</v>
       </c>
       <c r="AN72" s="3">
         <v>1.0</v>
@@ -15148,7 +16319,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>49</v>
@@ -15168,16 +16339,16 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>58</v>
@@ -15188,7 +16359,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>49</v>
@@ -15200,7 +16371,7 @@
         <v>53</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="L75" s="2" t="s">
         <v>56</v>
@@ -15217,13 +16388,13 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>51</v>
@@ -15232,7 +16403,7 @@
         <v>58</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="M76" s="3">
         <v>11.0</v>
@@ -15246,7 +16417,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>49</v>
@@ -15303,7 +16474,7 @@
         <v>0.0</v>
       </c>
       <c r="AM77" s="1" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="AN77" s="3">
         <v>2.0</v>
@@ -15335,7 +16506,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>62</v>
@@ -15347,21 +16518,21 @@
         <v>55</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="I79" s="2" t="s">
         <v>51</v>
@@ -15370,7 +16541,7 @@
         <v>58</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="M79" s="3">
         <v>10.0</v>
@@ -15378,7 +16549,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>62</v>
@@ -15435,7 +16606,7 @@
         <v>3.0</v>
       </c>
       <c r="AM80" s="1" t="s">
-        <v>282</v>
+        <v>295</v>
       </c>
       <c r="AN80" s="3">
         <v>0.0</v>
@@ -15467,7 +16638,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>69</v>
@@ -15487,13 +16658,13 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="I82" s="2" t="s">
         <v>53</v>
@@ -15510,7 +16681,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>69</v>
@@ -15570,7 +16741,7 @@
         <v>3.0</v>
       </c>
       <c r="AM83" s="1" t="s">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="AN83" s="3">
         <v>0.0</v>
@@ -15602,7 +16773,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>76</v>
@@ -15617,12 +16788,12 @@
         <v>58</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>76</v>
@@ -15645,13 +16816,13 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="I86" s="2" t="s">
         <v>53</v>
@@ -15665,13 +16836,13 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="I87" s="2" t="s">
         <v>77</v>
@@ -15685,7 +16856,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>76</v>
@@ -15745,7 +16916,7 @@
         <v>2.0</v>
       </c>
       <c r="AM88" s="1" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="AN88" s="3">
         <v>0.0</v>
@@ -15777,10 +16948,10 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>54</v>
@@ -15797,10 +16968,10 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="H90" s="1" t="s">
         <v>57</v>
@@ -15820,10 +16991,10 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="P91" s="3">
         <v>2.0</v>
@@ -15883,7 +17054,7 @@
         <v>2.0</v>
       </c>
       <c r="AM91" s="1" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="AN91" s="3">
         <v>0.0</v>
@@ -15915,10 +17086,10 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>63</v>
@@ -15930,15 +17101,15 @@
         <v>58</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H93" s="1" t="s">
         <v>57</v>
@@ -15958,10 +17129,10 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="P94" s="3">
         <v>0.0</v>
@@ -16018,7 +17189,7 @@
         <v>0.0</v>
       </c>
       <c r="AM94" s="1" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="AN94" s="3">
         <v>0.0</v>
@@ -16050,10 +17221,10 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>63</v>
@@ -16065,15 +17236,15 @@
         <v>58</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H96" s="1" t="s">
         <v>57</v>
@@ -16093,10 +17264,10 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="P97" s="3">
         <v>0.0</v>
@@ -16153,7 +17324,7 @@
         <v>3.0</v>
       </c>
       <c r="AM97" s="1" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="AN97" s="3">
         <v>0.0</v>
@@ -16185,13 +17356,13 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>51</v>
@@ -16205,7 +17376,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>49</v>
@@ -16225,7 +17396,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>49</v>
@@ -16240,18 +17411,18 @@
         <v>58</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="I101" s="2" t="s">
         <v>55</v>
@@ -16274,7 +17445,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>49</v>
@@ -16283,7 +17454,7 @@
         <v>2.0</v>
       </c>
       <c r="Q102" s="1" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="R102" s="1" t="s">
         <v>63</v>
@@ -16334,7 +17505,7 @@
         <v>0.0</v>
       </c>
       <c r="AM102" s="1" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="AN102" s="3">
         <v>1.0</v>
@@ -16366,7 +17537,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>62</v>
@@ -16378,15 +17549,15 @@
         <v>53</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>161</v>
+        <v>101</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>62</v>
@@ -16395,24 +17566,24 @@
         <v>54</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>64</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="I105" s="2" t="s">
         <v>53</v>
@@ -16435,7 +17606,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>62</v>
@@ -16495,7 +17666,7 @@
         <v>1.0</v>
       </c>
       <c r="AM106" s="1" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="AN106" s="3">
         <v>1.0</v>
@@ -16685,13 +17856,13 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>51</v>
@@ -16700,18 +17871,18 @@
         <v>58</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>53</v>
@@ -16725,16 +17896,16 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>58</v>
@@ -16745,22 +17916,22 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>53</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="M5" s="3">
         <v>6.0</v>
@@ -16774,10 +17945,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>57</v>
@@ -16789,7 +17960,7 @@
         <v>58</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="M6" s="3">
         <v>3.0</v>
@@ -16803,10 +17974,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="P7" s="3">
         <v>0.0</v>
@@ -16857,7 +18028,7 @@
         <v>0.0</v>
       </c>
       <c r="AM7" s="1" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="AN7" s="3">
         <v>2.0</v>
@@ -16889,7 +18060,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>49</v>
@@ -16904,18 +18075,18 @@
         <v>58</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>55</v>
@@ -16929,7 +18100,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>49</v>
@@ -16958,7 +18129,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>49</v>
@@ -16970,7 +18141,7 @@
         <v>63</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="S11" s="3">
         <v>14680.0</v>
@@ -17018,7 +18189,7 @@
         <v>0.0</v>
       </c>
       <c r="AM11" s="1" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="AN11" s="3">
         <v>1.0</v>
@@ -17050,7 +18221,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>62</v>
@@ -17070,42 +18241,42 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>55</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>53</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>160</v>
+        <v>83</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="M14" s="3">
         <v>17.0</v>
@@ -17119,7 +18290,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>62</v>
@@ -17131,7 +18302,7 @@
         <v>63</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="S15" s="3">
         <v>13889.0</v>
@@ -17179,7 +18350,7 @@
         <v>0.0</v>
       </c>
       <c r="AM15" s="1" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="AN15" s="3">
         <v>1.0</v>
@@ -17211,13 +18382,13 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>51</v>
@@ -17231,13 +18402,13 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>53</v>
@@ -17246,7 +18417,7 @@
         <v>71</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="M17" s="3">
         <v>7.0</v>
@@ -17260,13 +18431,13 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>78</v>
@@ -17275,12 +18446,12 @@
         <v>71</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>69</v>
@@ -17334,7 +18505,7 @@
         <v>0.0</v>
       </c>
       <c r="AM19" s="1" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="AN19" s="3">
         <v>1.0</v>
@@ -17366,7 +18537,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>76</v>
@@ -17381,18 +18552,18 @@
         <v>58</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>53</v>
@@ -17415,7 +18586,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>76</v>
@@ -17475,7 +18646,7 @@
         <v>0.0</v>
       </c>
       <c r="AM22" s="1" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="AN22" s="3">
         <v>1.0</v>
@@ -17507,10 +18678,10 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>63</v>
@@ -17522,18 +18693,18 @@
         <v>58</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>53</v>
@@ -17556,10 +18727,10 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="P25" s="3">
         <v>1.0</v>
@@ -17616,7 +18787,7 @@
         <v>0.0</v>
       </c>
       <c r="AM25" s="1" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c r="AN25" s="3">
         <v>1.0</v>
@@ -17648,13 +18819,13 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>53</v>
@@ -17668,13 +18839,13 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>51</v>
@@ -17683,15 +18854,15 @@
         <v>65</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>57</v>
@@ -17703,7 +18874,7 @@
         <v>58</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="M28" s="3">
         <v>7.0</v>
@@ -17717,19 +18888,19 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="P29" s="3">
         <v>0.0</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="S29" s="3">
         <v>9627.0</v>
@@ -17777,7 +18948,7 @@
         <v>1.0</v>
       </c>
       <c r="AM29" s="1" t="s">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="AN29" s="3">
         <v>1.0</v>
@@ -17809,13 +18980,13 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>51</v>
@@ -17824,15 +18995,15 @@
         <v>58</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>57</v>
@@ -17844,7 +19015,7 @@
         <v>71</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="M31" s="3">
         <v>8.0</v>
@@ -17858,13 +19029,13 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>51</v>
@@ -17873,24 +19044,24 @@
         <v>65</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="P33" s="3">
         <v>1.0</v>
       </c>
       <c r="Q33" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="S33" s="3">
         <v>8650.0</v>
@@ -17938,7 +19109,7 @@
         <v>0.0</v>
       </c>
       <c r="AM33" s="1" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="AN33" s="3">
         <v>1.0</v>
@@ -17970,7 +19141,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>49</v>
@@ -17985,32 +19156,32 @@
         <v>58</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>55</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>49</v>
@@ -18039,7 +19210,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>49</v>
@@ -18051,7 +19222,7 @@
         <v>63</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="S37" s="3">
         <v>13913.0</v>
@@ -18099,7 +19270,7 @@
         <v>5.0</v>
       </c>
       <c r="AM37" s="1" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="AN37" s="3">
         <v>1.0</v>
@@ -18131,7 +19302,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>62</v>
@@ -18146,18 +19317,18 @@
         <v>58</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>55</v>
@@ -18171,13 +19342,13 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>53</v>
@@ -18200,7 +19371,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>62</v>
@@ -18212,7 +19383,7 @@
         <v>63</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="S41" s="3">
         <v>13277.0</v>
@@ -18260,7 +19431,7 @@
         <v>0.0</v>
       </c>
       <c r="AM41" s="1" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="AN41" s="3">
         <v>1.0</v>
@@ -18292,13 +19463,13 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>51</v>
@@ -18312,13 +19483,13 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>53</v>
@@ -18327,7 +19498,7 @@
         <v>71</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="M43" s="3">
         <v>8.0</v>
@@ -18341,13 +19512,13 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>55</v>
@@ -18361,7 +19532,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>69</v>
@@ -18370,10 +19541,10 @@
         <v>0.0</v>
       </c>
       <c r="Q45" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="R45" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="S45" s="3">
         <v>12722.0</v>
@@ -18421,7 +19592,7 @@
         <v>0.0</v>
       </c>
       <c r="AM45" s="1" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="AN45" s="3">
         <v>1.0</v>
@@ -18453,7 +19624,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>76</v>
@@ -18468,18 +19639,18 @@
         <v>58</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>53</v>
@@ -18502,13 +19673,13 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>55</v>
@@ -18522,7 +19693,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>76</v>
@@ -18582,7 +19753,7 @@
         <v>0.0</v>
       </c>
       <c r="AM49" s="1" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
       <c r="AN49" s="3">
         <v>1.0</v>
@@ -18614,10 +19785,10 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>63</v>
@@ -18634,13 +19805,13 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>51</v>
@@ -18649,7 +19820,7 @@
         <v>58</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="M51" s="3">
         <v>8.0</v>
@@ -18663,10 +19834,10 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="P52" s="3">
         <v>0.0</v>
@@ -18723,7 +19894,7 @@
         <v>0.0</v>
       </c>
       <c r="AM52" s="1" t="s">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="AN52" s="3">
         <v>1.0</v>
@@ -18755,13 +19926,13 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>55</v>
@@ -18775,10 +19946,10 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
@@ -18794,7 +19965,7 @@
         <v>71</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="M54" s="3">
         <v>7.0</v>
@@ -18808,17 +19979,17 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
       <c r="G55" s="1"/>
       <c r="H55" s="1" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>51</v>
@@ -18832,10 +20003,10 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
@@ -18890,7 +20061,7 @@
         <v>0.0</v>
       </c>
       <c r="AM56" s="1" t="s">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="AN56" s="3">
         <v>1.0</v>
@@ -18922,13 +20093,13 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>51</v>
@@ -18937,18 +20108,18 @@
         <v>58</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>53</v>
@@ -18971,13 +20142,13 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>51</v>
@@ -18991,19 +20162,19 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="P60" s="3">
         <v>0.0</v>
       </c>
       <c r="Q60" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="R60" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="S60" s="3">
         <v>18556.619999999995</v>
@@ -19051,7 +20222,7 @@
         <v>0.0</v>
       </c>
       <c r="AM60" s="1" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="AN60" s="3">
         <v>1.0</v>
@@ -19083,7 +20254,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>49</v>
@@ -19098,18 +20269,18 @@
         <v>58</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>55</v>
@@ -19123,7 +20294,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>49</v>
@@ -19133,7 +20304,7 @@
       <c r="E63" s="1"/>
       <c r="G63" s="1"/>
       <c r="H63" s="1" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>53</v>
@@ -19156,7 +20327,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>49</v>
@@ -19172,7 +20343,7 @@
         <v>63</v>
       </c>
       <c r="R64" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="S64" s="3">
         <v>21825.50999999999</v>
@@ -19220,7 +20391,7 @@
         <v>0.0</v>
       </c>
       <c r="AM64" s="1" t="s">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="AN64" s="3">
         <v>1.0</v>
@@ -19252,7 +20423,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>62</v>
@@ -19267,18 +20438,18 @@
         <v>58</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>55</v>
@@ -19292,13 +20463,13 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="I67" s="2" t="s">
         <v>53</v>
@@ -19321,7 +20492,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>62</v>
@@ -19375,7 +20546,7 @@
         <v>0.0</v>
       </c>
       <c r="AM68" s="1" t="s">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="AN68" s="3">
         <v>1.0</v>
@@ -19407,13 +20578,13 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>51</v>
@@ -19427,13 +20598,13 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>53</v>
@@ -19442,7 +20613,7 @@
         <v>71</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="M70" s="3">
         <v>15.0</v>
@@ -19456,7 +20627,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>69</v>
@@ -19510,7 +20681,7 @@
         <v>0.0</v>
       </c>
       <c r="AM71" s="1" t="s">
-        <v>332</v>
+        <v>345</v>
       </c>
       <c r="AN71" s="3">
         <v>1.0</v>
@@ -19542,7 +20713,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>76</v>
@@ -19557,18 +20728,18 @@
         <v>58</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>53</v>
@@ -19591,7 +20762,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>76</v>
@@ -19654,7 +20825,7 @@
         <v>0.0</v>
       </c>
       <c r="AM74" s="1" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
       <c r="AN74" s="3">
         <v>1.0</v>
@@ -19686,10 +20857,10 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>63</v>
@@ -19706,13 +20877,13 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>53</v>
@@ -19735,13 +20906,13 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>55</v>
@@ -19764,10 +20935,10 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="P78" s="3">
         <v>0.0</v>
@@ -19824,7 +20995,7 @@
         <v>0.0</v>
       </c>
       <c r="AM78" s="1" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="AN78" s="3">
         <v>2.0</v>
@@ -19856,13 +21027,13 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>51</v>
@@ -19871,18 +21042,18 @@
         <v>58</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="I80" s="2" t="s">
         <v>53</v>
@@ -19905,10 +21076,10 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H81" s="1" t="s">
         <v>57</v>
@@ -19934,19 +21105,19 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="P82" s="3">
         <v>0.0</v>
       </c>
       <c r="Q82" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="R82" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="S82" s="3">
         <v>12752.009999999998</v>
@@ -19991,7 +21162,7 @@
         <v>0.0</v>
       </c>
       <c r="AM82" s="1" t="s">
-        <v>337</v>
+        <v>350</v>
       </c>
       <c r="AN82" s="3">
         <v>2.0</v>
@@ -20023,13 +21194,13 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>55</v>
@@ -20038,15 +21209,15 @@
         <v>58</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H84" s="1" t="s">
         <v>57</v>
@@ -20072,13 +21243,13 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="I85" s="2" t="s">
         <v>51</v>
@@ -20095,16 +21266,16 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="P86" s="3">
         <v>0.0</v>
       </c>
       <c r="R86" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="S86" s="3">
         <v>17035.32</v>
@@ -20152,7 +21323,7 @@
         <v>0.0</v>
       </c>
       <c r="AM86" s="1" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="AN86" s="3">
         <v>1.0</v>
@@ -20184,7 +21355,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>339</v>
+        <v>352</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>49</v>
@@ -20199,18 +21370,18 @@
         <v>58</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>339</v>
+        <v>352</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>55</v>
@@ -20224,7 +21395,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>339</v>
+        <v>352</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>49</v>
@@ -20253,7 +21424,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>339</v>
+        <v>352</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>49</v>
@@ -20265,7 +21436,7 @@
         <v>63</v>
       </c>
       <c r="R90" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="S90" s="3">
         <v>25392.46</v>
@@ -20313,7 +21484,7 @@
         <v>0.0</v>
       </c>
       <c r="AM90" s="1" t="s">
-        <v>340</v>
+        <v>353</v>
       </c>
       <c r="AN90" s="3">
         <v>1.0</v>
@@ -20345,7 +21516,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>341</v>
+        <v>354</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>62</v>
@@ -20360,18 +21531,18 @@
         <v>58</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>341</v>
+        <v>354</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>55</v>
@@ -20385,22 +21556,22 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>341</v>
+        <v>354</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="I93" s="2" t="s">
         <v>53</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>160</v>
+        <v>83</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="M93" s="3">
         <v>15.0</v>
@@ -20414,7 +21585,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>341</v>
+        <v>354</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>62</v>
@@ -20426,7 +21597,7 @@
         <v>63</v>
       </c>
       <c r="R94" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="S94" s="3">
         <v>23475.639999999996</v>
@@ -20474,7 +21645,7 @@
         <v>0.0</v>
       </c>
       <c r="AM94" s="1" t="s">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="AN94" s="3">
         <v>1.0</v>
@@ -20506,13 +21677,13 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>51</v>
@@ -20526,22 +21697,22 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="I96" s="2" t="s">
         <v>53</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="M96" s="3">
         <v>8.0</v>
@@ -20555,7 +21726,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>69</v>
@@ -20564,10 +21735,10 @@
         <v>0.0</v>
       </c>
       <c r="Q97" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="R97" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="S97" s="3">
         <v>19985.18999999999</v>
@@ -20615,7 +21786,7 @@
         <v>0.0</v>
       </c>
       <c r="AM97" s="1" t="s">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c r="AN97" s="3">
         <v>1.0</v>
@@ -20647,7 +21818,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>76</v>
@@ -20662,18 +21833,18 @@
         <v>58</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="I99" s="2" t="s">
         <v>51</v>
@@ -20690,13 +21861,13 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="I100" s="2" t="s">
         <v>53</v>
@@ -20719,7 +21890,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>76</v>
@@ -20776,7 +21947,7 @@
         <v>0.0</v>
       </c>
       <c r="AM101" s="1" t="s">
-        <v>346</v>
+        <v>359</v>
       </c>
       <c r="AN101" s="3">
         <v>1.0</v>
@@ -20808,13 +21979,13 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>347</v>
+        <v>360</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>55</v>
@@ -20823,18 +21994,18 @@
         <v>58</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>347</v>
+        <v>360</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="I103" s="2" t="s">
         <v>51</v>
@@ -20851,10 +22022,10 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>347</v>
+        <v>360</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="H104" s="1" t="s">
         <v>57</v>
@@ -20880,16 +22051,16 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>347</v>
+        <v>360</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="P105" s="3">
         <v>0.0</v>
       </c>
       <c r="R105" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="S105" s="3">
         <v>12356.0</v>
@@ -20937,7 +22108,7 @@
         <v>0.0</v>
       </c>
       <c r="AM105" s="1" t="s">
-        <v>348</v>
+        <v>361</v>
       </c>
       <c r="AN105" s="3">
         <v>1.0</v>
@@ -20969,13 +22140,13 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>349</v>
+        <v>362</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>55</v>
@@ -20984,18 +22155,18 @@
         <v>58</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>349</v>
+        <v>362</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="I107" s="2" t="s">
         <v>51</v>
@@ -21012,10 +22183,10 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>349</v>
+        <v>362</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H108" s="1" t="s">
         <v>57</v>
@@ -21041,16 +22212,16 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>349</v>
+        <v>362</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="P109" s="3">
         <v>0.0</v>
       </c>
       <c r="R109" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="S109" s="3">
         <v>8748.0</v>
@@ -21098,7 +22269,7 @@
         <v>0.0</v>
       </c>
       <c r="AM109" s="1" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="AN109" s="3">
         <v>1.0</v>
@@ -21130,13 +22301,13 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>55</v>
@@ -21145,15 +22316,15 @@
         <v>58</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H111" s="1" t="s">
         <v>57</v>
@@ -21179,13 +22350,13 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="I112" s="2" t="s">
         <v>51</v>
@@ -21208,10 +22379,10 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="P113" s="3">
         <v>0.0</v>
@@ -21262,7 +22433,7 @@
         <v>0.0</v>
       </c>
       <c r="AM113" s="1" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="AN113" s="3">
         <v>2.0</v>
@@ -21294,13 +22465,13 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>55</v>
@@ -21314,13 +22485,13 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>55</v>
@@ -21329,18 +22500,18 @@
         <v>58</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="I116" s="2" t="s">
         <v>53</v>
@@ -21363,13 +22534,13 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="I117" s="2" t="s">
         <v>51</v>
@@ -21386,7 +22557,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>49</v>
@@ -21395,7 +22566,7 @@
         <v>1.0</v>
       </c>
       <c r="R118" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="S118" s="3">
         <v>22791.559999999998</v>
@@ -21443,7 +22614,7 @@
         <v>0.0</v>
       </c>
       <c r="AM118" s="1" t="s">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="AN118" s="3">
         <v>1.0</v>
@@ -21475,13 +22646,13 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>51</v>
@@ -21495,13 +22666,13 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>55</v>
@@ -21515,7 +22686,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>62</v>
@@ -21544,7 +22715,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>62</v>
@@ -21598,7 +22769,7 @@
         <v>0.0</v>
       </c>
       <c r="AM122" s="1" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="AN122" s="3">
         <v>1.0</v>

--- a/admin_testy/reporty_google_testy/google_data/Pobočky/Prosek/Databaze Prosek 2026.xlsx
+++ b/admin_testy/reporty_google_testy/google_data/Pobočky/Prosek/Databaze Prosek 2026.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3054" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3207" uniqueCount="384">
   <si>
     <t>Datum</t>
   </si>
@@ -330,6 +330,69 @@
     <t>14 min 17 s</t>
   </si>
   <si>
+    <t>12.05.2026</t>
+  </si>
+  <si>
+    <t>11 min 41 s</t>
+  </si>
+  <si>
+    <t>13.05.2026</t>
+  </si>
+  <si>
+    <t>Putna Jaroslav</t>
+  </si>
+  <si>
+    <t>14.05.2026</t>
+  </si>
+  <si>
+    <t>Ahurieva Viktoriia</t>
+  </si>
+  <si>
+    <t>12 min 40 s</t>
+  </si>
+  <si>
+    <t>15.05.2026</t>
+  </si>
+  <si>
+    <t>20:00</t>
+  </si>
+  <si>
+    <t>Gorol Patrik</t>
+  </si>
+  <si>
+    <t>12 min 38 s</t>
+  </si>
+  <si>
+    <t>16.05.2026</t>
+  </si>
+  <si>
+    <t>Hanibal Filip</t>
+  </si>
+  <si>
+    <t>13 min 01 s</t>
+  </si>
+  <si>
+    <t>17.05.2026</t>
+  </si>
+  <si>
+    <t>Coufal Jakub</t>
+  </si>
+  <si>
+    <t>12 min 37 s</t>
+  </si>
+  <si>
+    <t>18.05.2026</t>
+  </si>
+  <si>
+    <t>12 min 09 s</t>
+  </si>
+  <si>
+    <t>19.05.2026</t>
+  </si>
+  <si>
+    <t>13 min 16 s</t>
+  </si>
+  <si>
     <t>01.04.2026</t>
   </si>
   <si>
@@ -399,9 +462,6 @@
     <t>10.04.2026</t>
   </si>
   <si>
-    <t>Ahurieva Viktoriia</t>
-  </si>
-  <si>
     <t>10 min 12 s</t>
   </si>
   <si>
@@ -471,9 +531,6 @@
     <t>17.04.2026</t>
   </si>
   <si>
-    <t>Putna Jaroslav</t>
-  </si>
-  <si>
     <t>9 min 34 s</t>
   </si>
   <si>
@@ -624,9 +681,6 @@
     <t>11.03.2026</t>
   </si>
   <si>
-    <t>20:00</t>
-  </si>
-  <si>
     <t>Novák Dalibor</t>
   </si>
   <si>
@@ -778,9 +832,6 @@
   </si>
   <si>
     <t>31.03.2026</t>
-  </si>
-  <si>
-    <t>Hanibal Filip</t>
   </si>
   <si>
     <t>13 min 15 s</t>
@@ -3269,6 +3320,1174 @@
         <v>0.3333333333333333</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="M44" s="3">
+        <v>17.0</v>
+      </c>
+      <c r="N44" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O44" s="3">
+        <v>765.0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="P45" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Q45" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="R45" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="S45" s="3">
+        <v>6981.0</v>
+      </c>
+      <c r="T45" s="3">
+        <v>5502.0</v>
+      </c>
+      <c r="U45" s="3">
+        <v>5308.0</v>
+      </c>
+      <c r="V45" s="3">
+        <v>8181.6</v>
+      </c>
+      <c r="W45" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X45" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Y45" s="3">
+        <v>2410.0</v>
+      </c>
+      <c r="AA45" s="3">
+        <v>1044.0</v>
+      </c>
+      <c r="AB45" s="3">
+        <v>30191.6</v>
+      </c>
+      <c r="AC45" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AD45" s="3">
+        <v>0.34344570918892625</v>
+      </c>
+      <c r="AI45" s="3">
+        <v>765.0</v>
+      </c>
+      <c r="AJ45" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK45" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL45" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="AM45" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AN45" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AO45" s="3">
+        <v>69.0</v>
+      </c>
+      <c r="AP45" s="3">
+        <v>17.0</v>
+      </c>
+      <c r="AQ45" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AR45" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS45" s="3">
+        <v>0.29411764705882354</v>
+      </c>
+      <c r="AT45" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU45" s="3">
+        <v>0.7058823529411764</v>
+      </c>
+      <c r="AV45" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="M48" s="3">
+        <v>14.0</v>
+      </c>
+      <c r="N48" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O48" s="3">
+        <v>630.0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="P49" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="Q49" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="R49" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="S49" s="3">
+        <v>7890.0</v>
+      </c>
+      <c r="T49" s="3">
+        <v>8642.0</v>
+      </c>
+      <c r="U49" s="3">
+        <v>5504.0</v>
+      </c>
+      <c r="V49" s="3">
+        <v>4911.0</v>
+      </c>
+      <c r="W49" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X49" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Y49" s="3">
+        <v>1513.0</v>
+      </c>
+      <c r="AA49" s="3">
+        <v>4075.0</v>
+      </c>
+      <c r="AB49" s="3">
+        <v>33165.0</v>
+      </c>
+      <c r="AC49" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AD49" s="3">
+        <v>0.38426959847876935</v>
+      </c>
+      <c r="AI49" s="3">
+        <v>630.0</v>
+      </c>
+      <c r="AJ49" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK49" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL49" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AM49" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="AN49" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AO49" s="3">
+        <v>86.0</v>
+      </c>
+      <c r="AP49" s="3">
+        <v>16.0</v>
+      </c>
+      <c r="AQ49" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AR49" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS49" s="3">
+        <v>0.0625</v>
+      </c>
+      <c r="AT49" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU49" s="3">
+        <v>0.9375</v>
+      </c>
+      <c r="AV49" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="M51" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="N51" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O51" s="3">
+        <v>450.0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="P52" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Q52" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="R52" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="S52" s="3">
+        <v>9727.0</v>
+      </c>
+      <c r="T52" s="3">
+        <v>6907.0</v>
+      </c>
+      <c r="U52" s="3">
+        <v>5387.0</v>
+      </c>
+      <c r="V52" s="3">
+        <v>3912.0</v>
+      </c>
+      <c r="W52" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X52" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Y52" s="3">
+        <v>2447.0</v>
+      </c>
+      <c r="AA52" s="3">
+        <v>1158.0</v>
+      </c>
+      <c r="AB52" s="3">
+        <v>29988.0</v>
+      </c>
+      <c r="AC52" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AD52" s="3">
+        <v>0.5762020312641186</v>
+      </c>
+      <c r="AI52" s="3">
+        <v>450.0</v>
+      </c>
+      <c r="AJ52" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK52" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL52" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AM52" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="AN52" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AO52" s="3">
+        <v>68.0</v>
+      </c>
+      <c r="AP52" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="AQ52" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AR52" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS52" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="AT52" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU52" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="AV52" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="M56" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N56" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O56" s="3">
+        <v>180.0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P57" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="Q57" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="R57" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="S57" s="3">
+        <v>21791.6</v>
+      </c>
+      <c r="T57" s="3">
+        <v>5998.0</v>
+      </c>
+      <c r="U57" s="3">
+        <v>6797.0</v>
+      </c>
+      <c r="V57" s="3">
+        <v>2909.0</v>
+      </c>
+      <c r="W57" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X57" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Y57" s="3">
+        <v>3343.0</v>
+      </c>
+      <c r="AA57" s="3">
+        <v>982.0</v>
+      </c>
+      <c r="AB57" s="3">
+        <v>42000.1</v>
+      </c>
+      <c r="AC57" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="AD57" s="3">
+        <v>0.3245846241687136</v>
+      </c>
+      <c r="AI57" s="3">
+        <v>180.0</v>
+      </c>
+      <c r="AJ57" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AK57" s="3">
+        <v>3808.0</v>
+      </c>
+      <c r="AL57" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AM57" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="AN57" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AO57" s="3">
+        <v>101.0</v>
+      </c>
+      <c r="AP57" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="AQ57" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AR57" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS57" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AT57" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU57" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AV57" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="L59" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="M59" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="P60" s="3">
+        <v>16.0</v>
+      </c>
+      <c r="Q60" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="R60" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="S60" s="3">
+        <v>15249.399999999998</v>
+      </c>
+      <c r="T60" s="3">
+        <v>9174.0</v>
+      </c>
+      <c r="U60" s="3">
+        <v>11729.0</v>
+      </c>
+      <c r="V60" s="3">
+        <v>8644.0</v>
+      </c>
+      <c r="W60" s="3">
+        <v>2261.0</v>
+      </c>
+      <c r="X60" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Y60" s="3">
+        <v>4411.0</v>
+      </c>
+      <c r="AA60" s="3">
+        <v>1552.0</v>
+      </c>
+      <c r="AB60" s="3">
+        <v>53020.40000000001</v>
+      </c>
+      <c r="AC60" s="3">
+        <v>-1.4551915228366852E-11</v>
+      </c>
+      <c r="AD60" s="3">
+        <v>0.19062155610950476</v>
+      </c>
+      <c r="AI60" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ60" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK60" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL60" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="AM60" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AN60" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO60" s="3">
+        <v>120.0</v>
+      </c>
+      <c r="AP60" s="3">
+        <v>19.0</v>
+      </c>
+      <c r="AQ60" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="AR60" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="AS60" s="3">
+        <v>0.3684210526315789</v>
+      </c>
+      <c r="AT60" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="AU60" s="3">
+        <v>0.631578947368421</v>
+      </c>
+      <c r="AV60" s="3">
+        <v>0.3684210526315789</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C63" s="1"/>
+      <c r="D63" s="1"/>
+      <c r="E63" s="1"/>
+      <c r="G63" s="1"/>
+      <c r="P63" s="3">
+        <v>11.0</v>
+      </c>
+      <c r="R63" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="S63" s="3">
+        <v>9700.4</v>
+      </c>
+      <c r="T63" s="3">
+        <v>3958.0</v>
+      </c>
+      <c r="U63" s="3">
+        <v>6080.0</v>
+      </c>
+      <c r="V63" s="3">
+        <v>6568.3</v>
+      </c>
+      <c r="W63" s="3">
+        <v>238.0</v>
+      </c>
+      <c r="X63" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Y63" s="3">
+        <v>1769.0</v>
+      </c>
+      <c r="AA63" s="3">
+        <v>1917.0</v>
+      </c>
+      <c r="AB63" s="3">
+        <v>30230.699999999997</v>
+      </c>
+      <c r="AC63" s="3">
+        <v>3.637978807091713E-12</v>
+      </c>
+      <c r="AD63" s="3">
+        <v>0.3015279313263798</v>
+      </c>
+      <c r="AI63" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ63" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK63" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL63" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AM63" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="AN63" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO63" s="3">
+        <v>74.0</v>
+      </c>
+      <c r="AP63" s="3">
+        <v>11.0</v>
+      </c>
+      <c r="AQ63" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="AR63" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AS63" s="3">
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="AT63" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU63" s="3">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="AV63" s="3">
+        <v>0.18181818181818182</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="P65" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="Q65" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="R65" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="S65" s="3">
+        <v>10020.1</v>
+      </c>
+      <c r="T65" s="3">
+        <v>4598.0</v>
+      </c>
+      <c r="U65" s="3">
+        <v>4438.0</v>
+      </c>
+      <c r="V65" s="3">
+        <v>4817.4</v>
+      </c>
+      <c r="W65" s="3">
+        <v>1145.0</v>
+      </c>
+      <c r="X65" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Y65" s="3">
+        <v>2751.0</v>
+      </c>
+      <c r="AA65" s="3">
+        <v>370.0</v>
+      </c>
+      <c r="AB65" s="3">
+        <v>28137.5</v>
+      </c>
+      <c r="AC65" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AD65" s="3">
+        <v>0.2441334657858156</v>
+      </c>
+      <c r="AI65" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ65" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AK65" s="3">
+        <v>119.0</v>
+      </c>
+      <c r="AL65" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AM65" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="AN65" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO65" s="3">
+        <v>69.0</v>
+      </c>
+      <c r="AP65" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="AQ65" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AR65" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS65" s="3">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="AT65" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU65" s="3">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="AV65" s="3">
+        <v>0.2222222222222222</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L68" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="M68" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="N68" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O68" s="3">
+        <v>315.0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="P69" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="Q69" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="R69" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="S69" s="3">
+        <v>9321.099999999999</v>
+      </c>
+      <c r="T69" s="3">
+        <v>5286.0</v>
+      </c>
+      <c r="U69" s="3">
+        <v>1529.0</v>
+      </c>
+      <c r="V69" s="3">
+        <v>2549.0</v>
+      </c>
+      <c r="W69" s="3">
+        <v>269.0</v>
+      </c>
+      <c r="X69" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Y69" s="3">
+        <v>1707.0</v>
+      </c>
+      <c r="AA69" s="3">
+        <v>1585.0</v>
+      </c>
+      <c r="AB69" s="3">
+        <v>23561.1</v>
+      </c>
+      <c r="AC69" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AD69" s="3">
+        <v>0.5746314317051575</v>
+      </c>
+      <c r="AE69" s="3">
+        <v>1000.0</v>
+      </c>
+      <c r="AI69" s="3">
+        <v>315.0</v>
+      </c>
+      <c r="AJ69" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK69" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL69" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AM69" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="AN69" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AO69" s="3">
+        <v>63.0</v>
+      </c>
+      <c r="AP69" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="AQ69" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AR69" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS69" s="3">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="AT69" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AU69" s="3">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="AV69" s="3">
+        <v>0.1111111111111111</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -3429,7 +4648,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>86</v>
@@ -3449,7 +4668,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>86</v>
@@ -3469,7 +4688,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>86</v>
@@ -3498,7 +4717,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>86</v>
@@ -3564,7 +4783,7 @@
         <v>1.0</v>
       </c>
       <c r="AM5" s="1" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="AN5" s="3">
         <v>1.0</v>
@@ -3596,7 +4815,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>90</v>
@@ -3616,7 +4835,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>90</v>
@@ -3645,7 +4864,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>90</v>
@@ -3708,7 +4927,7 @@
         <v>0.0</v>
       </c>
       <c r="AM8" s="1" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="AN8" s="3">
         <v>1.0</v>
@@ -3740,7 +4959,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>49</v>
@@ -3760,7 +4979,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>49</v>
@@ -3770,10 +4989,10 @@
       <c r="E10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>64</v>
@@ -3787,7 +5006,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>49</v>
@@ -3854,7 +5073,7 @@
         <v>3.0</v>
       </c>
       <c r="AM11" s="1" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="AN11" s="3">
         <v>0.0</v>
@@ -3886,7 +5105,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>62</v>
@@ -3906,13 +5125,13 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>53</v>
@@ -3935,7 +5154,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>62</v>
@@ -3998,7 +5217,7 @@
         <v>2.0</v>
       </c>
       <c r="AM14" s="1" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="AN14" s="3">
         <v>1.0</v>
@@ -4030,7 +5249,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>69</v>
@@ -4050,13 +5269,13 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>53</v>
@@ -4065,7 +5284,7 @@
         <v>71</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="M16" s="3">
         <v>8.0</v>
@@ -4079,7 +5298,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>69</v>
@@ -4139,7 +5358,7 @@
         <v>0.0</v>
       </c>
       <c r="AM17" s="1" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="AN17" s="3">
         <v>1.0</v>
@@ -4171,7 +5390,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>76</v>
@@ -4191,7 +5410,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>76</v>
@@ -4211,7 +5430,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>76</v>
@@ -4240,7 +5459,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>76</v>
@@ -4303,7 +5522,7 @@
         <v>3.0</v>
       </c>
       <c r="AM21" s="1" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="AN21" s="3">
         <v>1.0</v>
@@ -4335,7 +5554,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>82</v>
@@ -4355,7 +5574,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>82</v>
@@ -4375,7 +5594,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>82</v>
@@ -4404,7 +5623,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>82</v>
@@ -4467,7 +5686,7 @@
         <v>0.0</v>
       </c>
       <c r="AM25" s="1" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="AN25" s="3">
         <v>1.0</v>
@@ -4499,7 +5718,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>86</v>
@@ -4519,7 +5738,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>86</v>
@@ -4539,7 +5758,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>86</v>
@@ -4568,7 +5787,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>86</v>
@@ -4628,7 +5847,7 @@
         <v>1.0</v>
       </c>
       <c r="AM29" s="1" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="AN29" s="3">
         <v>1.0</v>
@@ -4660,7 +5879,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>90</v>
@@ -4680,7 +5899,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>90</v>
@@ -4700,7 +5919,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>90</v>
@@ -4729,7 +5948,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>90</v>
@@ -4789,7 +6008,7 @@
         <v>2.0</v>
       </c>
       <c r="AM33" s="1" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="AN33" s="3">
         <v>1.0</v>
@@ -4821,7 +6040,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>49</v>
@@ -4841,13 +6060,13 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>77</v>
@@ -4861,7 +6080,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>49</v>
@@ -4890,7 +6109,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>49</v>
@@ -4953,7 +6172,7 @@
         <v>0.0</v>
       </c>
       <c r="AM37" s="1" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="AN37" s="3">
         <v>1.0</v>
@@ -4985,7 +6204,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>62</v>
@@ -4997,7 +6216,7 @@
         <v>51</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>102</v>
@@ -5005,39 +6224,39 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>55</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>77</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>66</v>
@@ -5045,7 +6264,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>62</v>
@@ -5061,7 +6280,7 @@
         <v>50</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="S41" s="3">
         <v>17084.0</v>
@@ -5109,7 +6328,7 @@
         <v>2.0</v>
       </c>
       <c r="AM41" s="1" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="AN41" s="3">
         <v>0.0</v>
@@ -5141,13 +6360,13 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>51</v>
@@ -5161,7 +6380,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>69</v>
@@ -5181,13 +6400,13 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>55</v>
@@ -5201,7 +6420,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>69</v>
@@ -5211,7 +6430,7 @@
       <c r="E45" s="1"/>
       <c r="G45" s="1"/>
       <c r="H45" s="1" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>55</v>
@@ -5228,7 +6447,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>69</v>
@@ -5241,7 +6460,7 @@
         <v>2.0</v>
       </c>
       <c r="Q46" s="1" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="R46" s="1" t="s">
         <v>54</v>
@@ -5298,7 +6517,7 @@
         <v>1.0</v>
       </c>
       <c r="AM46" s="1" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="AN46" s="3">
         <v>0.0</v>
@@ -5330,7 +6549,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>76</v>
@@ -5350,7 +6569,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>76</v>
@@ -5370,7 +6589,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>76</v>
@@ -5399,7 +6618,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>76</v>
@@ -5459,7 +6678,7 @@
         <v>0.0</v>
       </c>
       <c r="AM50" s="1" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="AN50" s="3">
         <v>1.0</v>
@@ -5491,7 +6710,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>82</v>
@@ -5511,7 +6730,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>82</v>
@@ -5531,7 +6750,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>82</v>
@@ -5560,7 +6779,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>82</v>
@@ -5629,7 +6848,7 @@
         <v>1.0</v>
       </c>
       <c r="AM54" s="1" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="AN54" s="3">
         <v>1.0</v>
@@ -5661,7 +6880,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>86</v>
@@ -5673,15 +6892,15 @@
         <v>51</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>86</v>
@@ -5701,7 +6920,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>86</v>
@@ -5713,7 +6932,7 @@
         <v>51</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="L57" s="2" t="s">
         <v>102</v>
@@ -5730,22 +6949,22 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>86</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>58</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="M58" s="3">
         <v>3.0</v>
@@ -5759,7 +6978,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>86</v>
@@ -5819,7 +7038,7 @@
         <v>0.0</v>
       </c>
       <c r="AM59" s="1" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="AN59" s="3">
         <v>2.0</v>
@@ -5851,7 +7070,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>90</v>
@@ -5871,7 +7090,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>90</v>
@@ -5900,7 +7119,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>90</v>
@@ -5960,7 +7179,7 @@
         <v>1.0</v>
       </c>
       <c r="AM62" s="1" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="AN62" s="3">
         <v>1.0</v>
@@ -5992,7 +7211,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>49</v>
@@ -6012,13 +7231,13 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>55</v>
@@ -6032,7 +7251,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>49</v>
@@ -6042,7 +7261,7 @@
       <c r="E65" s="1"/>
       <c r="G65" s="1"/>
       <c r="H65" s="1" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>53</v>
@@ -6065,7 +7284,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>49</v>
@@ -6132,7 +7351,7 @@
         <v>0.0</v>
       </c>
       <c r="AM66" s="1" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="AN66" s="3">
         <v>1.0</v>
@@ -6164,7 +7383,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>62</v>
@@ -6184,7 +7403,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>62</v>
@@ -6204,7 +7423,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>62</v>
@@ -6216,15 +7435,15 @@
         <v>55</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>62</v>
@@ -6253,7 +7472,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>62</v>
@@ -6313,7 +7532,7 @@
         <v>2.0</v>
       </c>
       <c r="AM71" s="1" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="AN71" s="3">
         <v>1.0</v>
@@ -6345,7 +7564,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>69</v>
@@ -6365,13 +7584,13 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>55</v>
@@ -6385,7 +7604,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>69</v>
@@ -6448,7 +7667,7 @@
         <v>2.0</v>
       </c>
       <c r="AM74" s="1" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="AN74" s="3">
         <v>0.0</v>
@@ -6480,7 +7699,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>76</v>
@@ -6492,15 +7711,15 @@
         <v>51</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>76</v>
@@ -6520,7 +7739,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>76</v>
@@ -6549,7 +7768,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>76</v>
@@ -6612,7 +7831,7 @@
         <v>0.0</v>
       </c>
       <c r="AM78" s="1" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="AN78" s="3">
         <v>1.0</v>
@@ -6644,7 +7863,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>82</v>
@@ -6664,7 +7883,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>82</v>
@@ -6693,7 +7912,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>82</v>
@@ -6756,7 +7975,7 @@
         <v>1.0</v>
       </c>
       <c r="AM81" s="1" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="AN81" s="3">
         <v>1.0</v>
@@ -6788,7 +8007,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>86</v>
@@ -6808,7 +8027,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>86</v>
@@ -6828,7 +8047,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>86</v>
@@ -6857,7 +8076,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>86</v>
@@ -6917,7 +8136,7 @@
         <v>1.0</v>
       </c>
       <c r="AM85" s="1" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="AN85" s="3">
         <v>1.0</v>
@@ -6949,7 +8168,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>90</v>
@@ -6969,7 +8188,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>90</v>
@@ -6998,7 +8217,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>90</v>
@@ -7058,7 +8277,7 @@
         <v>1.0</v>
       </c>
       <c r="AM88" s="1" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="AN88" s="3">
         <v>1.0</v>
@@ -7090,7 +8309,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>49</v>
@@ -7110,13 +8329,13 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="I90" s="2" t="s">
         <v>53</v>
@@ -7139,7 +8358,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>49</v>
@@ -7199,7 +8418,7 @@
         <v>2.0</v>
       </c>
       <c r="AM91" s="1" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="AN91" s="3">
         <v>1.0</v>
@@ -7231,7 +8450,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>62</v>
@@ -7251,7 +8470,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>62</v>
@@ -7280,13 +8499,13 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="I94" s="2" t="s">
         <v>55</v>
@@ -7309,7 +8528,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>62</v>
@@ -7369,7 +8588,7 @@
         <v>0.0</v>
       </c>
       <c r="AM95" s="1" t="s">
-        <v>168</v>
+        <v>187</v>
       </c>
       <c r="AN95" s="3">
         <v>2.0</v>
@@ -7401,7 +8620,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>69</v>
@@ -7421,7 +8640,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>69</v>
@@ -7481,7 +8700,7 @@
         <v>0.0</v>
       </c>
       <c r="AM97" s="1" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="AN97" s="3">
         <v>0.0</v>
@@ -7513,7 +8732,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>76</v>
@@ -7533,7 +8752,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>76</v>
@@ -7556,7 +8775,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>76</v>
@@ -7616,7 +8835,7 @@
         <v>0.0</v>
       </c>
       <c r="AM100" s="1" t="s">
-        <v>171</v>
+        <v>190</v>
       </c>
       <c r="AN100" s="3">
         <v>0.0</v>
@@ -7648,7 +8867,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>82</v>
@@ -7668,7 +8887,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>82</v>
@@ -7688,7 +8907,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>82</v>
@@ -7780,7 +8999,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>86</v>
@@ -7800,7 +9019,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>86</v>
@@ -7809,13 +9028,13 @@
         <v>57</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="J105" s="2" t="s">
         <v>58</v>
       </c>
       <c r="L105" s="2" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="M105" s="3">
         <v>8.0</v>
@@ -7823,7 +9042,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>86</v>
@@ -7889,7 +9108,7 @@
         <v>2.0</v>
       </c>
       <c r="AM106" s="1" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="AN106" s="3">
         <v>0.0</v>
@@ -7921,7 +9140,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>90</v>
@@ -7941,7 +9160,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>90</v>
@@ -7956,7 +9175,7 @@
         <v>101</v>
       </c>
       <c r="L108" s="2" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="M108" s="3">
         <v>9.0</v>
@@ -7964,7 +9183,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>90</v>
@@ -8024,7 +9243,7 @@
         <v>2.0</v>
       </c>
       <c r="AM109" s="1" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="AN109" s="3">
         <v>0.0</v>
@@ -8214,7 +9433,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>69</v>
@@ -8226,7 +9445,7 @@
         <v>51</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>64</v>
@@ -8234,7 +9453,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>69</v>
@@ -8243,7 +9462,7 @@
         <v>63</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>71</v>
@@ -8254,13 +9473,13 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>53</v>
@@ -8269,7 +9488,7 @@
         <v>71</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="M4" s="3">
         <v>15.0</v>
@@ -8283,7 +9502,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>69</v>
@@ -8346,7 +9565,7 @@
         <v>5.0</v>
       </c>
       <c r="AM5" s="1" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="AN5" s="3">
         <v>1.0</v>
@@ -8378,7 +9597,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>76</v>
@@ -8398,7 +9617,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>76</v>
@@ -8418,7 +9637,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>76</v>
@@ -8438,7 +9657,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>76</v>
@@ -8467,7 +9686,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>76</v>
@@ -8527,7 +9746,7 @@
         <v>0.0</v>
       </c>
       <c r="AM10" s="1" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="AN10" s="3">
         <v>1.0</v>
@@ -8559,7 +9778,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>82</v>
@@ -8579,13 +9798,13 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>82</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>53</v>
@@ -8594,7 +9813,7 @@
         <v>71</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="M12" s="3">
         <v>8.0</v>
@@ -8608,7 +9827,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>82</v>
@@ -8671,7 +9890,7 @@
         <v>3.0</v>
       </c>
       <c r="AM13" s="1" t="s">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c r="AN13" s="3">
         <v>1.0</v>
@@ -8703,7 +9922,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>86</v>
@@ -8723,7 +9942,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>86</v>
@@ -8732,10 +9951,10 @@
         <v>50</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>70</v>
@@ -8743,7 +9962,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>86</v>
@@ -8763,7 +9982,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>86</v>
@@ -8786,7 +10005,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>86</v>
@@ -8849,7 +10068,7 @@
         <v>0.0</v>
       </c>
       <c r="AM18" s="1" t="s">
-        <v>187</v>
+        <v>206</v>
       </c>
       <c r="AN18" s="3">
         <v>0.0</v>
@@ -8881,7 +10100,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>90</v>
@@ -8901,7 +10120,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>90</v>
@@ -8921,7 +10140,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>90</v>
@@ -8944,7 +10163,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>90</v>
@@ -9010,7 +10229,7 @@
         <v>2.0</v>
       </c>
       <c r="AM22" s="1" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="AN22" s="3">
         <v>0.0</v>
@@ -9042,7 +10261,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>49</v>
@@ -9062,7 +10281,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>49</v>
@@ -9072,7 +10291,7 @@
       <c r="E24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>51</v>
@@ -9095,7 +10314,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>49</v>
@@ -9159,7 +10378,7 @@
         <v>3.0</v>
       </c>
       <c r="AM25" s="1" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="AN25" s="3">
         <v>1.0</v>
@@ -9191,7 +10410,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>62</v>
@@ -9206,12 +10425,12 @@
         <v>65</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>62</v>
@@ -9226,12 +10445,12 @@
         <v>64</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>62</v>
@@ -9241,7 +10460,7 @@
       <c r="E28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1" t="s">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>53</v>
@@ -9264,7 +10483,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>62</v>
@@ -9328,7 +10547,7 @@
         <v>7.0</v>
       </c>
       <c r="AM29" s="1" t="s">
-        <v>193</v>
+        <v>212</v>
       </c>
       <c r="AN29" s="3">
         <v>1.0</v>
@@ -9360,7 +10579,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>69</v>
@@ -9380,7 +10599,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>69</v>
@@ -9390,7 +10609,7 @@
       <c r="E31" s="1"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>53</v>
@@ -9399,7 +10618,7 @@
         <v>71</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="M31" s="3">
         <v>12.0</v>
@@ -9413,7 +10632,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>69</v>
@@ -9429,7 +10648,7 @@
         <v>50</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="S32" s="3">
         <v>12040.0</v>
@@ -9480,7 +10699,7 @@
         <v>9.0</v>
       </c>
       <c r="AM32" s="1" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="AN32" s="3">
         <v>1.0</v>
@@ -9512,7 +10731,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>76</v>
@@ -9532,7 +10751,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>76</v>
@@ -9561,7 +10780,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>76</v>
@@ -9621,7 +10840,7 @@
         <v>0.0</v>
       </c>
       <c r="AM35" s="1" t="s">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="AN35" s="3">
         <v>1.0</v>
@@ -9653,7 +10872,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>82</v>
@@ -9673,7 +10892,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>82</v>
@@ -9702,7 +10921,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>82</v>
@@ -9762,7 +10981,7 @@
         <v>0.0</v>
       </c>
       <c r="AM38" s="1" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="AN38" s="3">
         <v>1.0</v>
@@ -9794,7 +11013,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>86</v>
@@ -9814,7 +11033,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>86</v>
@@ -9834,19 +11053,19 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>86</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>78</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>202</v>
+        <v>112</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>56</v>
@@ -9854,13 +11073,13 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>86</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>51</v>
@@ -9874,7 +11093,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>86</v>
@@ -9903,7 +11122,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>86</v>
@@ -9963,7 +11182,7 @@
         <v>1.0</v>
       </c>
       <c r="AM44" s="1" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="AN44" s="3">
         <v>1.0</v>
@@ -9995,7 +11214,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>90</v>
@@ -10015,7 +11234,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>90</v>
@@ -10035,13 +11254,13 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>90</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>55</v>
@@ -10055,7 +11274,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>90</v>
@@ -10065,7 +11284,7 @@
       <c r="E48" s="1"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1" t="s">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>53</v>
@@ -10079,7 +11298,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>90</v>
@@ -10112,7 +11331,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>90</v>
@@ -10179,7 +11398,7 @@
         <v>1.0</v>
       </c>
       <c r="AM50" s="1" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="AN50" s="3">
         <v>1.0</v>
@@ -10211,7 +11430,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>49</v>
@@ -10223,15 +11442,15 @@
         <v>51</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>49</v>
@@ -10251,13 +11470,13 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>53</v>
@@ -10274,7 +11493,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>49</v>
@@ -10337,7 +11556,7 @@
         <v>3.0</v>
       </c>
       <c r="AM54" s="1" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="AN54" s="3">
         <v>0.0</v>
@@ -10369,7 +11588,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>62</v>
@@ -10389,7 +11608,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>62</v>
@@ -10401,30 +11620,30 @@
         <v>55</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>53</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="M57" s="3">
         <v>13.0</v>
@@ -10432,7 +11651,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>62</v>
@@ -10495,7 +11714,7 @@
         <v>5.0</v>
       </c>
       <c r="AM58" s="1" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="AN58" s="3">
         <v>0.0</v>
@@ -10527,7 +11746,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>69</v>
@@ -10547,13 +11766,13 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>53</v>
@@ -10562,7 +11781,7 @@
         <v>71</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="M60" s="3">
         <v>9.0</v>
@@ -10570,7 +11789,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>69</v>
@@ -10630,7 +11849,7 @@
         <v>6.0</v>
       </c>
       <c r="AM61" s="1" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="AN61" s="3">
         <v>0.0</v>
@@ -10662,7 +11881,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>76</v>
@@ -10682,7 +11901,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>76</v>
@@ -10702,7 +11921,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>76</v>
@@ -10714,10 +11933,10 @@
         <v>53</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="M64" s="3">
         <v>6.0</v>
@@ -10731,7 +11950,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>76</v>
@@ -10791,7 +12010,7 @@
         <v>2.0</v>
       </c>
       <c r="AM65" s="1" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="AN65" s="3">
         <v>1.0</v>
@@ -10823,7 +12042,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>82</v>
@@ -10843,7 +12062,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>82</v>
@@ -10872,7 +12091,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>82</v>
@@ -10932,7 +12151,7 @@
         <v>0.0</v>
       </c>
       <c r="AM68" s="1" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="AN68" s="3">
         <v>1.0</v>
@@ -10964,7 +12183,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>86</v>
@@ -10984,7 +12203,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>86</v>
@@ -11013,7 +12232,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>86</v>
@@ -11073,7 +12292,7 @@
         <v>0.0</v>
       </c>
       <c r="AM71" s="1" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="AN71" s="3">
         <v>1.0</v>
@@ -11105,7 +12324,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>90</v>
@@ -11125,7 +12344,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>90</v>
@@ -11145,13 +12364,13 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>90</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>77</v>
@@ -11165,7 +12384,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>90</v>
@@ -11194,7 +12413,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>90</v>
@@ -11257,7 +12476,7 @@
         <v>0.0</v>
       </c>
       <c r="AM76" s="1" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="AN76" s="3">
         <v>1.0</v>
@@ -11289,7 +12508,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>49</v>
@@ -11309,13 +12528,13 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>55</v>
@@ -11329,7 +12548,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>49</v>
@@ -11389,7 +12608,7 @@
         <v>4.0</v>
       </c>
       <c r="AM79" s="1" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="AN79" s="3">
         <v>0.0</v>
@@ -11421,7 +12640,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>62</v>
@@ -11433,15 +12652,15 @@
         <v>51</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>62</v>
@@ -11461,7 +12680,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>62</v>
@@ -11473,15 +12692,15 @@
         <v>78</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>62</v>
@@ -11541,7 +12760,7 @@
         <v>5.0</v>
       </c>
       <c r="AM83" s="1" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="AN83" s="3">
         <v>0.0</v>
@@ -11573,7 +12792,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>69</v>
@@ -11593,7 +12812,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>69</v>
@@ -11653,7 +12872,7 @@
         <v>2.0</v>
       </c>
       <c r="AM85" s="1" t="s">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="AN85" s="3">
         <v>0.0</v>
@@ -11685,7 +12904,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>76</v>
@@ -11705,7 +12924,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>76</v>
@@ -11717,7 +12936,7 @@
         <v>51</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>64</v>
@@ -11725,7 +12944,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>76</v>
@@ -11754,7 +12973,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>76</v>
@@ -11814,7 +13033,7 @@
         <v>0.0</v>
       </c>
       <c r="AM89" s="1" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="AN89" s="3">
         <v>1.0</v>
@@ -11846,7 +13065,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>82</v>
@@ -11858,15 +13077,15 @@
         <v>51</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>82</v>
@@ -11886,7 +13105,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>82</v>
@@ -11915,7 +13134,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>82</v>
@@ -11978,7 +13197,7 @@
         <v>0.0</v>
       </c>
       <c r="AM93" s="1" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="AN93" s="3">
         <v>1.0</v>
@@ -12010,7 +13229,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>86</v>
@@ -12022,15 +13241,15 @@
         <v>51</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>86</v>
@@ -12050,7 +13269,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>86</v>
@@ -12079,7 +13298,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>86</v>
@@ -12142,7 +13361,7 @@
         <v>1.0</v>
       </c>
       <c r="AM97" s="1" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="AN97" s="3">
         <v>1.0</v>
@@ -12174,7 +13393,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>90</v>
@@ -12194,7 +13413,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>90</v>
@@ -12223,7 +13442,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>90</v>
@@ -12286,7 +13505,7 @@
         <v>2.0</v>
       </c>
       <c r="AM100" s="1" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="AN100" s="3">
         <v>1.0</v>
@@ -12318,7 +13537,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>49</v>
@@ -12338,16 +13557,16 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>65</v>
@@ -12358,7 +13577,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>49</v>
@@ -12418,7 +13637,7 @@
         <v>4.0</v>
       </c>
       <c r="AM103" s="1" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="AN103" s="3">
         <v>0.0</v>
@@ -12450,7 +13669,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>62</v>
@@ -12462,15 +13681,15 @@
         <v>51</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>62</v>
@@ -12490,36 +13709,36 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>77</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="J107" s="2" t="s">
         <v>64</v>
@@ -12539,13 +13758,13 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="I108" s="2" t="s">
         <v>53</v>
@@ -12562,7 +13781,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>62</v>
@@ -12625,7 +13844,7 @@
         <v>1.0</v>
       </c>
       <c r="AM109" s="1" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="AN109" s="3">
         <v>1.0</v>
@@ -12657,7 +13876,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>69</v>
@@ -12677,13 +13896,13 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>55</v>
@@ -12697,7 +13916,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>69</v>
@@ -12717,7 +13936,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>69</v>
@@ -12781,7 +14000,7 @@
         <v>3.0</v>
       </c>
       <c r="AM113" s="1" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="AN113" s="3">
         <v>0.0</v>
@@ -12813,7 +14032,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>76</v>
@@ -12833,7 +14052,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>76</v>
@@ -12853,7 +14072,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>76</v>
@@ -12873,7 +14092,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>76</v>
@@ -12902,7 +14121,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>76</v>
@@ -12965,7 +14184,7 @@
         <v>0.0</v>
       </c>
       <c r="AM118" s="1" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="AN118" s="3">
         <v>1.0</v>
@@ -12997,7 +14216,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>82</v>
@@ -13017,7 +14236,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>82</v>
@@ -13037,13 +14256,13 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>82</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>254</v>
+        <v>116</v>
       </c>
       <c r="I121" s="2" t="s">
         <v>51</v>
@@ -13060,7 +14279,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>82</v>
@@ -13089,7 +14308,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>82</v>
@@ -13155,7 +14374,7 @@
         <v>0.0</v>
       </c>
       <c r="AM123" s="1" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="AN123" s="3">
         <v>1.0</v>
@@ -13345,13 +14564,13 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>51</v>
@@ -13365,13 +14584,13 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>53</v>
@@ -13380,7 +14599,7 @@
         <v>71</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="M3" s="3">
         <v>10.0</v>
@@ -13394,7 +14613,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>69</v>
@@ -13448,7 +14667,7 @@
         <v>0.0</v>
       </c>
       <c r="AM4" s="1" t="s">
-        <v>259</v>
+        <v>276</v>
       </c>
       <c r="AN4" s="3">
         <v>1.0</v>
@@ -13480,7 +14699,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>260</v>
+        <v>277</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>76</v>
@@ -13500,7 +14719,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>260</v>
+        <v>277</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>76</v>
@@ -13529,7 +14748,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>260</v>
+        <v>277</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>76</v>
@@ -13589,7 +14808,7 @@
         <v>1.0</v>
       </c>
       <c r="AM7" s="1" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="AN7" s="3">
         <v>1.0</v>
@@ -13621,7 +14840,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>82</v>
@@ -13641,13 +14860,13 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>82</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>53</v>
@@ -13670,13 +14889,13 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>82</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>51</v>
@@ -13693,7 +14912,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>82</v>
@@ -13750,7 +14969,7 @@
         <v>0.0</v>
       </c>
       <c r="AM11" s="1" t="s">
-        <v>263</v>
+        <v>280</v>
       </c>
       <c r="AN11" s="3">
         <v>1.0</v>
@@ -13782,13 +15001,13 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>264</v>
+        <v>281</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>51</v>
@@ -13802,13 +15021,13 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>264</v>
+        <v>281</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>86</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>53</v>
@@ -13831,7 +15050,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>264</v>
+        <v>281</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>86</v>
@@ -13840,10 +15059,10 @@
         <v>0.0</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="S14" s="3">
         <v>15925.179999999997</v>
@@ -13891,7 +15110,7 @@
         <v>0.0</v>
       </c>
       <c r="AM14" s="1" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="AN14" s="3">
         <v>1.0</v>
@@ -13923,7 +15142,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>266</v>
+        <v>283</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>90</v>
@@ -13943,13 +15162,13 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>266</v>
+        <v>283</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>90</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>51</v>
@@ -13966,7 +15185,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>266</v>
+        <v>283</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>90</v>
@@ -13995,7 +15214,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>266</v>
+        <v>283</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>90</v>
@@ -14052,7 +15271,7 @@
         <v>0.0</v>
       </c>
       <c r="AM18" s="1" t="s">
-        <v>267</v>
+        <v>284</v>
       </c>
       <c r="AN18" s="3">
         <v>1.0</v>
@@ -14084,13 +15303,13 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>51</v>
@@ -14104,13 +15323,13 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>55</v>
@@ -14124,7 +15343,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>49</v>
@@ -14153,7 +15372,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>49</v>
@@ -14207,7 +15426,7 @@
         <v>0.0</v>
       </c>
       <c r="AM22" s="1" t="s">
-        <v>269</v>
+        <v>286</v>
       </c>
       <c r="AN22" s="3">
         <v>1.0</v>
@@ -14239,13 +15458,13 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>270</v>
+        <v>287</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>51</v>
@@ -14259,22 +15478,22 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>270</v>
+        <v>287</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>53</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="M24" s="3">
         <v>10.0</v>
@@ -14288,13 +15507,13 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>270</v>
+        <v>287</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>55</v>
@@ -14311,13 +15530,13 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>270</v>
+        <v>287</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>53</v>
@@ -14340,7 +15559,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>270</v>
+        <v>287</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>62</v>
@@ -14394,7 +15613,7 @@
         <v>1.0</v>
       </c>
       <c r="AM27" s="1" t="s">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="AN27" s="3">
         <v>2.0</v>
@@ -14426,13 +15645,13 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>51</v>
@@ -14446,13 +15665,13 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>93</v>
@@ -14475,13 +15694,13 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>53</v>
@@ -14504,13 +15723,13 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>93</v>
@@ -14533,7 +15752,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>69</v>
@@ -14542,10 +15761,10 @@
         <v>0.0</v>
       </c>
       <c r="Q32" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="S32" s="3">
         <v>9567.0</v>
@@ -14593,7 +15812,7 @@
         <v>0.0</v>
       </c>
       <c r="AM32" s="1" t="s">
-        <v>274</v>
+        <v>291</v>
       </c>
       <c r="AN32" s="3">
         <v>3.0</v>
@@ -14625,13 +15844,13 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>76</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>51</v>
@@ -14645,7 +15864,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>76</v>
@@ -14665,13 +15884,13 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>53</v>
@@ -14694,13 +15913,13 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>93</v>
@@ -14723,7 +15942,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>76</v>
@@ -14732,7 +15951,7 @@
         <v>1.0</v>
       </c>
       <c r="Q37" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="R37" s="1" t="s">
         <v>63</v>
@@ -14783,7 +16002,7 @@
         <v>0.0</v>
       </c>
       <c r="AM37" s="1" t="s">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="AN37" s="3">
         <v>2.0</v>
@@ -14815,13 +16034,13 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>82</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>51</v>
@@ -14835,13 +16054,13 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>82</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>53</v>
@@ -14864,13 +16083,13 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>82</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>55</v>
@@ -14893,7 +16112,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>82</v>
@@ -14902,10 +16121,10 @@
         <v>0.0</v>
       </c>
       <c r="Q41" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="S41" s="3">
         <v>6459.0</v>
@@ -14953,7 +16172,7 @@
         <v>0.0</v>
       </c>
       <c r="AM41" s="1" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="AN41" s="3">
         <v>2.0</v>
@@ -14985,7 +16204,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>86</v>
@@ -15005,7 +16224,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>86</v>
@@ -15034,7 +16253,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>86</v>
@@ -15094,7 +16313,7 @@
         <v>0.0</v>
       </c>
       <c r="AM44" s="1" t="s">
-        <v>279</v>
+        <v>296</v>
       </c>
       <c r="AN44" s="3">
         <v>1.0</v>
@@ -15126,7 +16345,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>90</v>
@@ -15146,13 +16365,13 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>90</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>51</v>
@@ -15169,7 +16388,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>90</v>
@@ -15198,7 +16417,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>90</v>
@@ -15290,13 +16509,13 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>51</v>
@@ -15310,13 +16529,13 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>55</v>
@@ -15330,7 +16549,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>49</v>
@@ -15359,7 +16578,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>49</v>
@@ -15368,10 +16587,10 @@
         <v>1.0</v>
       </c>
       <c r="Q52" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="R52" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="S52" s="3">
         <v>23294.0</v>
@@ -15416,7 +16635,7 @@
         <v>4.0</v>
       </c>
       <c r="AM52" s="1" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="AN52" s="3">
         <v>1.0</v>
@@ -15448,13 +16667,13 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>70</v>
@@ -15468,13 +16687,13 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>55</v>
@@ -15488,13 +16707,13 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>53</v>
@@ -15517,7 +16736,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>62</v>
@@ -15571,7 +16790,7 @@
         <v>0.0</v>
       </c>
       <c r="AM56" s="1" t="s">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="AN56" s="3">
         <v>1.0</v>
@@ -15603,7 +16822,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>285</v>
+        <v>302</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>69</v>
@@ -15623,7 +16842,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>285</v>
+        <v>302</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>69</v>
@@ -15643,7 +16862,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>285</v>
+        <v>302</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>69</v>
@@ -15706,7 +16925,7 @@
         <v>0.0</v>
       </c>
       <c r="AM59" s="1" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="AN59" s="3">
         <v>0.0</v>
@@ -15738,13 +16957,13 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>286</v>
+        <v>303</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>51</v>
@@ -15761,7 +16980,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>286</v>
+        <v>303</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>76</v>
@@ -15790,7 +17009,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>286</v>
+        <v>303</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>76</v>
@@ -15844,7 +17063,7 @@
         <v>1.0</v>
       </c>
       <c r="AM62" s="1" t="s">
-        <v>287</v>
+        <v>304</v>
       </c>
       <c r="AN62" s="3">
         <v>1.0</v>
@@ -15876,7 +17095,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>82</v>
@@ -15896,13 +17115,13 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>82</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>51</v>
@@ -15919,7 +17138,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>82</v>
@@ -15948,7 +17167,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>82</v>
@@ -16005,7 +17224,7 @@
         <v>1.0</v>
       </c>
       <c r="AM66" s="1" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="AN66" s="3">
         <v>1.0</v>
@@ -16037,7 +17256,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>290</v>
+        <v>307</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>86</v>
@@ -16057,7 +17276,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>290</v>
+        <v>307</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>86</v>
@@ -16086,7 +17305,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>290</v>
+        <v>307</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>86</v>
@@ -16146,7 +17365,7 @@
         <v>0.0</v>
       </c>
       <c r="AM69" s="1" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="AN69" s="3">
         <v>1.0</v>
@@ -16178,7 +17397,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>90</v>
@@ -16198,7 +17417,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>90</v>
@@ -16227,7 +17446,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>90</v>
@@ -16319,7 +17538,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>49</v>
@@ -16339,13 +17558,13 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>93</v>
@@ -16359,7 +17578,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>49</v>
@@ -16388,13 +17607,13 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>51</v>
@@ -16417,7 +17636,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>49</v>
@@ -16474,7 +17693,7 @@
         <v>0.0</v>
       </c>
       <c r="AM77" s="1" t="s">
-        <v>293</v>
+        <v>310</v>
       </c>
       <c r="AN77" s="3">
         <v>2.0</v>
@@ -16506,7 +17725,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>62</v>
@@ -16518,21 +17737,21 @@
         <v>55</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="I79" s="2" t="s">
         <v>51</v>
@@ -16549,7 +17768,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>62</v>
@@ -16606,7 +17825,7 @@
         <v>3.0</v>
       </c>
       <c r="AM80" s="1" t="s">
-        <v>295</v>
+        <v>312</v>
       </c>
       <c r="AN80" s="3">
         <v>0.0</v>
@@ -16638,7 +17857,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>296</v>
+        <v>313</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>69</v>
@@ -16658,13 +17877,13 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>296</v>
+        <v>313</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="I82" s="2" t="s">
         <v>53</v>
@@ -16681,7 +17900,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>296</v>
+        <v>313</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>69</v>
@@ -16741,7 +17960,7 @@
         <v>3.0</v>
       </c>
       <c r="AM83" s="1" t="s">
-        <v>297</v>
+        <v>314</v>
       </c>
       <c r="AN83" s="3">
         <v>0.0</v>
@@ -16773,7 +17992,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>298</v>
+        <v>315</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>76</v>
@@ -16793,7 +18012,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>298</v>
+        <v>315</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>76</v>
@@ -16816,13 +18035,13 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>298</v>
+        <v>315</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>299</v>
+        <v>316</v>
       </c>
       <c r="I86" s="2" t="s">
         <v>53</v>
@@ -16836,13 +18055,13 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>298</v>
+        <v>315</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>300</v>
+        <v>317</v>
       </c>
       <c r="I87" s="2" t="s">
         <v>77</v>
@@ -16856,7 +18075,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>298</v>
+        <v>315</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>76</v>
@@ -16916,7 +18135,7 @@
         <v>2.0</v>
       </c>
       <c r="AM88" s="1" t="s">
-        <v>301</v>
+        <v>318</v>
       </c>
       <c r="AN88" s="3">
         <v>0.0</v>
@@ -16948,7 +18167,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>302</v>
+        <v>319</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>82</v>
@@ -16968,7 +18187,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>302</v>
+        <v>319</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>82</v>
@@ -16991,7 +18210,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>302</v>
+        <v>319</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>82</v>
@@ -17054,7 +18273,7 @@
         <v>2.0</v>
       </c>
       <c r="AM91" s="1" t="s">
-        <v>303</v>
+        <v>320</v>
       </c>
       <c r="AN91" s="3">
         <v>0.0</v>
@@ -17086,7 +18305,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>304</v>
+        <v>321</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>86</v>
@@ -17106,7 +18325,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>304</v>
+        <v>321</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>86</v>
@@ -17129,7 +18348,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>304</v>
+        <v>321</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>86</v>
@@ -17189,7 +18408,7 @@
         <v>0.0</v>
       </c>
       <c r="AM94" s="1" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="AN94" s="3">
         <v>0.0</v>
@@ -17221,7 +18440,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>90</v>
@@ -17241,7 +18460,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>90</v>
@@ -17264,7 +18483,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>90</v>
@@ -17324,7 +18543,7 @@
         <v>3.0</v>
       </c>
       <c r="AM97" s="1" t="s">
-        <v>306</v>
+        <v>323</v>
       </c>
       <c r="AN97" s="3">
         <v>0.0</v>
@@ -17356,13 +18575,13 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>307</v>
+        <v>324</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>51</v>
@@ -17376,7 +18595,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>307</v>
+        <v>324</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>49</v>
@@ -17396,7 +18615,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>307</v>
+        <v>324</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>49</v>
@@ -17416,13 +18635,13 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>307</v>
+        <v>324</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="I101" s="2" t="s">
         <v>55</v>
@@ -17445,7 +18664,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>307</v>
+        <v>324</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>49</v>
@@ -17454,7 +18673,7 @@
         <v>2.0</v>
       </c>
       <c r="Q102" s="1" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="R102" s="1" t="s">
         <v>63</v>
@@ -17505,7 +18724,7 @@
         <v>0.0</v>
       </c>
       <c r="AM102" s="1" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="AN102" s="3">
         <v>1.0</v>
@@ -17537,7 +18756,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>308</v>
+        <v>325</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>62</v>
@@ -17549,7 +18768,7 @@
         <v>53</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>309</v>
+        <v>326</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>101</v>
@@ -17557,7 +18776,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>308</v>
+        <v>325</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>62</v>
@@ -17566,24 +18785,24 @@
         <v>54</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>309</v>
+        <v>326</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>64</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>308</v>
+        <v>325</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="I105" s="2" t="s">
         <v>53</v>
@@ -17606,7 +18825,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>308</v>
+        <v>325</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>62</v>
@@ -17666,7 +18885,7 @@
         <v>1.0</v>
       </c>
       <c r="AM106" s="1" t="s">
-        <v>310</v>
+        <v>327</v>
       </c>
       <c r="AN106" s="3">
         <v>1.0</v>
@@ -17856,13 +19075,13 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>311</v>
+        <v>328</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>90</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>51</v>
@@ -17876,13 +19095,13 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>311</v>
+        <v>328</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>90</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>53</v>
@@ -17896,7 +19115,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>311</v>
+        <v>328</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>90</v>
@@ -17916,19 +19135,19 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>311</v>
+        <v>328</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>90</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>53</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>87</v>
@@ -17945,7 +19164,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>311</v>
+        <v>328</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>90</v>
@@ -17974,7 +19193,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>311</v>
+        <v>328</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>90</v>
@@ -18028,7 +19247,7 @@
         <v>0.0</v>
       </c>
       <c r="AM7" s="1" t="s">
-        <v>312</v>
+        <v>329</v>
       </c>
       <c r="AN7" s="3">
         <v>2.0</v>
@@ -18060,7 +19279,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>313</v>
+        <v>330</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>49</v>
@@ -18080,13 +19299,13 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>313</v>
+        <v>330</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>55</v>
@@ -18100,7 +19319,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>313</v>
+        <v>330</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>49</v>
@@ -18129,7 +19348,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>313</v>
+        <v>330</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>49</v>
@@ -18141,7 +19360,7 @@
         <v>63</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="S11" s="3">
         <v>14680.0</v>
@@ -18189,7 +19408,7 @@
         <v>0.0</v>
       </c>
       <c r="AM11" s="1" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="AN11" s="3">
         <v>1.0</v>
@@ -18221,7 +19440,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>314</v>
+        <v>331</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>62</v>
@@ -18241,33 +19460,33 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>314</v>
+        <v>331</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>55</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>314</v>
+        <v>331</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>53</v>
@@ -18290,7 +19509,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>314</v>
+        <v>331</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>62</v>
@@ -18302,7 +19521,7 @@
         <v>63</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="S15" s="3">
         <v>13889.0</v>
@@ -18350,7 +19569,7 @@
         <v>0.0</v>
       </c>
       <c r="AM15" s="1" t="s">
-        <v>315</v>
+        <v>332</v>
       </c>
       <c r="AN15" s="3">
         <v>1.0</v>
@@ -18382,13 +19601,13 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>51</v>
@@ -18402,13 +19621,13 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>53</v>
@@ -18417,7 +19636,7 @@
         <v>71</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="M17" s="3">
         <v>7.0</v>
@@ -18431,13 +19650,13 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>78</v>
@@ -18451,7 +19670,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>69</v>
@@ -18505,7 +19724,7 @@
         <v>0.0</v>
       </c>
       <c r="AM19" s="1" t="s">
-        <v>317</v>
+        <v>334</v>
       </c>
       <c r="AN19" s="3">
         <v>1.0</v>
@@ -18537,7 +19756,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>76</v>
@@ -18557,13 +19776,13 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>53</v>
@@ -18586,7 +19805,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>76</v>
@@ -18646,7 +19865,7 @@
         <v>0.0</v>
       </c>
       <c r="AM22" s="1" t="s">
-        <v>319</v>
+        <v>336</v>
       </c>
       <c r="AN22" s="3">
         <v>1.0</v>
@@ -18678,7 +19897,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>82</v>
@@ -18698,13 +19917,13 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>82</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>53</v>
@@ -18727,7 +19946,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>82</v>
@@ -18787,7 +20006,7 @@
         <v>0.0</v>
       </c>
       <c r="AM25" s="1" t="s">
-        <v>321</v>
+        <v>338</v>
       </c>
       <c r="AN25" s="3">
         <v>1.0</v>
@@ -18819,13 +20038,13 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>322</v>
+        <v>339</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>53</v>
@@ -18839,13 +20058,13 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>322</v>
+        <v>339</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>86</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>51</v>
@@ -18854,12 +20073,12 @@
         <v>65</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>322</v>
+        <v>339</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>86</v>
@@ -18888,7 +20107,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>322</v>
+        <v>339</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>86</v>
@@ -18897,10 +20116,10 @@
         <v>0.0</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="S29" s="3">
         <v>9627.0</v>
@@ -18948,7 +20167,7 @@
         <v>1.0</v>
       </c>
       <c r="AM29" s="1" t="s">
-        <v>323</v>
+        <v>340</v>
       </c>
       <c r="AN29" s="3">
         <v>1.0</v>
@@ -18980,13 +20199,13 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>90</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>51</v>
@@ -19000,7 +20219,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>90</v>
@@ -19015,7 +20234,7 @@
         <v>71</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="M31" s="3">
         <v>8.0</v>
@@ -19029,13 +20248,13 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>90</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>51</v>
@@ -19044,12 +20263,12 @@
         <v>65</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>90</v>
@@ -19058,10 +20277,10 @@
         <v>1.0</v>
       </c>
       <c r="Q33" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="S33" s="3">
         <v>8650.0</v>
@@ -19109,7 +20328,7 @@
         <v>0.0</v>
       </c>
       <c r="AM33" s="1" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="AN33" s="3">
         <v>1.0</v>
@@ -19141,7 +20360,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>49</v>
@@ -19161,27 +20380,27 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>55</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>49</v>
@@ -19210,7 +20429,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>49</v>
@@ -19222,7 +20441,7 @@
         <v>63</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="S37" s="3">
         <v>13913.0</v>
@@ -19270,7 +20489,7 @@
         <v>5.0</v>
       </c>
       <c r="AM37" s="1" t="s">
-        <v>327</v>
+        <v>344</v>
       </c>
       <c r="AN37" s="3">
         <v>1.0</v>
@@ -19302,7 +20521,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>328</v>
+        <v>345</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>62</v>
@@ -19322,13 +20541,13 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>328</v>
+        <v>345</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>55</v>
@@ -19342,13 +20561,13 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>328</v>
+        <v>345</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>53</v>
@@ -19371,7 +20590,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>328</v>
+        <v>345</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>62</v>
@@ -19383,7 +20602,7 @@
         <v>63</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="S41" s="3">
         <v>13277.0</v>
@@ -19431,7 +20650,7 @@
         <v>0.0</v>
       </c>
       <c r="AM41" s="1" t="s">
-        <v>329</v>
+        <v>346</v>
       </c>
       <c r="AN41" s="3">
         <v>1.0</v>
@@ -19463,13 +20682,13 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>330</v>
+        <v>347</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>51</v>
@@ -19483,13 +20702,13 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>330</v>
+        <v>347</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>53</v>
@@ -19498,7 +20717,7 @@
         <v>71</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="M43" s="3">
         <v>8.0</v>
@@ -19512,13 +20731,13 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>330</v>
+        <v>347</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>55</v>
@@ -19532,7 +20751,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>330</v>
+        <v>347</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>69</v>
@@ -19541,10 +20760,10 @@
         <v>0.0</v>
       </c>
       <c r="Q45" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="R45" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="S45" s="3">
         <v>12722.0</v>
@@ -19592,7 +20811,7 @@
         <v>0.0</v>
       </c>
       <c r="AM45" s="1" t="s">
-        <v>331</v>
+        <v>348</v>
       </c>
       <c r="AN45" s="3">
         <v>1.0</v>
@@ -19624,7 +20843,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>76</v>
@@ -19644,13 +20863,13 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>53</v>
@@ -19673,13 +20892,13 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>55</v>
@@ -19693,7 +20912,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>76</v>
@@ -19753,7 +20972,7 @@
         <v>0.0</v>
       </c>
       <c r="AM49" s="1" t="s">
-        <v>333</v>
+        <v>350</v>
       </c>
       <c r="AN49" s="3">
         <v>1.0</v>
@@ -19785,7 +21004,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>334</v>
+        <v>351</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>82</v>
@@ -19805,13 +21024,13 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>334</v>
+        <v>351</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>82</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>51</v>
@@ -19834,7 +21053,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>334</v>
+        <v>351</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>82</v>
@@ -19894,7 +21113,7 @@
         <v>0.0</v>
       </c>
       <c r="AM52" s="1" t="s">
-        <v>335</v>
+        <v>352</v>
       </c>
       <c r="AN52" s="3">
         <v>1.0</v>
@@ -19926,13 +21145,13 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>336</v>
+        <v>353</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>55</v>
@@ -19946,7 +21165,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>336</v>
+        <v>353</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>86</v>
@@ -19965,7 +21184,7 @@
         <v>71</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="M54" s="3">
         <v>7.0</v>
@@ -19979,7 +21198,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>336</v>
+        <v>353</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>86</v>
@@ -19989,7 +21208,7 @@
       <c r="E55" s="1"/>
       <c r="G55" s="1"/>
       <c r="H55" s="1" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>51</v>
@@ -20003,7 +21222,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>336</v>
+        <v>353</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>86</v>
@@ -20061,7 +21280,7 @@
         <v>0.0</v>
       </c>
       <c r="AM56" s="1" t="s">
-        <v>337</v>
+        <v>354</v>
       </c>
       <c r="AN56" s="3">
         <v>1.0</v>
@@ -20093,13 +21312,13 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>338</v>
+        <v>355</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>90</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>51</v>
@@ -20113,13 +21332,13 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>338</v>
+        <v>355</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>90</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>53</v>
@@ -20142,13 +21361,13 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>338</v>
+        <v>355</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>90</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>51</v>
@@ -20162,7 +21381,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>338</v>
+        <v>355</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>90</v>
@@ -20171,10 +21390,10 @@
         <v>0.0</v>
       </c>
       <c r="Q60" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="R60" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="S60" s="3">
         <v>18556.619999999995</v>
@@ -20222,7 +21441,7 @@
         <v>0.0</v>
       </c>
       <c r="AM60" s="1" t="s">
-        <v>339</v>
+        <v>356</v>
       </c>
       <c r="AN60" s="3">
         <v>1.0</v>
@@ -20254,7 +21473,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>340</v>
+        <v>357</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>49</v>
@@ -20274,13 +21493,13 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>340</v>
+        <v>357</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>55</v>
@@ -20294,7 +21513,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>340</v>
+        <v>357</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>49</v>
@@ -20304,7 +21523,7 @@
       <c r="E63" s="1"/>
       <c r="G63" s="1"/>
       <c r="H63" s="1" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>53</v>
@@ -20327,7 +21546,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>340</v>
+        <v>357</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>49</v>
@@ -20343,7 +21562,7 @@
         <v>63</v>
       </c>
       <c r="R64" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="S64" s="3">
         <v>21825.50999999999</v>
@@ -20391,7 +21610,7 @@
         <v>0.0</v>
       </c>
       <c r="AM64" s="1" t="s">
-        <v>341</v>
+        <v>358</v>
       </c>
       <c r="AN64" s="3">
         <v>1.0</v>
@@ -20423,7 +21642,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>342</v>
+        <v>359</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>62</v>
@@ -20443,13 +21662,13 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>342</v>
+        <v>359</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>55</v>
@@ -20463,13 +21682,13 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>342</v>
+        <v>359</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="I67" s="2" t="s">
         <v>53</v>
@@ -20492,7 +21711,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>342</v>
+        <v>359</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>62</v>
@@ -20546,7 +21765,7 @@
         <v>0.0</v>
       </c>
       <c r="AM68" s="1" t="s">
-        <v>343</v>
+        <v>360</v>
       </c>
       <c r="AN68" s="3">
         <v>1.0</v>
@@ -20578,13 +21797,13 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>344</v>
+        <v>361</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>51</v>
@@ -20598,13 +21817,13 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>344</v>
+        <v>361</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>53</v>
@@ -20613,7 +21832,7 @@
         <v>71</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="M70" s="3">
         <v>15.0</v>
@@ -20627,7 +21846,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>344</v>
+        <v>361</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>69</v>
@@ -20681,7 +21900,7 @@
         <v>0.0</v>
       </c>
       <c r="AM71" s="1" t="s">
-        <v>345</v>
+        <v>362</v>
       </c>
       <c r="AN71" s="3">
         <v>1.0</v>
@@ -20713,7 +21932,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>346</v>
+        <v>363</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>76</v>
@@ -20733,13 +21952,13 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>346</v>
+        <v>363</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>53</v>
@@ -20762,7 +21981,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>346</v>
+        <v>363</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>76</v>
@@ -20825,7 +22044,7 @@
         <v>0.0</v>
       </c>
       <c r="AM74" s="1" t="s">
-        <v>347</v>
+        <v>364</v>
       </c>
       <c r="AN74" s="3">
         <v>1.0</v>
@@ -20857,7 +22076,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>348</v>
+        <v>365</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>82</v>
@@ -20877,13 +22096,13 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>348</v>
+        <v>365</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>82</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>53</v>
@@ -20906,13 +22125,13 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>348</v>
+        <v>365</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>82</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>55</v>
@@ -20935,7 +22154,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>348</v>
+        <v>365</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>82</v>
@@ -20995,7 +22214,7 @@
         <v>0.0</v>
       </c>
       <c r="AM78" s="1" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="AN78" s="3">
         <v>2.0</v>
@@ -21027,13 +22246,13 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>349</v>
+        <v>366</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>51</v>
@@ -21047,13 +22266,13 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>349</v>
+        <v>366</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>86</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="I80" s="2" t="s">
         <v>53</v>
@@ -21076,7 +22295,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>349</v>
+        <v>366</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>86</v>
@@ -21105,7 +22324,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>349</v>
+        <v>366</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>86</v>
@@ -21114,10 +22333,10 @@
         <v>0.0</v>
       </c>
       <c r="Q82" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="R82" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="S82" s="3">
         <v>12752.009999999998</v>
@@ -21162,7 +22381,7 @@
         <v>0.0</v>
       </c>
       <c r="AM82" s="1" t="s">
-        <v>350</v>
+        <v>367</v>
       </c>
       <c r="AN82" s="3">
         <v>2.0</v>
@@ -21194,13 +22413,13 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>351</v>
+        <v>368</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>90</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>55</v>
@@ -21214,7 +22433,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>351</v>
+        <v>368</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>90</v>
@@ -21243,13 +22462,13 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>351</v>
+        <v>368</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>90</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="I85" s="2" t="s">
         <v>51</v>
@@ -21266,7 +22485,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>351</v>
+        <v>368</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>90</v>
@@ -21275,7 +22494,7 @@
         <v>0.0</v>
       </c>
       <c r="R86" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="S86" s="3">
         <v>17035.32</v>
@@ -21323,7 +22542,7 @@
         <v>0.0</v>
       </c>
       <c r="AM86" s="1" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="AN86" s="3">
         <v>1.0</v>
@@ -21355,7 +22574,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>352</v>
+        <v>369</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>49</v>
@@ -21375,13 +22594,13 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>352</v>
+        <v>369</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>55</v>
@@ -21395,7 +22614,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>352</v>
+        <v>369</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>49</v>
@@ -21424,7 +22643,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>352</v>
+        <v>369</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>49</v>
@@ -21436,7 +22655,7 @@
         <v>63</v>
       </c>
       <c r="R90" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="S90" s="3">
         <v>25392.46</v>
@@ -21484,7 +22703,7 @@
         <v>0.0</v>
       </c>
       <c r="AM90" s="1" t="s">
-        <v>353</v>
+        <v>370</v>
       </c>
       <c r="AN90" s="3">
         <v>1.0</v>
@@ -21516,7 +22735,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>354</v>
+        <v>371</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>62</v>
@@ -21536,13 +22755,13 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>354</v>
+        <v>371</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>55</v>
@@ -21556,13 +22775,13 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>354</v>
+        <v>371</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="I93" s="2" t="s">
         <v>53</v>
@@ -21585,7 +22804,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>354</v>
+        <v>371</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>62</v>
@@ -21597,7 +22816,7 @@
         <v>63</v>
       </c>
       <c r="R94" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="S94" s="3">
         <v>23475.639999999996</v>
@@ -21645,7 +22864,7 @@
         <v>0.0</v>
       </c>
       <c r="AM94" s="1" t="s">
-        <v>355</v>
+        <v>372</v>
       </c>
       <c r="AN94" s="3">
         <v>1.0</v>
@@ -21677,13 +22896,13 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>356</v>
+        <v>373</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>51</v>
@@ -21697,22 +22916,22 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>356</v>
+        <v>373</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="I96" s="2" t="s">
         <v>53</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="M96" s="3">
         <v>8.0</v>
@@ -21726,7 +22945,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>356</v>
+        <v>373</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>69</v>
@@ -21735,10 +22954,10 @@
         <v>0.0</v>
       </c>
       <c r="Q97" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="R97" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="S97" s="3">
         <v>19985.18999999999</v>
@@ -21786,7 +23005,7 @@
         <v>0.0</v>
       </c>
       <c r="AM97" s="1" t="s">
-        <v>357</v>
+        <v>374</v>
       </c>
       <c r="AN97" s="3">
         <v>1.0</v>
@@ -21818,7 +23037,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>76</v>
@@ -21838,13 +23057,13 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="I99" s="2" t="s">
         <v>51</v>
@@ -21861,13 +23080,13 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="I100" s="2" t="s">
         <v>53</v>
@@ -21890,7 +23109,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>76</v>
@@ -21947,7 +23166,7 @@
         <v>0.0</v>
       </c>
       <c r="AM101" s="1" t="s">
-        <v>359</v>
+        <v>376</v>
       </c>
       <c r="AN101" s="3">
         <v>1.0</v>
@@ -21979,13 +23198,13 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>360</v>
+        <v>377</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>82</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>55</v>
@@ -21999,13 +23218,13 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>360</v>
+        <v>377</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>82</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="I103" s="2" t="s">
         <v>51</v>
@@ -22022,7 +23241,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>360</v>
+        <v>377</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>82</v>
@@ -22051,7 +23270,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>360</v>
+        <v>377</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>82</v>
@@ -22060,7 +23279,7 @@
         <v>0.0</v>
       </c>
       <c r="R105" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="S105" s="3">
         <v>12356.0</v>
@@ -22108,7 +23327,7 @@
         <v>0.0</v>
       </c>
       <c r="AM105" s="1" t="s">
-        <v>361</v>
+        <v>378</v>
       </c>
       <c r="AN105" s="3">
         <v>1.0</v>
@@ -22140,13 +23359,13 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>362</v>
+        <v>379</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>55</v>
@@ -22160,13 +23379,13 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>362</v>
+        <v>379</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>86</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="I107" s="2" t="s">
         <v>51</v>
@@ -22183,7 +23402,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>362</v>
+        <v>379</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>86</v>
@@ -22212,7 +23431,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>362</v>
+        <v>379</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>86</v>
@@ -22221,7 +23440,7 @@
         <v>0.0</v>
       </c>
       <c r="R109" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="S109" s="3">
         <v>8748.0</v>
@@ -22269,7 +23488,7 @@
         <v>0.0</v>
       </c>
       <c r="AM109" s="1" t="s">
-        <v>363</v>
+        <v>380</v>
       </c>
       <c r="AN109" s="3">
         <v>1.0</v>
@@ -22301,13 +23520,13 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>364</v>
+        <v>381</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>90</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>55</v>
@@ -22321,7 +23540,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>364</v>
+        <v>381</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>90</v>
@@ -22350,13 +23569,13 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>364</v>
+        <v>381</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>90</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="I112" s="2" t="s">
         <v>51</v>
@@ -22379,7 +23598,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>364</v>
+        <v>381</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>90</v>
@@ -22433,7 +23652,7 @@
         <v>0.0</v>
       </c>
       <c r="AM113" s="1" t="s">
-        <v>269</v>
+        <v>286</v>
       </c>
       <c r="AN113" s="3">
         <v>2.0</v>
@@ -22465,13 +23684,13 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>365</v>
+        <v>382</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>55</v>
@@ -22485,13 +23704,13 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>365</v>
+        <v>382</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>55</v>
@@ -22505,13 +23724,13 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>365</v>
+        <v>382</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="I116" s="2" t="s">
         <v>53</v>
@@ -22534,13 +23753,13 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>365</v>
+        <v>382</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="I117" s="2" t="s">
         <v>51</v>
@@ -22557,7 +23776,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>365</v>
+        <v>382</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>49</v>
@@ -22566,7 +23785,7 @@
         <v>1.0</v>
       </c>
       <c r="R118" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="S118" s="3">
         <v>22791.559999999998</v>
@@ -22614,7 +23833,7 @@
         <v>0.0</v>
       </c>
       <c r="AM118" s="1" t="s">
-        <v>341</v>
+        <v>358</v>
       </c>
       <c r="AN118" s="3">
         <v>1.0</v>
@@ -22646,13 +23865,13 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>366</v>
+        <v>383</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>51</v>
@@ -22666,13 +23885,13 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>366</v>
+        <v>383</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>55</v>
@@ -22686,7 +23905,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>366</v>
+        <v>383</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>62</v>
@@ -22715,7 +23934,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>366</v>
+        <v>383</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>62</v>
@@ -22769,7 +23988,7 @@
         <v>0.0</v>
       </c>
       <c r="AM122" s="1" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="AN122" s="3">
         <v>1.0</v>

--- a/admin_testy/reporty_google_testy/google_data/Pobočky/Prosek/Databaze Prosek 2026.xlsx
+++ b/admin_testy/reporty_google_testy/google_data/Pobočky/Prosek/Databaze Prosek 2026.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3207" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3253" uniqueCount="387">
   <si>
     <t>Datum</t>
   </si>
@@ -393,6 +393,24 @@
     <t>13 min 16 s</t>
   </si>
   <si>
+    <t>20.05.2026</t>
+  </si>
+  <si>
+    <t>9 min 40 s</t>
+  </si>
+  <si>
+    <t>21.05.2026</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>Yarushynskyi Vladyslav</t>
+  </si>
+  <si>
+    <t>10 min 25 s</t>
+  </si>
+  <si>
     <t>01.04.2026</t>
   </si>
   <si>
@@ -429,9 +447,6 @@
     <t>05.04.2026</t>
   </si>
   <si>
-    <t>13:00</t>
-  </si>
-  <si>
     <t>9 min 31 s</t>
   </si>
   <si>
@@ -930,9 +945,6 @@
     <t>16.02.2026</t>
   </si>
   <si>
-    <t>10 min 25 s</t>
-  </si>
-  <si>
     <t>17.02.2026</t>
   </si>
   <si>
@@ -1132,9 +1144,6 @@
   </si>
   <si>
     <t>24.01.2026</t>
-  </si>
-  <si>
-    <t>9 min 40 s</t>
   </si>
   <si>
     <t>25.01.2026</t>
@@ -4488,6 +4497,328 @@
         <v>0.1111111111111111</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L71" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="M71" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N71" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O71" s="3">
+        <v>360.0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="P72" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Q72" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="R72" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="S72" s="3">
+        <v>10896.899999999998</v>
+      </c>
+      <c r="T72" s="3">
+        <v>5550.0</v>
+      </c>
+      <c r="U72" s="3">
+        <v>3677.0</v>
+      </c>
+      <c r="V72" s="3">
+        <v>5125.0</v>
+      </c>
+      <c r="W72" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X72" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Y72" s="3">
+        <v>2370.0</v>
+      </c>
+      <c r="AA72" s="3">
+        <v>2742.0</v>
+      </c>
+      <c r="AB72" s="3">
+        <v>30720.399999999998</v>
+      </c>
+      <c r="AC72" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="AD72" s="3">
+        <v>0.3227684363988876</v>
+      </c>
+      <c r="AI72" s="3">
+        <v>360.0</v>
+      </c>
+      <c r="AJ72" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK72" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL72" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AM72" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="AN72" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AO72" s="3">
+        <v>79.0</v>
+      </c>
+      <c r="AP72" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="AQ72" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AR72" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS72" s="3">
+        <v>0.125</v>
+      </c>
+      <c r="AT72" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU72" s="3">
+        <v>0.875</v>
+      </c>
+      <c r="AV72" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L76" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="M76" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="N76" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O76" s="3">
+        <v>270.0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="P77" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="Q77" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="R77" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="S77" s="3">
+        <v>14677.9</v>
+      </c>
+      <c r="T77" s="3">
+        <v>4388.0</v>
+      </c>
+      <c r="U77" s="3">
+        <v>4578.0</v>
+      </c>
+      <c r="V77" s="3">
+        <v>2943.0</v>
+      </c>
+      <c r="W77" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X77" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Y77" s="3">
+        <v>2173.0</v>
+      </c>
+      <c r="AA77" s="3">
+        <v>1999.0</v>
+      </c>
+      <c r="AB77" s="3">
+        <v>31028.899999999998</v>
+      </c>
+      <c r="AC77" s="3">
+        <v>3.637978807091713E-12</v>
+      </c>
+      <c r="AD77" s="3">
+        <v>0.39309287385464475</v>
+      </c>
+      <c r="AI77" s="3">
+        <v>270.0</v>
+      </c>
+      <c r="AJ77" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AK77" s="3">
+        <v>238.0</v>
+      </c>
+      <c r="AL77" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AM77" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="AN77" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AO77" s="3">
+        <v>81.0</v>
+      </c>
+      <c r="AP77" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="AQ77" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AR77" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS77" s="3">
+        <v>0.125</v>
+      </c>
+      <c r="AT77" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU77" s="3">
+        <v>0.875</v>
+      </c>
+      <c r="AV77" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -4648,7 +4979,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>86</v>
@@ -4668,7 +4999,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>86</v>
@@ -4688,7 +5019,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>86</v>
@@ -4717,7 +5048,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>86</v>
@@ -4783,7 +5114,7 @@
         <v>1.0</v>
       </c>
       <c r="AM5" s="1" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="AN5" s="3">
         <v>1.0</v>
@@ -4815,7 +5146,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>90</v>
@@ -4835,7 +5166,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>90</v>
@@ -4864,7 +5195,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>90</v>
@@ -4927,7 +5258,7 @@
         <v>0.0</v>
       </c>
       <c r="AM8" s="1" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="AN8" s="3">
         <v>1.0</v>
@@ -4959,7 +5290,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>49</v>
@@ -4979,7 +5310,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>49</v>
@@ -4989,10 +5320,10 @@
       <c r="E10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>64</v>
@@ -5006,7 +5337,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>49</v>
@@ -5073,7 +5404,7 @@
         <v>3.0</v>
       </c>
       <c r="AM11" s="1" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="AN11" s="3">
         <v>0.0</v>
@@ -5105,7 +5436,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>62</v>
@@ -5125,13 +5456,13 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>53</v>
@@ -5154,7 +5485,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>62</v>
@@ -5217,7 +5548,7 @@
         <v>2.0</v>
       </c>
       <c r="AM14" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="AN14" s="3">
         <v>1.0</v>
@@ -5249,7 +5580,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>69</v>
@@ -5269,13 +5600,13 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>53</v>
@@ -5284,7 +5615,7 @@
         <v>71</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="M16" s="3">
         <v>8.0</v>
@@ -5298,7 +5629,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>69</v>
@@ -5358,7 +5689,7 @@
         <v>0.0</v>
       </c>
       <c r="AM17" s="1" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AN17" s="3">
         <v>1.0</v>
@@ -5390,7 +5721,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>76</v>
@@ -5410,7 +5741,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>76</v>
@@ -5430,7 +5761,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>76</v>
@@ -5459,7 +5790,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>76</v>
@@ -5522,7 +5853,7 @@
         <v>3.0</v>
       </c>
       <c r="AM21" s="1" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="AN21" s="3">
         <v>1.0</v>
@@ -5554,7 +5885,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>82</v>
@@ -5574,7 +5905,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>82</v>
@@ -5594,7 +5925,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>82</v>
@@ -5623,7 +5954,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>82</v>
@@ -5686,7 +6017,7 @@
         <v>0.0</v>
       </c>
       <c r="AM25" s="1" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="AN25" s="3">
         <v>1.0</v>
@@ -5718,7 +6049,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>86</v>
@@ -5738,7 +6069,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>86</v>
@@ -5758,7 +6089,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>86</v>
@@ -5787,7 +6118,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>86</v>
@@ -5847,7 +6178,7 @@
         <v>1.0</v>
       </c>
       <c r="AM29" s="1" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="AN29" s="3">
         <v>1.0</v>
@@ -5879,7 +6210,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>90</v>
@@ -5899,7 +6230,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>90</v>
@@ -5919,7 +6250,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>90</v>
@@ -5948,7 +6279,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>90</v>
@@ -6008,7 +6339,7 @@
         <v>2.0</v>
       </c>
       <c r="AM33" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="AN33" s="3">
         <v>1.0</v>
@@ -6040,7 +6371,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>49</v>
@@ -6060,7 +6391,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>49</v>
@@ -6080,7 +6411,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>49</v>
@@ -6109,7 +6440,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>49</v>
@@ -6172,7 +6503,7 @@
         <v>0.0</v>
       </c>
       <c r="AM37" s="1" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="AN37" s="3">
         <v>1.0</v>
@@ -6204,7 +6535,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>62</v>
@@ -6216,7 +6547,7 @@
         <v>51</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>102</v>
@@ -6224,39 +6555,39 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>55</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>77</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>66</v>
@@ -6264,7 +6595,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>62</v>
@@ -6280,7 +6611,7 @@
         <v>50</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="S41" s="3">
         <v>17084.0</v>
@@ -6328,7 +6659,7 @@
         <v>2.0</v>
       </c>
       <c r="AM41" s="1" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="AN41" s="3">
         <v>0.0</v>
@@ -6360,13 +6691,13 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>51</v>
@@ -6380,7 +6711,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>69</v>
@@ -6400,13 +6731,13 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>55</v>
@@ -6420,7 +6751,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>69</v>
@@ -6430,7 +6761,7 @@
       <c r="E45" s="1"/>
       <c r="G45" s="1"/>
       <c r="H45" s="1" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>55</v>
@@ -6447,7 +6778,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>69</v>
@@ -6460,7 +6791,7 @@
         <v>2.0</v>
       </c>
       <c r="Q46" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="R46" s="1" t="s">
         <v>54</v>
@@ -6517,7 +6848,7 @@
         <v>1.0</v>
       </c>
       <c r="AM46" s="1" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="AN46" s="3">
         <v>0.0</v>
@@ -6549,7 +6880,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>76</v>
@@ -6569,7 +6900,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>76</v>
@@ -6589,7 +6920,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>76</v>
@@ -6618,7 +6949,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>76</v>
@@ -6678,7 +7009,7 @@
         <v>0.0</v>
       </c>
       <c r="AM50" s="1" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="AN50" s="3">
         <v>1.0</v>
@@ -6710,7 +7041,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>82</v>
@@ -6730,7 +7061,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>82</v>
@@ -6750,7 +7081,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>82</v>
@@ -6779,7 +7110,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>82</v>
@@ -6848,7 +7179,7 @@
         <v>1.0</v>
       </c>
       <c r="AM54" s="1" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="AN54" s="3">
         <v>1.0</v>
@@ -6880,7 +7211,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>86</v>
@@ -6892,15 +7223,15 @@
         <v>51</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>86</v>
@@ -6920,7 +7251,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>86</v>
@@ -6932,7 +7263,7 @@
         <v>51</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="L57" s="2" t="s">
         <v>102</v>
@@ -6949,22 +7280,22 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>86</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>58</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="M58" s="3">
         <v>3.0</v>
@@ -6978,7 +7309,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>86</v>
@@ -7038,7 +7369,7 @@
         <v>0.0</v>
       </c>
       <c r="AM59" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="AN59" s="3">
         <v>2.0</v>
@@ -7070,7 +7401,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>90</v>
@@ -7090,7 +7421,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>90</v>
@@ -7119,7 +7450,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>90</v>
@@ -7179,7 +7510,7 @@
         <v>1.0</v>
       </c>
       <c r="AM62" s="1" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="AN62" s="3">
         <v>1.0</v>
@@ -7211,7 +7542,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>49</v>
@@ -7231,7 +7562,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>49</v>
@@ -7251,7 +7582,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>49</v>
@@ -7261,7 +7592,7 @@
       <c r="E65" s="1"/>
       <c r="G65" s="1"/>
       <c r="H65" s="1" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>53</v>
@@ -7284,7 +7615,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>49</v>
@@ -7351,7 +7682,7 @@
         <v>0.0</v>
       </c>
       <c r="AM66" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="AN66" s="3">
         <v>1.0</v>
@@ -7383,7 +7714,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>62</v>
@@ -7403,7 +7734,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>62</v>
@@ -7423,7 +7754,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>62</v>
@@ -7435,15 +7766,15 @@
         <v>55</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>62</v>
@@ -7472,7 +7803,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>62</v>
@@ -7532,7 +7863,7 @@
         <v>2.0</v>
       </c>
       <c r="AM71" s="1" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="AN71" s="3">
         <v>1.0</v>
@@ -7564,7 +7895,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>69</v>
@@ -7584,13 +7915,13 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>55</v>
@@ -7604,7 +7935,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>69</v>
@@ -7667,7 +7998,7 @@
         <v>2.0</v>
       </c>
       <c r="AM74" s="1" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="AN74" s="3">
         <v>0.0</v>
@@ -7699,7 +8030,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>76</v>
@@ -7711,15 +8042,15 @@
         <v>51</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>76</v>
@@ -7739,7 +8070,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>76</v>
@@ -7768,7 +8099,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>76</v>
@@ -7831,7 +8162,7 @@
         <v>0.0</v>
       </c>
       <c r="AM78" s="1" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="AN78" s="3">
         <v>1.0</v>
@@ -7863,7 +8194,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>82</v>
@@ -7883,7 +8214,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>82</v>
@@ -7912,7 +8243,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>82</v>
@@ -7975,7 +8306,7 @@
         <v>1.0</v>
       </c>
       <c r="AM81" s="1" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="AN81" s="3">
         <v>1.0</v>
@@ -8007,7 +8338,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>86</v>
@@ -8027,7 +8358,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>86</v>
@@ -8047,7 +8378,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>86</v>
@@ -8076,7 +8407,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>86</v>
@@ -8136,7 +8467,7 @@
         <v>1.0</v>
       </c>
       <c r="AM85" s="1" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="AN85" s="3">
         <v>1.0</v>
@@ -8168,7 +8499,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>90</v>
@@ -8188,7 +8519,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>90</v>
@@ -8217,7 +8548,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>90</v>
@@ -8277,7 +8608,7 @@
         <v>1.0</v>
       </c>
       <c r="AM88" s="1" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="AN88" s="3">
         <v>1.0</v>
@@ -8309,7 +8640,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>49</v>
@@ -8329,13 +8660,13 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="I90" s="2" t="s">
         <v>53</v>
@@ -8358,7 +8689,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>49</v>
@@ -8418,7 +8749,7 @@
         <v>2.0</v>
       </c>
       <c r="AM91" s="1" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="AN91" s="3">
         <v>1.0</v>
@@ -8450,7 +8781,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>62</v>
@@ -8470,7 +8801,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>62</v>
@@ -8499,13 +8830,13 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="I94" s="2" t="s">
         <v>55</v>
@@ -8528,7 +8859,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>62</v>
@@ -8588,7 +8919,7 @@
         <v>0.0</v>
       </c>
       <c r="AM95" s="1" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="AN95" s="3">
         <v>2.0</v>
@@ -8620,7 +8951,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>69</v>
@@ -8640,7 +8971,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>69</v>
@@ -8700,7 +9031,7 @@
         <v>0.0</v>
       </c>
       <c r="AM97" s="1" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="AN97" s="3">
         <v>0.0</v>
@@ -8732,7 +9063,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>76</v>
@@ -8752,7 +9083,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>76</v>
@@ -8775,7 +9106,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>76</v>
@@ -8835,7 +9166,7 @@
         <v>0.0</v>
       </c>
       <c r="AM100" s="1" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="AN100" s="3">
         <v>0.0</v>
@@ -8867,7 +9198,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>82</v>
@@ -8887,7 +9218,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>82</v>
@@ -8907,7 +9238,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>82</v>
@@ -8999,7 +9330,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>86</v>
@@ -9019,7 +9350,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>86</v>
@@ -9028,13 +9359,13 @@
         <v>57</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="J105" s="2" t="s">
         <v>58</v>
       </c>
       <c r="L105" s="2" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="M105" s="3">
         <v>8.0</v>
@@ -9042,7 +9373,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>86</v>
@@ -9108,7 +9439,7 @@
         <v>2.0</v>
       </c>
       <c r="AM106" s="1" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="AN106" s="3">
         <v>0.0</v>
@@ -9140,7 +9471,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>90</v>
@@ -9160,7 +9491,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>90</v>
@@ -9175,7 +9506,7 @@
         <v>101</v>
       </c>
       <c r="L108" s="2" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="M108" s="3">
         <v>9.0</v>
@@ -9183,7 +9514,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>90</v>
@@ -9243,7 +9574,7 @@
         <v>2.0</v>
       </c>
       <c r="AM109" s="1" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="AN109" s="3">
         <v>0.0</v>
@@ -9433,7 +9764,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>69</v>
@@ -9445,7 +9776,7 @@
         <v>51</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>64</v>
@@ -9453,7 +9784,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>69</v>
@@ -9462,7 +9793,7 @@
         <v>63</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>71</v>
@@ -9473,13 +9804,13 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>53</v>
@@ -9488,7 +9819,7 @@
         <v>71</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="M4" s="3">
         <v>15.0</v>
@@ -9502,7 +9833,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>69</v>
@@ -9565,7 +9896,7 @@
         <v>5.0</v>
       </c>
       <c r="AM5" s="1" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="AN5" s="3">
         <v>1.0</v>
@@ -9597,7 +9928,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>76</v>
@@ -9617,7 +9948,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>76</v>
@@ -9637,7 +9968,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>76</v>
@@ -9657,7 +9988,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>76</v>
@@ -9686,7 +10017,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>76</v>
@@ -9746,7 +10077,7 @@
         <v>0.0</v>
       </c>
       <c r="AM10" s="1" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="AN10" s="3">
         <v>1.0</v>
@@ -9778,7 +10109,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>82</v>
@@ -9798,13 +10129,13 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>82</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>53</v>
@@ -9813,7 +10144,7 @@
         <v>71</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="M12" s="3">
         <v>8.0</v>
@@ -9827,7 +10158,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>82</v>
@@ -9890,7 +10221,7 @@
         <v>3.0</v>
       </c>
       <c r="AM13" s="1" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="AN13" s="3">
         <v>1.0</v>
@@ -9922,7 +10253,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>86</v>
@@ -9942,7 +10273,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>86</v>
@@ -9951,10 +10282,10 @@
         <v>50</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>70</v>
@@ -9962,7 +10293,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>86</v>
@@ -9982,7 +10313,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>86</v>
@@ -10005,7 +10336,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>86</v>
@@ -10068,7 +10399,7 @@
         <v>0.0</v>
       </c>
       <c r="AM18" s="1" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="AN18" s="3">
         <v>0.0</v>
@@ -10100,7 +10431,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>90</v>
@@ -10120,7 +10451,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>90</v>
@@ -10140,7 +10471,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>90</v>
@@ -10163,7 +10494,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>90</v>
@@ -10229,7 +10560,7 @@
         <v>2.0</v>
       </c>
       <c r="AM22" s="1" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="AN22" s="3">
         <v>0.0</v>
@@ -10261,7 +10592,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>49</v>
@@ -10281,7 +10612,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>49</v>
@@ -10291,7 +10622,7 @@
       <c r="E24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>51</v>
@@ -10314,7 +10645,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>49</v>
@@ -10378,7 +10709,7 @@
         <v>3.0</v>
       </c>
       <c r="AM25" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="AN25" s="3">
         <v>1.0</v>
@@ -10410,7 +10741,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>62</v>
@@ -10425,12 +10756,12 @@
         <v>65</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>62</v>
@@ -10445,12 +10776,12 @@
         <v>64</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>62</v>
@@ -10460,7 +10791,7 @@
       <c r="E28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>53</v>
@@ -10483,7 +10814,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>62</v>
@@ -10547,7 +10878,7 @@
         <v>7.0</v>
       </c>
       <c r="AM29" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="AN29" s="3">
         <v>1.0</v>
@@ -10579,7 +10910,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>69</v>
@@ -10599,7 +10930,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>69</v>
@@ -10609,7 +10940,7 @@
       <c r="E31" s="1"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>53</v>
@@ -10618,7 +10949,7 @@
         <v>71</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="M31" s="3">
         <v>12.0</v>
@@ -10632,7 +10963,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>69</v>
@@ -10648,7 +10979,7 @@
         <v>50</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="S32" s="3">
         <v>12040.0</v>
@@ -10699,7 +11030,7 @@
         <v>9.0</v>
       </c>
       <c r="AM32" s="1" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="AN32" s="3">
         <v>1.0</v>
@@ -10731,7 +11062,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>76</v>
@@ -10751,7 +11082,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>76</v>
@@ -10780,7 +11111,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>76</v>
@@ -10840,7 +11171,7 @@
         <v>0.0</v>
       </c>
       <c r="AM35" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="AN35" s="3">
         <v>1.0</v>
@@ -10872,7 +11203,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>82</v>
@@ -10892,7 +11223,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>82</v>
@@ -10921,7 +11252,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>82</v>
@@ -10981,7 +11312,7 @@
         <v>0.0</v>
       </c>
       <c r="AM38" s="1" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="AN38" s="3">
         <v>1.0</v>
@@ -11013,7 +11344,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>86</v>
@@ -11033,7 +11364,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>86</v>
@@ -11053,13 +11384,13 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>86</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>78</v>
@@ -11073,13 +11404,13 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>86</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>51</v>
@@ -11093,7 +11424,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>86</v>
@@ -11122,7 +11453,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>86</v>
@@ -11182,7 +11513,7 @@
         <v>1.0</v>
       </c>
       <c r="AM44" s="1" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="AN44" s="3">
         <v>1.0</v>
@@ -11214,7 +11545,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>90</v>
@@ -11234,7 +11565,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>90</v>
@@ -11254,13 +11585,13 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>90</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>55</v>
@@ -11274,7 +11605,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>90</v>
@@ -11284,7 +11615,7 @@
       <c r="E48" s="1"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>53</v>
@@ -11298,7 +11629,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>90</v>
@@ -11331,7 +11662,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>90</v>
@@ -11398,7 +11729,7 @@
         <v>1.0</v>
       </c>
       <c r="AM50" s="1" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="AN50" s="3">
         <v>1.0</v>
@@ -11430,7 +11761,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>49</v>
@@ -11442,15 +11773,15 @@
         <v>51</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>49</v>
@@ -11470,13 +11801,13 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>53</v>
@@ -11493,7 +11824,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>49</v>
@@ -11556,7 +11887,7 @@
         <v>3.0</v>
       </c>
       <c r="AM54" s="1" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="AN54" s="3">
         <v>0.0</v>
@@ -11588,7 +11919,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>62</v>
@@ -11608,7 +11939,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>62</v>
@@ -11620,30 +11951,30 @@
         <v>55</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>53</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="M57" s="3">
         <v>13.0</v>
@@ -11651,7 +11982,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>62</v>
@@ -11714,7 +12045,7 @@
         <v>5.0</v>
       </c>
       <c r="AM58" s="1" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="AN58" s="3">
         <v>0.0</v>
@@ -11746,7 +12077,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>69</v>
@@ -11766,13 +12097,13 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>53</v>
@@ -11781,7 +12112,7 @@
         <v>71</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="M60" s="3">
         <v>9.0</v>
@@ -11789,7 +12120,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>69</v>
@@ -11849,7 +12180,7 @@
         <v>6.0</v>
       </c>
       <c r="AM61" s="1" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="AN61" s="3">
         <v>0.0</v>
@@ -11881,7 +12212,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>76</v>
@@ -11901,7 +12232,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>76</v>
@@ -11921,7 +12252,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>76</v>
@@ -11933,10 +12264,10 @@
         <v>53</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="M64" s="3">
         <v>6.0</v>
@@ -11950,7 +12281,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>76</v>
@@ -12010,7 +12341,7 @@
         <v>2.0</v>
       </c>
       <c r="AM65" s="1" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="AN65" s="3">
         <v>1.0</v>
@@ -12042,7 +12373,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>82</v>
@@ -12062,7 +12393,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>82</v>
@@ -12091,7 +12422,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>82</v>
@@ -12151,7 +12482,7 @@
         <v>0.0</v>
       </c>
       <c r="AM68" s="1" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="AN68" s="3">
         <v>1.0</v>
@@ -12183,7 +12514,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>86</v>
@@ -12203,7 +12534,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>86</v>
@@ -12232,7 +12563,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>86</v>
@@ -12292,7 +12623,7 @@
         <v>0.0</v>
       </c>
       <c r="AM71" s="1" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="AN71" s="3">
         <v>1.0</v>
@@ -12324,7 +12655,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>90</v>
@@ -12344,7 +12675,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>90</v>
@@ -12364,13 +12695,13 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>90</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>77</v>
@@ -12384,7 +12715,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>90</v>
@@ -12413,7 +12744,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>90</v>
@@ -12476,7 +12807,7 @@
         <v>0.0</v>
       </c>
       <c r="AM76" s="1" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="AN76" s="3">
         <v>1.0</v>
@@ -12508,7 +12839,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>49</v>
@@ -12528,13 +12859,13 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>55</v>
@@ -12548,7 +12879,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>49</v>
@@ -12608,7 +12939,7 @@
         <v>4.0</v>
       </c>
       <c r="AM79" s="1" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="AN79" s="3">
         <v>0.0</v>
@@ -12640,7 +12971,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>62</v>
@@ -12652,15 +12983,15 @@
         <v>51</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>62</v>
@@ -12680,7 +13011,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>62</v>
@@ -12692,15 +13023,15 @@
         <v>78</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>62</v>
@@ -12760,7 +13091,7 @@
         <v>5.0</v>
       </c>
       <c r="AM83" s="1" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="AN83" s="3">
         <v>0.0</v>
@@ -12792,7 +13123,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>69</v>
@@ -12812,7 +13143,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>69</v>
@@ -12872,7 +13203,7 @@
         <v>2.0</v>
       </c>
       <c r="AM85" s="1" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="AN85" s="3">
         <v>0.0</v>
@@ -12904,7 +13235,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>76</v>
@@ -12924,7 +13255,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>76</v>
@@ -12936,7 +13267,7 @@
         <v>51</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>64</v>
@@ -12944,7 +13275,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>76</v>
@@ -12973,7 +13304,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>76</v>
@@ -13033,7 +13364,7 @@
         <v>0.0</v>
       </c>
       <c r="AM89" s="1" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="AN89" s="3">
         <v>1.0</v>
@@ -13065,7 +13396,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>82</v>
@@ -13077,15 +13408,15 @@
         <v>51</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>82</v>
@@ -13105,7 +13436,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>82</v>
@@ -13134,7 +13465,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>82</v>
@@ -13197,7 +13528,7 @@
         <v>0.0</v>
       </c>
       <c r="AM93" s="1" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="AN93" s="3">
         <v>1.0</v>
@@ -13229,7 +13560,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>86</v>
@@ -13241,15 +13572,15 @@
         <v>51</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>86</v>
@@ -13269,7 +13600,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>86</v>
@@ -13298,7 +13629,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>86</v>
@@ -13361,7 +13692,7 @@
         <v>1.0</v>
       </c>
       <c r="AM97" s="1" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="AN97" s="3">
         <v>1.0</v>
@@ -13393,7 +13724,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>90</v>
@@ -13413,7 +13744,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>90</v>
@@ -13442,7 +13773,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>90</v>
@@ -13505,7 +13836,7 @@
         <v>2.0</v>
       </c>
       <c r="AM100" s="1" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="AN100" s="3">
         <v>1.0</v>
@@ -13537,7 +13868,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>49</v>
@@ -13557,16 +13888,16 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>65</v>
@@ -13577,7 +13908,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>49</v>
@@ -13637,7 +13968,7 @@
         <v>4.0</v>
       </c>
       <c r="AM103" s="1" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="AN103" s="3">
         <v>0.0</v>
@@ -13669,7 +14000,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>62</v>
@@ -13681,15 +14012,15 @@
         <v>51</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>62</v>
@@ -13709,36 +14040,36 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>77</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="J107" s="2" t="s">
         <v>64</v>
@@ -13758,13 +14089,13 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="I108" s="2" t="s">
         <v>53</v>
@@ -13781,7 +14112,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>62</v>
@@ -13844,7 +14175,7 @@
         <v>1.0</v>
       </c>
       <c r="AM109" s="1" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="AN109" s="3">
         <v>1.0</v>
@@ -13876,7 +14207,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>69</v>
@@ -13896,13 +14227,13 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>55</v>
@@ -13916,7 +14247,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>69</v>
@@ -13936,7 +14267,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>69</v>
@@ -14000,7 +14331,7 @@
         <v>3.0</v>
       </c>
       <c r="AM113" s="1" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="AN113" s="3">
         <v>0.0</v>
@@ -14032,7 +14363,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>76</v>
@@ -14052,7 +14383,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>76</v>
@@ -14072,7 +14403,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>76</v>
@@ -14092,7 +14423,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>76</v>
@@ -14121,7 +14452,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>76</v>
@@ -14184,7 +14515,7 @@
         <v>0.0</v>
       </c>
       <c r="AM118" s="1" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="AN118" s="3">
         <v>1.0</v>
@@ -14216,7 +14547,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>82</v>
@@ -14236,7 +14567,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>82</v>
@@ -14256,7 +14587,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>82</v>
@@ -14279,7 +14610,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>82</v>
@@ -14308,7 +14639,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>82</v>
@@ -14374,7 +14705,7 @@
         <v>0.0</v>
       </c>
       <c r="AM123" s="1" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="AN123" s="3">
         <v>1.0</v>
@@ -14564,13 +14895,13 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>51</v>
@@ -14584,13 +14915,13 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>53</v>
@@ -14599,7 +14930,7 @@
         <v>71</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="M3" s="3">
         <v>10.0</v>
@@ -14613,7 +14944,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>69</v>
@@ -14667,7 +14998,7 @@
         <v>0.0</v>
       </c>
       <c r="AM4" s="1" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="AN4" s="3">
         <v>1.0</v>
@@ -14699,7 +15030,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>76</v>
@@ -14719,7 +15050,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>76</v>
@@ -14748,7 +15079,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>76</v>
@@ -14808,7 +15139,7 @@
         <v>1.0</v>
       </c>
       <c r="AM7" s="1" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AN7" s="3">
         <v>1.0</v>
@@ -14840,7 +15171,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>82</v>
@@ -14860,13 +15191,13 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>82</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>53</v>
@@ -14889,13 +15220,13 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>82</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>51</v>
@@ -14912,7 +15243,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>82</v>
@@ -14969,7 +15300,7 @@
         <v>0.0</v>
       </c>
       <c r="AM11" s="1" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="AN11" s="3">
         <v>1.0</v>
@@ -15001,13 +15332,13 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>51</v>
@@ -15021,13 +15352,13 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>86</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>53</v>
@@ -15050,7 +15381,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>86</v>
@@ -15059,10 +15390,10 @@
         <v>0.0</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="S14" s="3">
         <v>15925.179999999997</v>
@@ -15110,7 +15441,7 @@
         <v>0.0</v>
       </c>
       <c r="AM14" s="1" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="AN14" s="3">
         <v>1.0</v>
@@ -15142,7 +15473,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>90</v>
@@ -15162,13 +15493,13 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>90</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>51</v>
@@ -15185,7 +15516,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>90</v>
@@ -15214,7 +15545,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>90</v>
@@ -15271,7 +15602,7 @@
         <v>0.0</v>
       </c>
       <c r="AM18" s="1" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="AN18" s="3">
         <v>1.0</v>
@@ -15303,13 +15634,13 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>51</v>
@@ -15323,13 +15654,13 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>55</v>
@@ -15343,7 +15674,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>49</v>
@@ -15372,7 +15703,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>49</v>
@@ -15426,7 +15757,7 @@
         <v>0.0</v>
       </c>
       <c r="AM22" s="1" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="AN22" s="3">
         <v>1.0</v>
@@ -15458,13 +15789,13 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>51</v>
@@ -15478,22 +15809,22 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>53</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="M24" s="3">
         <v>10.0</v>
@@ -15507,13 +15838,13 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>55</v>
@@ -15530,13 +15861,13 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>53</v>
@@ -15559,7 +15890,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>62</v>
@@ -15613,7 +15944,7 @@
         <v>1.0</v>
       </c>
       <c r="AM27" s="1" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="AN27" s="3">
         <v>2.0</v>
@@ -15645,13 +15976,13 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>51</v>
@@ -15665,13 +15996,13 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>93</v>
@@ -15694,13 +16025,13 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>53</v>
@@ -15723,13 +16054,13 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>93</v>
@@ -15752,7 +16083,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>69</v>
@@ -15761,10 +16092,10 @@
         <v>0.0</v>
       </c>
       <c r="Q32" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="S32" s="3">
         <v>9567.0</v>
@@ -15812,7 +16143,7 @@
         <v>0.0</v>
       </c>
       <c r="AM32" s="1" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="AN32" s="3">
         <v>3.0</v>
@@ -15844,13 +16175,13 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>76</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>51</v>
@@ -15864,7 +16195,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>76</v>
@@ -15884,13 +16215,13 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>53</v>
@@ -15913,13 +16244,13 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>93</v>
@@ -15942,7 +16273,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>76</v>
@@ -15951,7 +16282,7 @@
         <v>1.0</v>
       </c>
       <c r="Q37" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="R37" s="1" t="s">
         <v>63</v>
@@ -16002,7 +16333,7 @@
         <v>0.0</v>
       </c>
       <c r="AM37" s="1" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="AN37" s="3">
         <v>2.0</v>
@@ -16034,13 +16365,13 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>82</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>51</v>
@@ -16054,13 +16385,13 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>82</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>53</v>
@@ -16083,13 +16414,13 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>82</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>55</v>
@@ -16112,7 +16443,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>82</v>
@@ -16121,10 +16452,10 @@
         <v>0.0</v>
       </c>
       <c r="Q41" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="S41" s="3">
         <v>6459.0</v>
@@ -16172,7 +16503,7 @@
         <v>0.0</v>
       </c>
       <c r="AM41" s="1" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="AN41" s="3">
         <v>2.0</v>
@@ -16204,7 +16535,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>86</v>
@@ -16224,7 +16555,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>86</v>
@@ -16253,7 +16584,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>86</v>
@@ -16313,7 +16644,7 @@
         <v>0.0</v>
       </c>
       <c r="AM44" s="1" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="AN44" s="3">
         <v>1.0</v>
@@ -16345,7 +16676,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>90</v>
@@ -16365,13 +16696,13 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>90</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>51</v>
@@ -16388,7 +16719,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>90</v>
@@ -16417,7 +16748,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>90</v>
@@ -16509,13 +16840,13 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>51</v>
@@ -16529,13 +16860,13 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>55</v>
@@ -16549,7 +16880,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>49</v>
@@ -16578,7 +16909,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>49</v>
@@ -16587,10 +16918,10 @@
         <v>1.0</v>
       </c>
       <c r="Q52" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="R52" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="S52" s="3">
         <v>23294.0</v>
@@ -16635,7 +16966,7 @@
         <v>4.0</v>
       </c>
       <c r="AM52" s="1" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="AN52" s="3">
         <v>1.0</v>
@@ -16667,13 +16998,13 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>70</v>
@@ -16687,13 +17018,13 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>55</v>
@@ -16707,13 +17038,13 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>53</v>
@@ -16736,7 +17067,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>62</v>
@@ -16790,7 +17121,7 @@
         <v>0.0</v>
       </c>
       <c r="AM56" s="1" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="AN56" s="3">
         <v>1.0</v>
@@ -16822,7 +17153,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>69</v>
@@ -16842,7 +17173,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>69</v>
@@ -16862,7 +17193,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>69</v>
@@ -16925,7 +17256,7 @@
         <v>0.0</v>
       </c>
       <c r="AM59" s="1" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="AN59" s="3">
         <v>0.0</v>
@@ -16957,13 +17288,13 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>51</v>
@@ -16980,7 +17311,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>76</v>
@@ -17009,7 +17340,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>76</v>
@@ -17063,7 +17394,7 @@
         <v>1.0</v>
       </c>
       <c r="AM62" s="1" t="s">
-        <v>304</v>
+        <v>130</v>
       </c>
       <c r="AN62" s="3">
         <v>1.0</v>
@@ -17095,7 +17426,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>82</v>
@@ -17115,13 +17446,13 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>82</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>51</v>
@@ -17138,7 +17469,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>82</v>
@@ -17167,7 +17498,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>82</v>
@@ -17224,7 +17555,7 @@
         <v>1.0</v>
       </c>
       <c r="AM66" s="1" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="AN66" s="3">
         <v>1.0</v>
@@ -17256,7 +17587,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>86</v>
@@ -17276,7 +17607,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>86</v>
@@ -17305,7 +17636,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>86</v>
@@ -17365,7 +17696,7 @@
         <v>0.0</v>
       </c>
       <c r="AM69" s="1" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="AN69" s="3">
         <v>1.0</v>
@@ -17397,7 +17728,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>90</v>
@@ -17417,7 +17748,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>90</v>
@@ -17446,7 +17777,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>90</v>
@@ -17538,7 +17869,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>49</v>
@@ -17558,13 +17889,13 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>93</v>
@@ -17578,7 +17909,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>49</v>
@@ -17607,13 +17938,13 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>51</v>
@@ -17636,7 +17967,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>49</v>
@@ -17693,7 +18024,7 @@
         <v>0.0</v>
       </c>
       <c r="AM77" s="1" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="AN77" s="3">
         <v>2.0</v>
@@ -17725,7 +18056,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>62</v>
@@ -17737,21 +18068,21 @@
         <v>55</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="I79" s="2" t="s">
         <v>51</v>
@@ -17768,7 +18099,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>62</v>
@@ -17825,7 +18156,7 @@
         <v>3.0</v>
       </c>
       <c r="AM80" s="1" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="AN80" s="3">
         <v>0.0</v>
@@ -17857,7 +18188,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>69</v>
@@ -17877,13 +18208,13 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="I82" s="2" t="s">
         <v>53</v>
@@ -17900,7 +18231,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>69</v>
@@ -17960,7 +18291,7 @@
         <v>3.0</v>
       </c>
       <c r="AM83" s="1" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="AN83" s="3">
         <v>0.0</v>
@@ -17992,7 +18323,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>76</v>
@@ -18012,7 +18343,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>76</v>
@@ -18035,13 +18366,13 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="I86" s="2" t="s">
         <v>53</v>
@@ -18055,13 +18386,13 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="I87" s="2" t="s">
         <v>77</v>
@@ -18075,7 +18406,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>76</v>
@@ -18135,7 +18466,7 @@
         <v>2.0</v>
       </c>
       <c r="AM88" s="1" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="AN88" s="3">
         <v>0.0</v>
@@ -18167,7 +18498,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>82</v>
@@ -18187,7 +18518,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>82</v>
@@ -18210,7 +18541,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>82</v>
@@ -18273,7 +18604,7 @@
         <v>2.0</v>
       </c>
       <c r="AM91" s="1" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="AN91" s="3">
         <v>0.0</v>
@@ -18305,7 +18636,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>86</v>
@@ -18325,7 +18656,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>86</v>
@@ -18348,7 +18679,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>86</v>
@@ -18408,7 +18739,7 @@
         <v>0.0</v>
       </c>
       <c r="AM94" s="1" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="AN94" s="3">
         <v>0.0</v>
@@ -18440,7 +18771,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>90</v>
@@ -18460,7 +18791,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>90</v>
@@ -18483,7 +18814,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>90</v>
@@ -18543,7 +18874,7 @@
         <v>3.0</v>
       </c>
       <c r="AM97" s="1" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="AN97" s="3">
         <v>0.0</v>
@@ -18575,7 +18906,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>49</v>
@@ -18595,7 +18926,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>49</v>
@@ -18615,7 +18946,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>49</v>
@@ -18635,13 +18966,13 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I101" s="2" t="s">
         <v>55</v>
@@ -18664,7 +18995,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>49</v>
@@ -18724,7 +19055,7 @@
         <v>0.0</v>
       </c>
       <c r="AM102" s="1" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="AN102" s="3">
         <v>1.0</v>
@@ -18756,7 +19087,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>62</v>
@@ -18768,7 +19099,7 @@
         <v>53</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>101</v>
@@ -18776,7 +19107,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>62</v>
@@ -18785,24 +19116,24 @@
         <v>54</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>64</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I105" s="2" t="s">
         <v>53</v>
@@ -18825,7 +19156,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>62</v>
@@ -18885,7 +19216,7 @@
         <v>1.0</v>
       </c>
       <c r="AM106" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="AN106" s="3">
         <v>1.0</v>
@@ -19075,13 +19406,13 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>90</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>51</v>
@@ -19095,13 +19426,13 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>90</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>53</v>
@@ -19115,7 +19446,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>90</v>
@@ -19135,19 +19466,19 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>90</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>53</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>87</v>
@@ -19164,7 +19495,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>90</v>
@@ -19193,7 +19524,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>90</v>
@@ -19247,7 +19578,7 @@
         <v>0.0</v>
       </c>
       <c r="AM7" s="1" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="AN7" s="3">
         <v>2.0</v>
@@ -19279,7 +19610,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>49</v>
@@ -19299,13 +19630,13 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>55</v>
@@ -19319,7 +19650,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>49</v>
@@ -19348,7 +19679,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>49</v>
@@ -19360,7 +19691,7 @@
         <v>63</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="S11" s="3">
         <v>14680.0</v>
@@ -19408,7 +19739,7 @@
         <v>0.0</v>
       </c>
       <c r="AM11" s="1" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="AN11" s="3">
         <v>1.0</v>
@@ -19440,7 +19771,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>62</v>
@@ -19460,33 +19791,33 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>55</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>53</v>
@@ -19509,7 +19840,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>62</v>
@@ -19521,7 +19852,7 @@
         <v>63</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="S15" s="3">
         <v>13889.0</v>
@@ -19569,7 +19900,7 @@
         <v>0.0</v>
       </c>
       <c r="AM15" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="AN15" s="3">
         <v>1.0</v>
@@ -19601,13 +19932,13 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>51</v>
@@ -19621,13 +19952,13 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>53</v>
@@ -19636,7 +19967,7 @@
         <v>71</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="M17" s="3">
         <v>7.0</v>
@@ -19650,13 +19981,13 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>78</v>
@@ -19670,7 +20001,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>69</v>
@@ -19724,7 +20055,7 @@
         <v>0.0</v>
       </c>
       <c r="AM19" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="AN19" s="3">
         <v>1.0</v>
@@ -19756,7 +20087,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>76</v>
@@ -19776,13 +20107,13 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>53</v>
@@ -19805,7 +20136,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>76</v>
@@ -19865,7 +20196,7 @@
         <v>0.0</v>
       </c>
       <c r="AM22" s="1" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="AN22" s="3">
         <v>1.0</v>
@@ -19897,7 +20228,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>82</v>
@@ -19917,13 +20248,13 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>82</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>53</v>
@@ -19946,7 +20277,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>82</v>
@@ -20006,7 +20337,7 @@
         <v>0.0</v>
       </c>
       <c r="AM25" s="1" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="AN25" s="3">
         <v>1.0</v>
@@ -20038,13 +20369,13 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>53</v>
@@ -20058,13 +20389,13 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>86</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>51</v>
@@ -20073,12 +20404,12 @@
         <v>65</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>86</v>
@@ -20107,7 +20438,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>86</v>
@@ -20116,10 +20447,10 @@
         <v>0.0</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="S29" s="3">
         <v>9627.0</v>
@@ -20167,7 +20498,7 @@
         <v>1.0</v>
       </c>
       <c r="AM29" s="1" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="AN29" s="3">
         <v>1.0</v>
@@ -20199,13 +20530,13 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>90</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>51</v>
@@ -20219,7 +20550,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>90</v>
@@ -20234,7 +20565,7 @@
         <v>71</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="M31" s="3">
         <v>8.0</v>
@@ -20248,13 +20579,13 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>90</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>51</v>
@@ -20263,12 +20594,12 @@
         <v>65</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>90</v>
@@ -20277,10 +20608,10 @@
         <v>1.0</v>
       </c>
       <c r="Q33" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="S33" s="3">
         <v>8650.0</v>
@@ -20328,7 +20659,7 @@
         <v>0.0</v>
       </c>
       <c r="AM33" s="1" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="AN33" s="3">
         <v>1.0</v>
@@ -20360,7 +20691,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>49</v>
@@ -20380,27 +20711,27 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>55</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>49</v>
@@ -20429,7 +20760,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>49</v>
@@ -20441,7 +20772,7 @@
         <v>63</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="S37" s="3">
         <v>13913.0</v>
@@ -20489,7 +20820,7 @@
         <v>5.0</v>
       </c>
       <c r="AM37" s="1" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="AN37" s="3">
         <v>1.0</v>
@@ -20521,7 +20852,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>62</v>
@@ -20541,13 +20872,13 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>55</v>
@@ -20561,13 +20892,13 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>53</v>
@@ -20590,7 +20921,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>62</v>
@@ -20602,7 +20933,7 @@
         <v>63</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="S41" s="3">
         <v>13277.0</v>
@@ -20650,7 +20981,7 @@
         <v>0.0</v>
       </c>
       <c r="AM41" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="AN41" s="3">
         <v>1.0</v>
@@ -20682,13 +21013,13 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>51</v>
@@ -20702,13 +21033,13 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>53</v>
@@ -20717,7 +21048,7 @@
         <v>71</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="M43" s="3">
         <v>8.0</v>
@@ -20731,13 +21062,13 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>55</v>
@@ -20751,7 +21082,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>69</v>
@@ -20760,10 +21091,10 @@
         <v>0.0</v>
       </c>
       <c r="Q45" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="R45" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="S45" s="3">
         <v>12722.0</v>
@@ -20811,7 +21142,7 @@
         <v>0.0</v>
       </c>
       <c r="AM45" s="1" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="AN45" s="3">
         <v>1.0</v>
@@ -20843,7 +21174,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>76</v>
@@ -20863,13 +21194,13 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>53</v>
@@ -20892,13 +21223,13 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>55</v>
@@ -20912,7 +21243,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>76</v>
@@ -20972,7 +21303,7 @@
         <v>0.0</v>
       </c>
       <c r="AM49" s="1" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="AN49" s="3">
         <v>1.0</v>
@@ -21004,7 +21335,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>82</v>
@@ -21024,13 +21355,13 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>82</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>51</v>
@@ -21053,7 +21384,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>82</v>
@@ -21113,7 +21444,7 @@
         <v>0.0</v>
       </c>
       <c r="AM52" s="1" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="AN52" s="3">
         <v>1.0</v>
@@ -21145,13 +21476,13 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>55</v>
@@ -21165,7 +21496,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>86</v>
@@ -21184,7 +21515,7 @@
         <v>71</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="M54" s="3">
         <v>7.0</v>
@@ -21198,7 +21529,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>86</v>
@@ -21208,7 +21539,7 @@
       <c r="E55" s="1"/>
       <c r="G55" s="1"/>
       <c r="H55" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>51</v>
@@ -21222,7 +21553,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>86</v>
@@ -21280,7 +21611,7 @@
         <v>0.0</v>
       </c>
       <c r="AM56" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="AN56" s="3">
         <v>1.0</v>
@@ -21312,13 +21643,13 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>90</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>51</v>
@@ -21332,13 +21663,13 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>90</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>53</v>
@@ -21361,13 +21692,13 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>90</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>51</v>
@@ -21381,7 +21712,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>90</v>
@@ -21390,10 +21721,10 @@
         <v>0.0</v>
       </c>
       <c r="Q60" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="R60" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="S60" s="3">
         <v>18556.619999999995</v>
@@ -21441,7 +21772,7 @@
         <v>0.0</v>
       </c>
       <c r="AM60" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="AN60" s="3">
         <v>1.0</v>
@@ -21473,7 +21804,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>49</v>
@@ -21493,13 +21824,13 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>55</v>
@@ -21513,7 +21844,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>49</v>
@@ -21523,7 +21854,7 @@
       <c r="E63" s="1"/>
       <c r="G63" s="1"/>
       <c r="H63" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>53</v>
@@ -21546,7 +21877,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>49</v>
@@ -21562,7 +21893,7 @@
         <v>63</v>
       </c>
       <c r="R64" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="S64" s="3">
         <v>21825.50999999999</v>
@@ -21610,7 +21941,7 @@
         <v>0.0</v>
       </c>
       <c r="AM64" s="1" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="AN64" s="3">
         <v>1.0</v>
@@ -21642,7 +21973,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>62</v>
@@ -21662,13 +21993,13 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>55</v>
@@ -21682,13 +22013,13 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="I67" s="2" t="s">
         <v>53</v>
@@ -21711,7 +22042,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>62</v>
@@ -21765,7 +22096,7 @@
         <v>0.0</v>
       </c>
       <c r="AM68" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="AN68" s="3">
         <v>1.0</v>
@@ -21797,13 +22128,13 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>51</v>
@@ -21817,13 +22148,13 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>53</v>
@@ -21832,7 +22163,7 @@
         <v>71</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="M70" s="3">
         <v>15.0</v>
@@ -21846,7 +22177,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>69</v>
@@ -21900,7 +22231,7 @@
         <v>0.0</v>
       </c>
       <c r="AM71" s="1" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="AN71" s="3">
         <v>1.0</v>
@@ -21932,7 +22263,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>76</v>
@@ -21952,13 +22283,13 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>53</v>
@@ -21981,7 +22312,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>76</v>
@@ -22044,7 +22375,7 @@
         <v>0.0</v>
       </c>
       <c r="AM74" s="1" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="AN74" s="3">
         <v>1.0</v>
@@ -22076,7 +22407,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>82</v>
@@ -22096,13 +22427,13 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>82</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>53</v>
@@ -22125,13 +22456,13 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>82</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>55</v>
@@ -22154,7 +22485,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>82</v>
@@ -22214,7 +22545,7 @@
         <v>0.0</v>
       </c>
       <c r="AM78" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="AN78" s="3">
         <v>2.0</v>
@@ -22246,13 +22577,13 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>51</v>
@@ -22266,13 +22597,13 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>86</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="I80" s="2" t="s">
         <v>53</v>
@@ -22295,7 +22626,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>86</v>
@@ -22324,7 +22655,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>86</v>
@@ -22333,10 +22664,10 @@
         <v>0.0</v>
       </c>
       <c r="Q82" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="R82" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="S82" s="3">
         <v>12752.009999999998</v>
@@ -22381,7 +22712,7 @@
         <v>0.0</v>
       </c>
       <c r="AM82" s="1" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="AN82" s="3">
         <v>2.0</v>
@@ -22413,13 +22744,13 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>90</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>55</v>
@@ -22433,7 +22764,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>90</v>
@@ -22462,13 +22793,13 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>90</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="I85" s="2" t="s">
         <v>51</v>
@@ -22485,7 +22816,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>90</v>
@@ -22494,7 +22825,7 @@
         <v>0.0</v>
       </c>
       <c r="R86" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="S86" s="3">
         <v>17035.32</v>
@@ -22542,7 +22873,7 @@
         <v>0.0</v>
       </c>
       <c r="AM86" s="1" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="AN86" s="3">
         <v>1.0</v>
@@ -22574,7 +22905,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>49</v>
@@ -22594,13 +22925,13 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>55</v>
@@ -22614,7 +22945,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>49</v>
@@ -22643,7 +22974,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>49</v>
@@ -22655,7 +22986,7 @@
         <v>63</v>
       </c>
       <c r="R90" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="S90" s="3">
         <v>25392.46</v>
@@ -22703,7 +23034,7 @@
         <v>0.0</v>
       </c>
       <c r="AM90" s="1" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="AN90" s="3">
         <v>1.0</v>
@@ -22735,7 +23066,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>62</v>
@@ -22755,13 +23086,13 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>55</v>
@@ -22775,13 +23106,13 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="I93" s="2" t="s">
         <v>53</v>
@@ -22804,7 +23135,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>62</v>
@@ -22816,7 +23147,7 @@
         <v>63</v>
       </c>
       <c r="R94" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="S94" s="3">
         <v>23475.639999999996</v>
@@ -22864,7 +23195,7 @@
         <v>0.0</v>
       </c>
       <c r="AM94" s="1" t="s">
-        <v>372</v>
+        <v>126</v>
       </c>
       <c r="AN94" s="3">
         <v>1.0</v>
@@ -22896,13 +23227,13 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>51</v>
@@ -22916,22 +23247,22 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="I96" s="2" t="s">
         <v>53</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="M96" s="3">
         <v>8.0</v>
@@ -22945,7 +23276,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>69</v>
@@ -22954,10 +23285,10 @@
         <v>0.0</v>
       </c>
       <c r="Q97" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="R97" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="S97" s="3">
         <v>19985.18999999999</v>
@@ -23005,7 +23336,7 @@
         <v>0.0</v>
       </c>
       <c r="AM97" s="1" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AN97" s="3">
         <v>1.0</v>
@@ -23037,7 +23368,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>76</v>
@@ -23057,13 +23388,13 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="I99" s="2" t="s">
         <v>51</v>
@@ -23080,13 +23411,13 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="I100" s="2" t="s">
         <v>53</v>
@@ -23109,7 +23440,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>76</v>
@@ -23166,7 +23497,7 @@
         <v>0.0</v>
       </c>
       <c r="AM101" s="1" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="AN101" s="3">
         <v>1.0</v>
@@ -23198,13 +23529,13 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>82</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>55</v>
@@ -23218,13 +23549,13 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>82</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="I103" s="2" t="s">
         <v>51</v>
@@ -23241,7 +23572,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>82</v>
@@ -23270,7 +23601,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>82</v>
@@ -23279,7 +23610,7 @@
         <v>0.0</v>
       </c>
       <c r="R105" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="S105" s="3">
         <v>12356.0</v>
@@ -23327,7 +23658,7 @@
         <v>0.0</v>
       </c>
       <c r="AM105" s="1" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="AN105" s="3">
         <v>1.0</v>
@@ -23359,13 +23690,13 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>55</v>
@@ -23379,13 +23710,13 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>86</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="I107" s="2" t="s">
         <v>51</v>
@@ -23402,7 +23733,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>86</v>
@@ -23431,7 +23762,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>86</v>
@@ -23440,7 +23771,7 @@
         <v>0.0</v>
       </c>
       <c r="R109" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="S109" s="3">
         <v>8748.0</v>
@@ -23488,7 +23819,7 @@
         <v>0.0</v>
       </c>
       <c r="AM109" s="1" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AN109" s="3">
         <v>1.0</v>
@@ -23520,13 +23851,13 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>90</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>55</v>
@@ -23540,7 +23871,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>90</v>
@@ -23569,13 +23900,13 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>90</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="I112" s="2" t="s">
         <v>51</v>
@@ -23598,7 +23929,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>90</v>
@@ -23652,7 +23983,7 @@
         <v>0.0</v>
       </c>
       <c r="AM113" s="1" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="AN113" s="3">
         <v>2.0</v>
@@ -23684,13 +24015,13 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>55</v>
@@ -23704,13 +24035,13 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>55</v>
@@ -23724,13 +24055,13 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="I116" s="2" t="s">
         <v>53</v>
@@ -23753,13 +24084,13 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="I117" s="2" t="s">
         <v>51</v>
@@ -23776,7 +24107,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>49</v>
@@ -23785,7 +24116,7 @@
         <v>1.0</v>
       </c>
       <c r="R118" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="S118" s="3">
         <v>22791.559999999998</v>
@@ -23833,7 +24164,7 @@
         <v>0.0</v>
       </c>
       <c r="AM118" s="1" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="AN118" s="3">
         <v>1.0</v>
@@ -23865,13 +24196,13 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>51</v>
@@ -23885,13 +24216,13 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>55</v>
@@ -23905,7 +24236,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>62</v>
@@ -23934,7 +24265,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>62</v>
@@ -23988,7 +24319,7 @@
         <v>0.0</v>
       </c>
       <c r="AM122" s="1" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="AN122" s="3">
         <v>1.0</v>

--- a/admin_testy/reporty_google_testy/google_data/Pobočky/Prosek/Databaze Prosek 2026.xlsx
+++ b/admin_testy/reporty_google_testy/google_data/Pobočky/Prosek/Databaze Prosek 2026.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3253" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3459" uniqueCount="405">
   <si>
     <t>Datum</t>
   </si>
@@ -411,6 +411,75 @@
     <t>10 min 25 s</t>
   </si>
   <si>
+    <t>22.05.2026</t>
+  </si>
+  <si>
+    <t>12 min 16 s</t>
+  </si>
+  <si>
+    <t>23.05.2026</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>19:00</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>24.05.2026</t>
+  </si>
+  <si>
+    <t>Fáberová Kateřina</t>
+  </si>
+  <si>
+    <t>10 min 22 s</t>
+  </si>
+  <si>
+    <t>25.05.2026</t>
+  </si>
+  <si>
+    <t>11 min 31 s</t>
+  </si>
+  <si>
+    <t>26.05.2026</t>
+  </si>
+  <si>
+    <t>10 min 14 s</t>
+  </si>
+  <si>
+    <t>27.05.2026</t>
+  </si>
+  <si>
+    <t>11 min 44 s</t>
+  </si>
+  <si>
+    <t>28.05.2026</t>
+  </si>
+  <si>
+    <t>15 min 03 s</t>
+  </si>
+  <si>
+    <t>29.05.2026</t>
+  </si>
+  <si>
+    <t>14 min 23 s</t>
+  </si>
+  <si>
+    <t>30.05.2026</t>
+  </si>
+  <si>
+    <t>17:30</t>
+  </si>
+  <si>
+    <t>09:30</t>
+  </si>
+  <si>
+    <t>12 min 04 s</t>
+  </si>
+  <si>
     <t>01.04.2026</t>
   </si>
   <si>
@@ -429,9 +498,6 @@
     <t>Kormash Liubov</t>
   </si>
   <si>
-    <t>19:00</t>
-  </si>
-  <si>
     <t>10 min 18 s</t>
   </si>
   <si>
@@ -483,9 +549,6 @@
     <t>11.04.2026</t>
   </si>
   <si>
-    <t>18:30</t>
-  </si>
-  <si>
     <t>Pešová Hana</t>
   </si>
   <si>
@@ -507,9 +570,6 @@
     <t>12.04.2026</t>
   </si>
   <si>
-    <t>Fáberová Kateřina</t>
-  </si>
-  <si>
     <t>10 min 19 s</t>
   </si>
   <si>
@@ -528,9 +588,6 @@
     <t>15.04.2026</t>
   </si>
   <si>
-    <t>17:30</t>
-  </si>
-  <si>
     <t>07:30</t>
   </si>
   <si>
@@ -646,9 +703,6 @@
   </si>
   <si>
     <t>04.03.2026</t>
-  </si>
-  <si>
-    <t>12:00</t>
   </si>
   <si>
     <t>11 min 47 s</t>
@@ -4819,6 +4873,1461 @@
         <v>0.0</v>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J79" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="L79" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="M79" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N79" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O79" s="3">
+        <v>135.0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P80" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="Q80" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="R80" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="S80" s="3">
+        <v>14186.199999999999</v>
+      </c>
+      <c r="T80" s="3">
+        <v>8497.0</v>
+      </c>
+      <c r="U80" s="3">
+        <v>9215.0</v>
+      </c>
+      <c r="V80" s="3">
+        <v>3629.6</v>
+      </c>
+      <c r="W80" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X80" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Y80" s="3">
+        <v>4898.0</v>
+      </c>
+      <c r="AA80" s="3">
+        <v>1815.0</v>
+      </c>
+      <c r="AB80" s="3">
+        <v>43073.8</v>
+      </c>
+      <c r="AC80" s="3">
+        <v>1.999999999992724</v>
+      </c>
+      <c r="AD80" s="3">
+        <v>0.2244479185386102</v>
+      </c>
+      <c r="AE80" s="3">
+        <v>700.0</v>
+      </c>
+      <c r="AI80" s="3">
+        <v>135.0</v>
+      </c>
+      <c r="AJ80" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AK80" s="3">
+        <v>1605.0</v>
+      </c>
+      <c r="AL80" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AM80" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="AN80" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AO80" s="3">
+        <v>103.0</v>
+      </c>
+      <c r="AP80" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="AQ80" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AR80" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AS80" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="AT80" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AU80" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="AV80" s="3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="J83" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="L83" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="M83" s="3">
+        <v>11.0</v>
+      </c>
+      <c r="N83" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O83" s="3">
+        <v>495.0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="P84" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="Q84" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="R84" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="S84" s="3">
+        <v>15409.4</v>
+      </c>
+      <c r="T84" s="3">
+        <v>6675.0</v>
+      </c>
+      <c r="U84" s="3">
+        <v>6038.0</v>
+      </c>
+      <c r="V84" s="3">
+        <v>7438.6</v>
+      </c>
+      <c r="W84" s="3">
+        <v>637.0</v>
+      </c>
+      <c r="X84" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Y84" s="3">
+        <v>3964.0</v>
+      </c>
+      <c r="AA84" s="3">
+        <v>1210.0</v>
+      </c>
+      <c r="AB84" s="3">
+        <v>41868.0</v>
+      </c>
+      <c r="AC84" s="3">
+        <v>-1.0</v>
+      </c>
+      <c r="AD84" s="3">
+        <v>0.33793008162674093</v>
+      </c>
+      <c r="AI84" s="3">
+        <v>495.0</v>
+      </c>
+      <c r="AJ84" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK84" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL84" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="AM84" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="AN84" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AO84" s="3">
+        <v>103.0</v>
+      </c>
+      <c r="AP84" s="3">
+        <v>13.0</v>
+      </c>
+      <c r="AQ84" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AR84" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS84" s="3">
+        <v>0.23076923076923078</v>
+      </c>
+      <c r="AT84" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU84" s="3">
+        <v>0.7692307692307692</v>
+      </c>
+      <c r="AV84" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J87" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="L87" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="M87" s="3">
+        <v>11.0</v>
+      </c>
+      <c r="N87" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O87" s="3">
+        <v>495.0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="P88" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="Q88" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="R88" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="S88" s="3">
+        <v>10376.099999999999</v>
+      </c>
+      <c r="T88" s="3">
+        <v>5018.0</v>
+      </c>
+      <c r="U88" s="3">
+        <v>9624.0</v>
+      </c>
+      <c r="V88" s="3">
+        <v>5948.0</v>
+      </c>
+      <c r="W88" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X88" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Y88" s="3">
+        <v>3004.0</v>
+      </c>
+      <c r="AA88" s="3">
+        <v>3440.0</v>
+      </c>
+      <c r="AB88" s="3">
+        <v>37907.600000000006</v>
+      </c>
+      <c r="AC88" s="3">
+        <v>-2.500000000007276</v>
+      </c>
+      <c r="AD88" s="3">
+        <v>0.3136679661479066</v>
+      </c>
+      <c r="AI88" s="3">
+        <v>495.0</v>
+      </c>
+      <c r="AJ88" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AK88" s="3">
+        <v>331.0</v>
+      </c>
+      <c r="AL88" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="AM88" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="AN88" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AO88" s="3">
+        <v>95.0</v>
+      </c>
+      <c r="AP88" s="3">
+        <v>12.0</v>
+      </c>
+      <c r="AQ88" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AR88" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AS88" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="AT88" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AU88" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="AV88" s="3">
+        <v>0.08333333333333333</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J90" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L90" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="M90" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="N90" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O90" s="3">
+        <v>225.0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="P91" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="R91" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="S91" s="3">
+        <v>11321.999999999998</v>
+      </c>
+      <c r="T91" s="3">
+        <v>4051.0</v>
+      </c>
+      <c r="U91" s="3">
+        <v>4255.0</v>
+      </c>
+      <c r="V91" s="3">
+        <v>3532.0</v>
+      </c>
+      <c r="W91" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X91" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Y91" s="3">
+        <v>2960.0</v>
+      </c>
+      <c r="AA91" s="3">
+        <v>655.0</v>
+      </c>
+      <c r="AB91" s="3">
+        <v>27797.0</v>
+      </c>
+      <c r="AC91" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AD91" s="3">
+        <v>0.351274435138626</v>
+      </c>
+      <c r="AG91" s="3">
+        <v>119.0</v>
+      </c>
+      <c r="AH91" s="3">
+        <v>679.0</v>
+      </c>
+      <c r="AI91" s="3">
+        <v>225.0</v>
+      </c>
+      <c r="AJ91" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK91" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL91" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="AM91" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="AN91" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AO91" s="3">
+        <v>63.0</v>
+      </c>
+      <c r="AP91" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="AQ91" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AR91" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS91" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="AT91" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU91" s="3">
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="AV91" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="P95" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="Q95" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="R95" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="S95" s="3">
+        <v>10818.7</v>
+      </c>
+      <c r="T95" s="3">
+        <v>4237.0</v>
+      </c>
+      <c r="U95" s="3">
+        <v>3039.0</v>
+      </c>
+      <c r="V95" s="3">
+        <v>2923.0</v>
+      </c>
+      <c r="W95" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X95" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Y95" s="3">
+        <v>2952.0</v>
+      </c>
+      <c r="AA95" s="3">
+        <v>204.0</v>
+      </c>
+      <c r="AB95" s="3">
+        <v>24873.699999999997</v>
+      </c>
+      <c r="AC95" s="3">
+        <v>3.637978807091713E-12</v>
+      </c>
+      <c r="AD95" s="3">
+        <v>0.4335517801351784</v>
+      </c>
+      <c r="AE95" s="3">
+        <v>700.0</v>
+      </c>
+      <c r="AI95" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ95" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AK95" s="3">
+        <v>2274.0</v>
+      </c>
+      <c r="AL95" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AM95" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="AN95" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO95" s="3">
+        <v>62.0</v>
+      </c>
+      <c r="AP95" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="AQ95" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AR95" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS95" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="AT95" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AU95" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="AV95" s="3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I98" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J98" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L98" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="M98" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="N98" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O98" s="3">
+        <v>315.0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="P99" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="Q99" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="R99" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="S99" s="3">
+        <v>7615.1</v>
+      </c>
+      <c r="T99" s="3">
+        <v>4693.0</v>
+      </c>
+      <c r="U99" s="3">
+        <v>2737.0</v>
+      </c>
+      <c r="V99" s="3">
+        <v>6056.0</v>
+      </c>
+      <c r="W99" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X99" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Y99" s="3">
+        <v>2313.0</v>
+      </c>
+      <c r="AA99" s="3">
+        <v>790.0</v>
+      </c>
+      <c r="AB99" s="3">
+        <v>24520.1</v>
+      </c>
+      <c r="AC99" s="3">
+        <v>-1.0</v>
+      </c>
+      <c r="AD99" s="3">
+        <v>0.5109886156071299</v>
+      </c>
+      <c r="AI99" s="3">
+        <v>315.0</v>
+      </c>
+      <c r="AJ99" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AK99" s="3">
+        <v>215.0</v>
+      </c>
+      <c r="AL99" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AM99" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="AN99" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AO99" s="3">
+        <v>61.0</v>
+      </c>
+      <c r="AP99" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="AQ99" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AR99" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AS99" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="AT99" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AU99" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="AV99" s="3">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I103" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J103" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L103" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="M103" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N103" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O103" s="3">
+        <v>360.0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="P104" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="Q104" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="R104" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="S104" s="3">
+        <v>9831.8</v>
+      </c>
+      <c r="T104" s="3">
+        <v>4779.0</v>
+      </c>
+      <c r="U104" s="3">
+        <v>9356.0</v>
+      </c>
+      <c r="V104" s="3">
+        <v>3472.0</v>
+      </c>
+      <c r="W104" s="3">
+        <v>477.0</v>
+      </c>
+      <c r="X104" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Y104" s="3">
+        <v>1370.0</v>
+      </c>
+      <c r="AA104" s="3">
+        <v>2530.0</v>
+      </c>
+      <c r="AB104" s="3">
+        <v>32972.8</v>
+      </c>
+      <c r="AC104" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AD104" s="3">
+        <v>0.44101523053997194</v>
+      </c>
+      <c r="AH104" s="3">
+        <v>798.0</v>
+      </c>
+      <c r="AI104" s="3">
+        <v>360.0</v>
+      </c>
+      <c r="AJ104" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK104" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL104" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AM104" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="AN104" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AO104" s="3">
+        <v>78.0</v>
+      </c>
+      <c r="AP104" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="AQ104" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AR104" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS104" s="3">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="AT104" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU104" s="3">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="AV104" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H108" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I108" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J108" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="L108" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M108" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="N108" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O108" s="3">
+        <v>405.0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P109" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="Q109" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="R109" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="S109" s="3">
+        <v>12144.199999999999</v>
+      </c>
+      <c r="T109" s="3">
+        <v>8678.0</v>
+      </c>
+      <c r="U109" s="3">
+        <v>8716.0</v>
+      </c>
+      <c r="V109" s="3">
+        <v>6295.0</v>
+      </c>
+      <c r="W109" s="3">
+        <v>890.0</v>
+      </c>
+      <c r="X109" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Y109" s="3">
+        <v>3508.0</v>
+      </c>
+      <c r="AA109" s="3">
+        <v>1220.0</v>
+      </c>
+      <c r="AB109" s="3">
+        <v>41858.700000000004</v>
+      </c>
+      <c r="AC109" s="3">
+        <v>-2.500000000007276</v>
+      </c>
+      <c r="AD109" s="3">
+        <v>0.34880217382643003</v>
+      </c>
+      <c r="AI109" s="3">
+        <v>405.0</v>
+      </c>
+      <c r="AJ109" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK109" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL109" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AM109" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="AN109" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AO109" s="3">
+        <v>107.0</v>
+      </c>
+      <c r="AP109" s="3">
+        <v>14.0</v>
+      </c>
+      <c r="AQ109" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AR109" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS109" s="3">
+        <v>0.07142857142857142</v>
+      </c>
+      <c r="AT109" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU109" s="3">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="AV109" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G111" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H112" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I112" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J112" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="L112" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="M112" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="N112" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O112" s="3">
+        <v>405.0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="P113" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="Q113" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="R113" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="S113" s="3">
+        <v>13886.8</v>
+      </c>
+      <c r="T113" s="3">
+        <v>6042.0</v>
+      </c>
+      <c r="U113" s="3">
+        <v>4373.0</v>
+      </c>
+      <c r="V113" s="3">
+        <v>5403.0</v>
+      </c>
+      <c r="W113" s="3">
+        <v>443.0</v>
+      </c>
+      <c r="X113" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Y113" s="3">
+        <v>1926.0</v>
+      </c>
+      <c r="AA113" s="3">
+        <v>1258.0</v>
+      </c>
+      <c r="AB113" s="3">
+        <v>34436.8</v>
+      </c>
+      <c r="AC113" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AD113" s="3">
+        <v>0.4157159072140381</v>
+      </c>
+      <c r="AE113" s="3">
+        <v>700.0</v>
+      </c>
+      <c r="AI113" s="3">
+        <v>405.0</v>
+      </c>
+      <c r="AJ113" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AK113" s="3">
+        <v>497.0</v>
+      </c>
+      <c r="AL113" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AM113" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="AN113" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AO113" s="3">
+        <v>84.0</v>
+      </c>
+      <c r="AP113" s="3">
+        <v>12.0</v>
+      </c>
+      <c r="AQ113" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AR113" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS113" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AT113" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU113" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AV113" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -4979,7 +6488,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>86</v>
@@ -4999,7 +6508,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>86</v>
@@ -5019,7 +6528,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>86</v>
@@ -5048,7 +6557,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>86</v>
@@ -5114,7 +6623,7 @@
         <v>1.0</v>
       </c>
       <c r="AM5" s="1" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="AN5" s="3">
         <v>1.0</v>
@@ -5146,7 +6655,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>90</v>
@@ -5166,7 +6675,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>90</v>
@@ -5195,7 +6704,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>90</v>
@@ -5258,7 +6767,7 @@
         <v>0.0</v>
       </c>
       <c r="AM8" s="1" t="s">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="AN8" s="3">
         <v>1.0</v>
@@ -5290,7 +6799,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>49</v>
@@ -5310,7 +6819,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>49</v>
@@ -5320,10 +6829,10 @@
       <c r="E10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>64</v>
@@ -5337,7 +6846,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>49</v>
@@ -5404,7 +6913,7 @@
         <v>3.0</v>
       </c>
       <c r="AM11" s="1" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="AN11" s="3">
         <v>0.0</v>
@@ -5436,7 +6945,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>62</v>
@@ -5456,13 +6965,13 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>53</v>
@@ -5485,7 +6994,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>62</v>
@@ -5548,7 +7057,7 @@
         <v>2.0</v>
       </c>
       <c r="AM14" s="1" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="AN14" s="3">
         <v>1.0</v>
@@ -5580,7 +7089,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>142</v>
+        <v>164</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>69</v>
@@ -5600,13 +7109,13 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>142</v>
+        <v>164</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>53</v>
@@ -5629,7 +7138,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>142</v>
+        <v>164</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>69</v>
@@ -5689,7 +7198,7 @@
         <v>0.0</v>
       </c>
       <c r="AM17" s="1" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="AN17" s="3">
         <v>1.0</v>
@@ -5721,7 +7230,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>76</v>
@@ -5741,7 +7250,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>76</v>
@@ -5761,7 +7270,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>76</v>
@@ -5790,7 +7299,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>76</v>
@@ -5853,7 +7362,7 @@
         <v>3.0</v>
       </c>
       <c r="AM21" s="1" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="AN21" s="3">
         <v>1.0</v>
@@ -5885,7 +7394,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>82</v>
@@ -5905,7 +7414,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>82</v>
@@ -5925,7 +7434,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>82</v>
@@ -5954,7 +7463,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>82</v>
@@ -6017,7 +7526,7 @@
         <v>0.0</v>
       </c>
       <c r="AM25" s="1" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="AN25" s="3">
         <v>1.0</v>
@@ -6049,7 +7558,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>86</v>
@@ -6069,7 +7578,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>86</v>
@@ -6089,7 +7598,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>86</v>
@@ -6118,7 +7627,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>86</v>
@@ -6178,7 +7687,7 @@
         <v>1.0</v>
       </c>
       <c r="AM29" s="1" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="AN29" s="3">
         <v>1.0</v>
@@ -6210,7 +7719,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>90</v>
@@ -6230,7 +7739,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>90</v>
@@ -6250,7 +7759,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>90</v>
@@ -6279,7 +7788,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>90</v>
@@ -6339,7 +7848,7 @@
         <v>2.0</v>
       </c>
       <c r="AM33" s="1" t="s">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="AN33" s="3">
         <v>1.0</v>
@@ -6371,7 +7880,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>49</v>
@@ -6391,7 +7900,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>49</v>
@@ -6411,7 +7920,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>49</v>
@@ -6440,7 +7949,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>49</v>
@@ -6503,7 +8012,7 @@
         <v>0.0</v>
       </c>
       <c r="AM37" s="1" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="AN37" s="3">
         <v>1.0</v>
@@ -6535,7 +8044,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>62</v>
@@ -6547,7 +8056,7 @@
         <v>51</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>102</v>
@@ -6555,39 +8064,39 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>55</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>77</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>66</v>
@@ -6595,7 +8104,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>62</v>
@@ -6611,7 +8120,7 @@
         <v>50</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="S41" s="3">
         <v>17084.0</v>
@@ -6659,7 +8168,7 @@
         <v>2.0</v>
       </c>
       <c r="AM41" s="1" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="AN41" s="3">
         <v>0.0</v>
@@ -6691,13 +8200,13 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>51</v>
@@ -6711,7 +8220,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>69</v>
@@ -6731,13 +8240,13 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>55</v>
@@ -6751,7 +8260,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>69</v>
@@ -6761,7 +8270,7 @@
       <c r="E45" s="1"/>
       <c r="G45" s="1"/>
       <c r="H45" s="1" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>55</v>
@@ -6778,7 +8287,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>69</v>
@@ -6791,7 +8300,7 @@
         <v>2.0</v>
       </c>
       <c r="Q46" s="1" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="R46" s="1" t="s">
         <v>54</v>
@@ -6848,7 +8357,7 @@
         <v>1.0</v>
       </c>
       <c r="AM46" s="1" t="s">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="AN46" s="3">
         <v>0.0</v>
@@ -6880,7 +8389,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>76</v>
@@ -6900,7 +8409,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>76</v>
@@ -6920,7 +8429,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>76</v>
@@ -6949,7 +8458,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>76</v>
@@ -7009,7 +8518,7 @@
         <v>0.0</v>
       </c>
       <c r="AM50" s="1" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="AN50" s="3">
         <v>1.0</v>
@@ -7041,7 +8550,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>82</v>
@@ -7061,7 +8570,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>82</v>
@@ -7081,7 +8590,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>82</v>
@@ -7110,7 +8619,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>82</v>
@@ -7179,7 +8688,7 @@
         <v>1.0</v>
       </c>
       <c r="AM54" s="1" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="AN54" s="3">
         <v>1.0</v>
@@ -7211,7 +8720,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>86</v>
@@ -7223,15 +8732,15 @@
         <v>51</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>171</v>
+        <v>190</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>86</v>
@@ -7251,7 +8760,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>86</v>
@@ -7263,7 +8772,7 @@
         <v>51</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="L57" s="2" t="s">
         <v>102</v>
@@ -7280,22 +8789,22 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>86</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>58</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="M58" s="3">
         <v>3.0</v>
@@ -7309,7 +8818,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>86</v>
@@ -7369,7 +8878,7 @@
         <v>0.0</v>
       </c>
       <c r="AM59" s="1" t="s">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="AN59" s="3">
         <v>2.0</v>
@@ -7401,7 +8910,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>90</v>
@@ -7421,7 +8930,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>90</v>
@@ -7450,7 +8959,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>90</v>
@@ -7510,7 +9019,7 @@
         <v>1.0</v>
       </c>
       <c r="AM62" s="1" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="AN62" s="3">
         <v>1.0</v>
@@ -7542,7 +9051,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>49</v>
@@ -7562,7 +9071,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>49</v>
@@ -7582,7 +9091,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>49</v>
@@ -7592,7 +9101,7 @@
       <c r="E65" s="1"/>
       <c r="G65" s="1"/>
       <c r="H65" s="1" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>53</v>
@@ -7615,7 +9124,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>49</v>
@@ -7682,7 +9191,7 @@
         <v>0.0</v>
       </c>
       <c r="AM66" s="1" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="AN66" s="3">
         <v>1.0</v>
@@ -7714,7 +9223,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>62</v>
@@ -7734,7 +9243,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>62</v>
@@ -7754,7 +9263,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>62</v>
@@ -7766,15 +9275,15 @@
         <v>55</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>62</v>
@@ -7803,7 +9312,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>62</v>
@@ -7863,7 +9372,7 @@
         <v>2.0</v>
       </c>
       <c r="AM71" s="1" t="s">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="AN71" s="3">
         <v>1.0</v>
@@ -7895,7 +9404,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>69</v>
@@ -7915,13 +9424,13 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>55</v>
@@ -7935,7 +9444,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>69</v>
@@ -7998,7 +9507,7 @@
         <v>2.0</v>
       </c>
       <c r="AM74" s="1" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="AN74" s="3">
         <v>0.0</v>
@@ -8030,7 +9539,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>76</v>
@@ -8042,15 +9551,15 @@
         <v>51</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>171</v>
+        <v>190</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>76</v>
@@ -8070,7 +9579,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>76</v>
@@ -8099,7 +9608,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>76</v>
@@ -8162,7 +9671,7 @@
         <v>0.0</v>
       </c>
       <c r="AM78" s="1" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="AN78" s="3">
         <v>1.0</v>
@@ -8194,7 +9703,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>82</v>
@@ -8214,7 +9723,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>82</v>
@@ -8243,7 +9752,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>82</v>
@@ -8306,7 +9815,7 @@
         <v>1.0</v>
       </c>
       <c r="AM81" s="1" t="s">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c r="AN81" s="3">
         <v>1.0</v>
@@ -8338,7 +9847,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>86</v>
@@ -8358,7 +9867,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>86</v>
@@ -8378,7 +9887,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>86</v>
@@ -8407,7 +9916,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>86</v>
@@ -8467,7 +9976,7 @@
         <v>1.0</v>
       </c>
       <c r="AM85" s="1" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="AN85" s="3">
         <v>1.0</v>
@@ -8499,7 +10008,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>187</v>
+        <v>206</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>90</v>
@@ -8519,7 +10028,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>187</v>
+        <v>206</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>90</v>
@@ -8548,7 +10057,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>187</v>
+        <v>206</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>90</v>
@@ -8608,7 +10117,7 @@
         <v>1.0</v>
       </c>
       <c r="AM88" s="1" t="s">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="AN88" s="3">
         <v>1.0</v>
@@ -8640,7 +10149,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>49</v>
@@ -8660,13 +10169,13 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="I90" s="2" t="s">
         <v>53</v>
@@ -8689,7 +10198,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>49</v>
@@ -8749,7 +10258,7 @@
         <v>2.0</v>
       </c>
       <c r="AM91" s="1" t="s">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="AN91" s="3">
         <v>1.0</v>
@@ -8781,7 +10290,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>62</v>
@@ -8801,7 +10310,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>62</v>
@@ -8830,13 +10339,13 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="I94" s="2" t="s">
         <v>55</v>
@@ -8859,7 +10368,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>62</v>
@@ -8919,7 +10428,7 @@
         <v>0.0</v>
       </c>
       <c r="AM95" s="1" t="s">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="AN95" s="3">
         <v>2.0</v>
@@ -8951,7 +10460,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>193</v>
+        <v>212</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>69</v>
@@ -8971,7 +10480,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>193</v>
+        <v>212</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>69</v>
@@ -9031,7 +10540,7 @@
         <v>0.0</v>
       </c>
       <c r="AM97" s="1" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="AN97" s="3">
         <v>0.0</v>
@@ -9063,7 +10572,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>76</v>
@@ -9083,7 +10592,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>76</v>
@@ -9106,7 +10615,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>76</v>
@@ -9166,7 +10675,7 @@
         <v>0.0</v>
       </c>
       <c r="AM100" s="1" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="AN100" s="3">
         <v>0.0</v>
@@ -9198,7 +10707,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>82</v>
@@ -9218,7 +10727,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>82</v>
@@ -9238,7 +10747,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>82</v>
@@ -9330,7 +10839,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>86</v>
@@ -9350,7 +10859,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>86</v>
@@ -9359,13 +10868,13 @@
         <v>57</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="J105" s="2" t="s">
         <v>58</v>
       </c>
       <c r="L105" s="2" t="s">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="M105" s="3">
         <v>8.0</v>
@@ -9373,7 +10882,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>86</v>
@@ -9439,7 +10948,7 @@
         <v>2.0</v>
       </c>
       <c r="AM106" s="1" t="s">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="AN106" s="3">
         <v>0.0</v>
@@ -9471,7 +10980,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>90</v>
@@ -9491,7 +11000,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>90</v>
@@ -9506,7 +11015,7 @@
         <v>101</v>
       </c>
       <c r="L108" s="2" t="s">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="M108" s="3">
         <v>9.0</v>
@@ -9514,7 +11023,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>90</v>
@@ -9574,7 +11083,7 @@
         <v>2.0</v>
       </c>
       <c r="AM109" s="1" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="AN109" s="3">
         <v>0.0</v>
@@ -9764,7 +11273,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>69</v>
@@ -9784,7 +11293,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>69</v>
@@ -9804,13 +11313,13 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>53</v>
@@ -9833,7 +11342,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>69</v>
@@ -9896,7 +11405,7 @@
         <v>5.0</v>
       </c>
       <c r="AM5" s="1" t="s">
-        <v>204</v>
+        <v>223</v>
       </c>
       <c r="AN5" s="3">
         <v>1.0</v>
@@ -9928,7 +11437,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>76</v>
@@ -9948,7 +11457,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>76</v>
@@ -9968,7 +11477,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>76</v>
@@ -9988,7 +11497,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>76</v>
@@ -10017,7 +11526,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>76</v>
@@ -10077,7 +11586,7 @@
         <v>0.0</v>
       </c>
       <c r="AM10" s="1" t="s">
-        <v>206</v>
+        <v>225</v>
       </c>
       <c r="AN10" s="3">
         <v>1.0</v>
@@ -10109,7 +11618,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>82</v>
@@ -10129,13 +11638,13 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>82</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>53</v>
@@ -10158,7 +11667,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>82</v>
@@ -10221,7 +11730,7 @@
         <v>3.0</v>
       </c>
       <c r="AM13" s="1" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="AN13" s="3">
         <v>1.0</v>
@@ -10253,7 +11762,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>86</v>
@@ -10273,7 +11782,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>86</v>
@@ -10282,10 +11791,10 @@
         <v>50</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>210</v>
+        <v>136</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>70</v>
@@ -10293,7 +11802,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>86</v>
@@ -10313,7 +11822,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>86</v>
@@ -10336,7 +11845,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>86</v>
@@ -10399,7 +11908,7 @@
         <v>0.0</v>
       </c>
       <c r="AM18" s="1" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="AN18" s="3">
         <v>0.0</v>
@@ -10431,7 +11940,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>90</v>
@@ -10451,7 +11960,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>90</v>
@@ -10471,7 +11980,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>90</v>
@@ -10494,7 +12003,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>90</v>
@@ -10560,7 +12069,7 @@
         <v>2.0</v>
       </c>
       <c r="AM22" s="1" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="AN22" s="3">
         <v>0.0</v>
@@ -10592,7 +12101,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>49</v>
@@ -10612,7 +12121,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>49</v>
@@ -10622,7 +12131,7 @@
       <c r="E24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1" t="s">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>51</v>
@@ -10645,7 +12154,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>49</v>
@@ -10709,7 +12218,7 @@
         <v>3.0</v>
       </c>
       <c r="AM25" s="1" t="s">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="AN25" s="3">
         <v>1.0</v>
@@ -10741,7 +12250,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>62</v>
@@ -10756,12 +12265,12 @@
         <v>65</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>210</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>62</v>
@@ -10776,12 +12285,12 @@
         <v>64</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>210</v>
+        <v>136</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>62</v>
@@ -10791,7 +12300,7 @@
       <c r="E28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>53</v>
@@ -10814,7 +12323,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>62</v>
@@ -10878,7 +12387,7 @@
         <v>7.0</v>
       </c>
       <c r="AM29" s="1" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="AN29" s="3">
         <v>1.0</v>
@@ -10910,7 +12419,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>69</v>
@@ -10930,7 +12439,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>69</v>
@@ -10940,7 +12449,7 @@
       <c r="E31" s="1"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1" t="s">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>53</v>
@@ -10963,7 +12472,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>69</v>
@@ -10979,7 +12488,7 @@
         <v>50</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="S32" s="3">
         <v>12040.0</v>
@@ -11030,7 +12539,7 @@
         <v>9.0</v>
       </c>
       <c r="AM32" s="1" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="AN32" s="3">
         <v>1.0</v>
@@ -11062,7 +12571,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>76</v>
@@ -11082,7 +12591,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>76</v>
@@ -11111,7 +12620,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>76</v>
@@ -11171,7 +12680,7 @@
         <v>0.0</v>
       </c>
       <c r="AM35" s="1" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="AN35" s="3">
         <v>1.0</v>
@@ -11203,7 +12712,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>82</v>
@@ -11223,7 +12732,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>82</v>
@@ -11252,7 +12761,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>82</v>
@@ -11312,7 +12821,7 @@
         <v>0.0</v>
       </c>
       <c r="AM38" s="1" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="AN38" s="3">
         <v>1.0</v>
@@ -11344,7 +12853,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>86</v>
@@ -11364,7 +12873,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>86</v>
@@ -11384,13 +12893,13 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>86</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>78</v>
@@ -11404,13 +12913,13 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>86</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>51</v>
@@ -11424,7 +12933,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>86</v>
@@ -11453,7 +12962,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>86</v>
@@ -11513,7 +13022,7 @@
         <v>1.0</v>
       </c>
       <c r="AM44" s="1" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="AN44" s="3">
         <v>1.0</v>
@@ -11545,7 +13054,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>90</v>
@@ -11565,7 +13074,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>90</v>
@@ -11585,13 +13094,13 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>90</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>55</v>
@@ -11605,7 +13114,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>90</v>
@@ -11615,7 +13124,7 @@
       <c r="E48" s="1"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>53</v>
@@ -11629,7 +13138,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>90</v>
@@ -11662,7 +13171,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>90</v>
@@ -11729,7 +13238,7 @@
         <v>1.0</v>
       </c>
       <c r="AM50" s="1" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="AN50" s="3">
         <v>1.0</v>
@@ -11761,7 +13270,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>49</v>
@@ -11773,7 +13282,7 @@
         <v>51</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>128</v>
@@ -11781,7 +13290,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>49</v>
@@ -11801,13 +13310,13 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>53</v>
@@ -11824,7 +13333,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>49</v>
@@ -11887,7 +13396,7 @@
         <v>3.0</v>
       </c>
       <c r="AM54" s="1" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="AN54" s="3">
         <v>0.0</v>
@@ -11919,7 +13428,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>62</v>
@@ -11939,7 +13448,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>62</v>
@@ -11951,30 +13460,30 @@
         <v>55</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>53</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="M57" s="3">
         <v>13.0</v>
@@ -11982,7 +13491,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>62</v>
@@ -12045,7 +13554,7 @@
         <v>5.0</v>
       </c>
       <c r="AM58" s="1" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="AN58" s="3">
         <v>0.0</v>
@@ -12077,7 +13586,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>69</v>
@@ -12097,13 +13606,13 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>53</v>
@@ -12120,7 +13629,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>69</v>
@@ -12180,7 +13689,7 @@
         <v>6.0</v>
       </c>
       <c r="AM61" s="1" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="AN61" s="3">
         <v>0.0</v>
@@ -12212,7 +13721,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>76</v>
@@ -12232,7 +13741,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>76</v>
@@ -12252,7 +13761,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>76</v>
@@ -12264,10 +13773,10 @@
         <v>53</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>210</v>
+        <v>136</v>
       </c>
       <c r="M64" s="3">
         <v>6.0</v>
@@ -12281,7 +13790,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>76</v>
@@ -12341,7 +13850,7 @@
         <v>2.0</v>
       </c>
       <c r="AM65" s="1" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="AN65" s="3">
         <v>1.0</v>
@@ -12373,7 +13882,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>82</v>
@@ -12393,7 +13902,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>82</v>
@@ -12422,7 +13931,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>82</v>
@@ -12482,7 +13991,7 @@
         <v>0.0</v>
       </c>
       <c r="AM68" s="1" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="AN68" s="3">
         <v>1.0</v>
@@ -12514,7 +14023,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>86</v>
@@ -12534,7 +14043,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>86</v>
@@ -12563,7 +14072,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>86</v>
@@ -12623,7 +14132,7 @@
         <v>0.0</v>
       </c>
       <c r="AM71" s="1" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="AN71" s="3">
         <v>1.0</v>
@@ -12655,7 +14164,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>90</v>
@@ -12675,7 +14184,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>90</v>
@@ -12695,13 +14204,13 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>90</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>77</v>
@@ -12715,7 +14224,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>90</v>
@@ -12744,7 +14253,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>90</v>
@@ -12807,7 +14316,7 @@
         <v>0.0</v>
       </c>
       <c r="AM76" s="1" t="s">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="AN76" s="3">
         <v>1.0</v>
@@ -12839,7 +14348,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>49</v>
@@ -12859,13 +14368,13 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>55</v>
@@ -12879,7 +14388,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>49</v>
@@ -12939,7 +14448,7 @@
         <v>4.0</v>
       </c>
       <c r="AM79" s="1" t="s">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="AN79" s="3">
         <v>0.0</v>
@@ -12971,7 +14480,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>62</v>
@@ -12983,15 +14492,15 @@
         <v>51</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>171</v>
+        <v>190</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>62</v>
@@ -13011,7 +14520,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>62</v>
@@ -13023,15 +14532,15 @@
         <v>78</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>62</v>
@@ -13091,7 +14600,7 @@
         <v>5.0</v>
       </c>
       <c r="AM83" s="1" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="AN83" s="3">
         <v>0.0</v>
@@ -13123,7 +14632,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>69</v>
@@ -13143,7 +14652,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>69</v>
@@ -13203,7 +14712,7 @@
         <v>2.0</v>
       </c>
       <c r="AM85" s="1" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="AN85" s="3">
         <v>0.0</v>
@@ -13235,7 +14744,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>76</v>
@@ -13255,7 +14764,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>76</v>
@@ -13275,7 +14784,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>76</v>
@@ -13304,7 +14813,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>76</v>
@@ -13364,7 +14873,7 @@
         <v>0.0</v>
       </c>
       <c r="AM89" s="1" t="s">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="AN89" s="3">
         <v>1.0</v>
@@ -13396,7 +14905,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>82</v>
@@ -13408,15 +14917,15 @@
         <v>51</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>171</v>
+        <v>190</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>82</v>
@@ -13436,7 +14945,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>82</v>
@@ -13465,7 +14974,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>82</v>
@@ -13528,7 +15037,7 @@
         <v>0.0</v>
       </c>
       <c r="AM93" s="1" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="AN93" s="3">
         <v>1.0</v>
@@ -13560,7 +15069,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>86</v>
@@ -13572,15 +15081,15 @@
         <v>51</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>171</v>
+        <v>190</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>86</v>
@@ -13600,7 +15109,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>86</v>
@@ -13629,7 +15138,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>86</v>
@@ -13692,7 +15201,7 @@
         <v>1.0</v>
       </c>
       <c r="AM97" s="1" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="AN97" s="3">
         <v>1.0</v>
@@ -13724,7 +15233,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>90</v>
@@ -13744,7 +15253,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>90</v>
@@ -13773,7 +15282,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>90</v>
@@ -13836,7 +15345,7 @@
         <v>2.0</v>
       </c>
       <c r="AM100" s="1" t="s">
-        <v>262</v>
+        <v>280</v>
       </c>
       <c r="AN100" s="3">
         <v>1.0</v>
@@ -13868,7 +15377,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>263</v>
+        <v>281</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>49</v>
@@ -13888,16 +15397,16 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>263</v>
+        <v>281</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>65</v>
@@ -13908,7 +15417,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>263</v>
+        <v>281</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>49</v>
@@ -13968,7 +15477,7 @@
         <v>4.0</v>
       </c>
       <c r="AM103" s="1" t="s">
-        <v>264</v>
+        <v>282</v>
       </c>
       <c r="AN103" s="3">
         <v>0.0</v>
@@ -14000,7 +15509,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>62</v>
@@ -14012,15 +15521,15 @@
         <v>51</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>266</v>
+        <v>284</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>267</v>
+        <v>285</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>62</v>
@@ -14040,36 +15549,36 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>77</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>268</v>
+        <v>286</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>269</v>
+        <v>287</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>210</v>
+        <v>136</v>
       </c>
       <c r="J107" s="2" t="s">
         <v>64</v>
@@ -14089,13 +15598,13 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="I108" s="2" t="s">
         <v>53</v>
@@ -14112,7 +15621,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>62</v>
@@ -14175,7 +15684,7 @@
         <v>1.0</v>
       </c>
       <c r="AM109" s="1" t="s">
-        <v>271</v>
+        <v>289</v>
       </c>
       <c r="AN109" s="3">
         <v>1.0</v>
@@ -14207,7 +15716,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>69</v>
@@ -14227,13 +15736,13 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>55</v>
@@ -14247,7 +15756,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>69</v>
@@ -14267,7 +15776,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>69</v>
@@ -14331,7 +15840,7 @@
         <v>3.0</v>
       </c>
       <c r="AM113" s="1" t="s">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="AN113" s="3">
         <v>0.0</v>
@@ -14363,7 +15872,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>76</v>
@@ -14383,7 +15892,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>76</v>
@@ -14403,7 +15912,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>76</v>
@@ -14423,7 +15932,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>76</v>
@@ -14452,7 +15961,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>76</v>
@@ -14515,7 +16024,7 @@
         <v>0.0</v>
       </c>
       <c r="AM118" s="1" t="s">
-        <v>275</v>
+        <v>293</v>
       </c>
       <c r="AN118" s="3">
         <v>1.0</v>
@@ -14547,7 +16056,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>82</v>
@@ -14567,7 +16076,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>82</v>
@@ -14587,7 +16096,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>82</v>
@@ -14610,7 +16119,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>82</v>
@@ -14639,7 +16148,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>82</v>
@@ -14705,7 +16214,7 @@
         <v>0.0</v>
       </c>
       <c r="AM123" s="1" t="s">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="AN123" s="3">
         <v>1.0</v>
@@ -14895,13 +16404,13 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>51</v>
@@ -14915,13 +16424,13 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>53</v>
@@ -14944,7 +16453,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>69</v>
@@ -14998,7 +16507,7 @@
         <v>0.0</v>
       </c>
       <c r="AM4" s="1" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="AN4" s="3">
         <v>1.0</v>
@@ -15030,7 +16539,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>76</v>
@@ -15050,7 +16559,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>76</v>
@@ -15079,7 +16588,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>76</v>
@@ -15139,7 +16648,7 @@
         <v>1.0</v>
       </c>
       <c r="AM7" s="1" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="AN7" s="3">
         <v>1.0</v>
@@ -15171,7 +16680,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>82</v>
@@ -15191,13 +16700,13 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>82</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>53</v>
@@ -15220,13 +16729,13 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>82</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>51</v>
@@ -15243,7 +16752,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>82</v>
@@ -15300,7 +16809,7 @@
         <v>0.0</v>
       </c>
       <c r="AM11" s="1" t="s">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="AN11" s="3">
         <v>1.0</v>
@@ -15332,13 +16841,13 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>51</v>
@@ -15352,13 +16861,13 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>86</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>53</v>
@@ -15381,7 +16890,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>86</v>
@@ -15390,10 +16899,10 @@
         <v>0.0</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="S14" s="3">
         <v>15925.179999999997</v>
@@ -15441,7 +16950,7 @@
         <v>0.0</v>
       </c>
       <c r="AM14" s="1" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="AN14" s="3">
         <v>1.0</v>
@@ -15473,7 +16982,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>90</v>
@@ -15493,13 +17002,13 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>90</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>51</v>
@@ -15516,7 +17025,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>90</v>
@@ -15545,7 +17054,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>90</v>
@@ -15602,7 +17111,7 @@
         <v>0.0</v>
       </c>
       <c r="AM18" s="1" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="AN18" s="3">
         <v>1.0</v>
@@ -15634,13 +17143,13 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>51</v>
@@ -15654,13 +17163,13 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>55</v>
@@ -15674,7 +17183,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>49</v>
@@ -15703,7 +17212,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>49</v>
@@ -15757,7 +17266,7 @@
         <v>0.0</v>
       </c>
       <c r="AM22" s="1" t="s">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="AN22" s="3">
         <v>1.0</v>
@@ -15789,13 +17298,13 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>51</v>
@@ -15809,22 +17318,22 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>293</v>
+        <v>311</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>53</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>210</v>
+        <v>136</v>
       </c>
       <c r="M24" s="3">
         <v>10.0</v>
@@ -15838,13 +17347,13 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>55</v>
@@ -15861,13 +17370,13 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>53</v>
@@ -15890,7 +17399,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>62</v>
@@ -15944,7 +17453,7 @@
         <v>1.0</v>
       </c>
       <c r="AM27" s="1" t="s">
-        <v>294</v>
+        <v>312</v>
       </c>
       <c r="AN27" s="3">
         <v>2.0</v>
@@ -15976,13 +17485,13 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>51</v>
@@ -15996,13 +17505,13 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>293</v>
+        <v>311</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>93</v>
@@ -16025,13 +17534,13 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>53</v>
@@ -16054,13 +17563,13 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>93</v>
@@ -16083,7 +17592,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>69</v>
@@ -16092,10 +17601,10 @@
         <v>0.0</v>
       </c>
       <c r="Q32" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="S32" s="3">
         <v>9567.0</v>
@@ -16143,7 +17652,7 @@
         <v>0.0</v>
       </c>
       <c r="AM32" s="1" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
       <c r="AN32" s="3">
         <v>3.0</v>
@@ -16175,13 +17684,13 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>297</v>
+        <v>315</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>76</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>51</v>
@@ -16195,7 +17704,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>297</v>
+        <v>315</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>76</v>
@@ -16215,13 +17724,13 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>297</v>
+        <v>315</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>53</v>
@@ -16244,13 +17753,13 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>297</v>
+        <v>315</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>293</v>
+        <v>311</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>93</v>
@@ -16273,7 +17782,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>297</v>
+        <v>315</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>76</v>
@@ -16282,7 +17791,7 @@
         <v>1.0</v>
       </c>
       <c r="Q37" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="R37" s="1" t="s">
         <v>63</v>
@@ -16333,7 +17842,7 @@
         <v>0.0</v>
       </c>
       <c r="AM37" s="1" t="s">
-        <v>298</v>
+        <v>316</v>
       </c>
       <c r="AN37" s="3">
         <v>2.0</v>
@@ -16365,13 +17874,13 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>82</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>51</v>
@@ -16385,13 +17894,13 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>82</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>53</v>
@@ -16414,13 +17923,13 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>82</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>293</v>
+        <v>311</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>55</v>
@@ -16443,7 +17952,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>82</v>
@@ -16452,10 +17961,10 @@
         <v>0.0</v>
       </c>
       <c r="Q41" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="S41" s="3">
         <v>6459.0</v>
@@ -16503,7 +18012,7 @@
         <v>0.0</v>
       </c>
       <c r="AM41" s="1" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="AN41" s="3">
         <v>2.0</v>
@@ -16535,7 +18044,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>300</v>
+        <v>318</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>86</v>
@@ -16555,7 +18064,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>300</v>
+        <v>318</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>86</v>
@@ -16584,7 +18093,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>300</v>
+        <v>318</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>86</v>
@@ -16644,7 +18153,7 @@
         <v>0.0</v>
       </c>
       <c r="AM44" s="1" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="AN44" s="3">
         <v>1.0</v>
@@ -16676,7 +18185,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>90</v>
@@ -16696,13 +18205,13 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>90</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>51</v>
@@ -16719,7 +18228,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>90</v>
@@ -16748,7 +18257,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>90</v>
@@ -16840,13 +18349,13 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>51</v>
@@ -16860,13 +18369,13 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>55</v>
@@ -16880,7 +18389,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>49</v>
@@ -16909,7 +18418,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>49</v>
@@ -16918,10 +18427,10 @@
         <v>1.0</v>
       </c>
       <c r="Q52" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="R52" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="S52" s="3">
         <v>23294.0</v>
@@ -16966,7 +18475,7 @@
         <v>4.0</v>
       </c>
       <c r="AM52" s="1" t="s">
-        <v>304</v>
+        <v>322</v>
       </c>
       <c r="AN52" s="3">
         <v>1.0</v>
@@ -16998,13 +18507,13 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>70</v>
@@ -17018,13 +18527,13 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>55</v>
@@ -17038,13 +18547,13 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>53</v>
@@ -17067,7 +18576,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>62</v>
@@ -17121,7 +18630,7 @@
         <v>0.0</v>
       </c>
       <c r="AM56" s="1" t="s">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="AN56" s="3">
         <v>1.0</v>
@@ -17153,7 +18662,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>69</v>
@@ -17173,7 +18682,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>69</v>
@@ -17193,7 +18702,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>69</v>
@@ -17256,7 +18765,7 @@
         <v>0.0</v>
       </c>
       <c r="AM59" s="1" t="s">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="AN59" s="3">
         <v>0.0</v>
@@ -17288,13 +18797,13 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>51</v>
@@ -17311,7 +18820,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>76</v>
@@ -17340,7 +18849,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>76</v>
@@ -17426,7 +18935,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>82</v>
@@ -17446,13 +18955,13 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>82</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>51</v>
@@ -17469,7 +18978,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>82</v>
@@ -17498,7 +19007,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>82</v>
@@ -17555,7 +19064,7 @@
         <v>1.0</v>
       </c>
       <c r="AM66" s="1" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="AN66" s="3">
         <v>1.0</v>
@@ -17587,7 +19096,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>311</v>
+        <v>329</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>86</v>
@@ -17607,7 +19116,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>311</v>
+        <v>329</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>86</v>
@@ -17636,7 +19145,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>311</v>
+        <v>329</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>86</v>
@@ -17696,7 +19205,7 @@
         <v>0.0</v>
       </c>
       <c r="AM69" s="1" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="AN69" s="3">
         <v>1.0</v>
@@ -17728,7 +19237,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>90</v>
@@ -17748,7 +19257,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>90</v>
@@ -17777,7 +19286,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>90</v>
@@ -17869,7 +19378,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>49</v>
@@ -17889,13 +19398,13 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>93</v>
@@ -17909,7 +19418,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>49</v>
@@ -17938,13 +19447,13 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>51</v>
@@ -17967,7 +19476,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>49</v>
@@ -18024,7 +19533,7 @@
         <v>0.0</v>
       </c>
       <c r="AM77" s="1" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="AN77" s="3">
         <v>2.0</v>
@@ -18056,7 +19565,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>62</v>
@@ -18068,21 +19577,21 @@
         <v>55</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="I79" s="2" t="s">
         <v>51</v>
@@ -18099,7 +19608,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>62</v>
@@ -18156,7 +19665,7 @@
         <v>3.0</v>
       </c>
       <c r="AM80" s="1" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="AN80" s="3">
         <v>0.0</v>
@@ -18188,7 +19697,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>69</v>
@@ -18208,13 +19717,13 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="I82" s="2" t="s">
         <v>53</v>
@@ -18231,7 +19740,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>69</v>
@@ -18291,7 +19800,7 @@
         <v>3.0</v>
       </c>
       <c r="AM83" s="1" t="s">
-        <v>318</v>
+        <v>336</v>
       </c>
       <c r="AN83" s="3">
         <v>0.0</v>
@@ -18323,7 +19832,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>319</v>
+        <v>337</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>76</v>
@@ -18343,7 +19852,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>319</v>
+        <v>337</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>76</v>
@@ -18366,13 +19875,13 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>319</v>
+        <v>337</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="I86" s="2" t="s">
         <v>53</v>
@@ -18386,13 +19895,13 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>319</v>
+        <v>337</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="I87" s="2" t="s">
         <v>77</v>
@@ -18406,7 +19915,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>319</v>
+        <v>337</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>76</v>
@@ -18466,7 +19975,7 @@
         <v>2.0</v>
       </c>
       <c r="AM88" s="1" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="AN88" s="3">
         <v>0.0</v>
@@ -18498,7 +20007,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>82</v>
@@ -18518,7 +20027,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>82</v>
@@ -18541,7 +20050,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>82</v>
@@ -18604,7 +20113,7 @@
         <v>2.0</v>
       </c>
       <c r="AM91" s="1" t="s">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="AN91" s="3">
         <v>0.0</v>
@@ -18636,7 +20145,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>325</v>
+        <v>343</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>86</v>
@@ -18656,7 +20165,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>325</v>
+        <v>343</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>86</v>
@@ -18679,7 +20188,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>325</v>
+        <v>343</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>86</v>
@@ -18739,7 +20248,7 @@
         <v>0.0</v>
       </c>
       <c r="AM94" s="1" t="s">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="AN94" s="3">
         <v>0.0</v>
@@ -18771,7 +20280,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>326</v>
+        <v>344</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>90</v>
@@ -18791,7 +20300,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>326</v>
+        <v>344</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>90</v>
@@ -18814,7 +20323,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>326</v>
+        <v>344</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>90</v>
@@ -18874,7 +20383,7 @@
         <v>3.0</v>
       </c>
       <c r="AM97" s="1" t="s">
-        <v>327</v>
+        <v>345</v>
       </c>
       <c r="AN97" s="3">
         <v>0.0</v>
@@ -18906,7 +20415,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>328</v>
+        <v>346</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>49</v>
@@ -18926,7 +20435,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>328</v>
+        <v>346</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>49</v>
@@ -18946,7 +20455,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>328</v>
+        <v>346</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>49</v>
@@ -18966,13 +20475,13 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>328</v>
+        <v>346</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>293</v>
+        <v>311</v>
       </c>
       <c r="I101" s="2" t="s">
         <v>55</v>
@@ -18995,7 +20504,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>328</v>
+        <v>346</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>49</v>
@@ -19055,7 +20564,7 @@
         <v>0.0</v>
       </c>
       <c r="AM102" s="1" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="AN102" s="3">
         <v>1.0</v>
@@ -19087,7 +20596,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>329</v>
+        <v>347</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>62</v>
@@ -19099,7 +20608,7 @@
         <v>53</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>330</v>
+        <v>348</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>101</v>
@@ -19107,7 +20616,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>329</v>
+        <v>347</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>62</v>
@@ -19116,24 +20625,24 @@
         <v>54</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>330</v>
+        <v>348</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>64</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>198</v>
+        <v>217</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>329</v>
+        <v>347</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>293</v>
+        <v>311</v>
       </c>
       <c r="I105" s="2" t="s">
         <v>53</v>
@@ -19156,7 +20665,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>329</v>
+        <v>347</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>62</v>
@@ -19216,7 +20725,7 @@
         <v>1.0</v>
       </c>
       <c r="AM106" s="1" t="s">
-        <v>331</v>
+        <v>349</v>
       </c>
       <c r="AN106" s="3">
         <v>1.0</v>
@@ -19406,13 +20915,13 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>90</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>51</v>
@@ -19426,13 +20935,13 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>90</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>53</v>
@@ -19446,7 +20955,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>90</v>
@@ -19466,19 +20975,19 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>90</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>53</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>87</v>
@@ -19495,7 +21004,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>90</v>
@@ -19524,7 +21033,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>90</v>
@@ -19578,7 +21087,7 @@
         <v>0.0</v>
       </c>
       <c r="AM7" s="1" t="s">
-        <v>333</v>
+        <v>351</v>
       </c>
       <c r="AN7" s="3">
         <v>2.0</v>
@@ -19610,7 +21119,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>334</v>
+        <v>352</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>49</v>
@@ -19630,13 +21139,13 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>334</v>
+        <v>352</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>55</v>
@@ -19650,7 +21159,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>334</v>
+        <v>352</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>49</v>
@@ -19679,7 +21188,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>334</v>
+        <v>352</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>49</v>
@@ -19691,7 +21200,7 @@
         <v>63</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="S11" s="3">
         <v>14680.0</v>
@@ -19739,7 +21248,7 @@
         <v>0.0</v>
       </c>
       <c r="AM11" s="1" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="AN11" s="3">
         <v>1.0</v>
@@ -19771,7 +21280,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>62</v>
@@ -19791,33 +21300,33 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>55</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>53</v>
@@ -19840,7 +21349,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>62</v>
@@ -19852,7 +21361,7 @@
         <v>63</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="S15" s="3">
         <v>13889.0</v>
@@ -19900,7 +21409,7 @@
         <v>0.0</v>
       </c>
       <c r="AM15" s="1" t="s">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="AN15" s="3">
         <v>1.0</v>
@@ -19932,13 +21441,13 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>337</v>
+        <v>355</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>51</v>
@@ -19952,13 +21461,13 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>337</v>
+        <v>355</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>53</v>
@@ -19981,13 +21490,13 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>337</v>
+        <v>355</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>78</v>
@@ -20001,7 +21510,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>337</v>
+        <v>355</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>69</v>
@@ -20055,7 +21564,7 @@
         <v>0.0</v>
       </c>
       <c r="AM19" s="1" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="AN19" s="3">
         <v>1.0</v>
@@ -20087,7 +21596,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>339</v>
+        <v>357</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>76</v>
@@ -20107,13 +21616,13 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>339</v>
+        <v>357</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>53</v>
@@ -20136,7 +21645,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>339</v>
+        <v>357</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>76</v>
@@ -20196,7 +21705,7 @@
         <v>0.0</v>
       </c>
       <c r="AM22" s="1" t="s">
-        <v>340</v>
+        <v>358</v>
       </c>
       <c r="AN22" s="3">
         <v>1.0</v>
@@ -20228,7 +21737,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>341</v>
+        <v>359</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>82</v>
@@ -20248,13 +21757,13 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>341</v>
+        <v>359</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>82</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>53</v>
@@ -20277,7 +21786,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>341</v>
+        <v>359</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>82</v>
@@ -20337,7 +21846,7 @@
         <v>0.0</v>
       </c>
       <c r="AM25" s="1" t="s">
-        <v>342</v>
+        <v>360</v>
       </c>
       <c r="AN25" s="3">
         <v>1.0</v>
@@ -20369,13 +21878,13 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>343</v>
+        <v>361</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>53</v>
@@ -20389,13 +21898,13 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>343</v>
+        <v>361</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>86</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>51</v>
@@ -20404,12 +21913,12 @@
         <v>65</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>210</v>
+        <v>136</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>343</v>
+        <v>361</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>86</v>
@@ -20438,7 +21947,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>343</v>
+        <v>361</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>86</v>
@@ -20447,10 +21956,10 @@
         <v>0.0</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="S29" s="3">
         <v>9627.0</v>
@@ -20498,7 +22007,7 @@
         <v>1.0</v>
       </c>
       <c r="AM29" s="1" t="s">
-        <v>344</v>
+        <v>362</v>
       </c>
       <c r="AN29" s="3">
         <v>1.0</v>
@@ -20530,13 +22039,13 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>345</v>
+        <v>363</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>90</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>51</v>
@@ -20550,7 +22059,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>345</v>
+        <v>363</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>90</v>
@@ -20579,13 +22088,13 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>345</v>
+        <v>363</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>90</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>51</v>
@@ -20594,12 +22103,12 @@
         <v>65</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>210</v>
+        <v>136</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>345</v>
+        <v>363</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>90</v>
@@ -20608,10 +22117,10 @@
         <v>1.0</v>
       </c>
       <c r="Q33" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="S33" s="3">
         <v>8650.0</v>
@@ -20659,7 +22168,7 @@
         <v>0.0</v>
       </c>
       <c r="AM33" s="1" t="s">
-        <v>346</v>
+        <v>364</v>
       </c>
       <c r="AN33" s="3">
         <v>1.0</v>
@@ -20691,7 +22200,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>347</v>
+        <v>365</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>49</v>
@@ -20711,27 +22220,27 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>347</v>
+        <v>365</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>55</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>347</v>
+        <v>365</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>49</v>
@@ -20760,7 +22269,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>347</v>
+        <v>365</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>49</v>
@@ -20772,7 +22281,7 @@
         <v>63</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="S37" s="3">
         <v>13913.0</v>
@@ -20820,7 +22329,7 @@
         <v>5.0</v>
       </c>
       <c r="AM37" s="1" t="s">
-        <v>348</v>
+        <v>366</v>
       </c>
       <c r="AN37" s="3">
         <v>1.0</v>
@@ -20852,7 +22361,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>349</v>
+        <v>367</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>62</v>
@@ -20872,13 +22381,13 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>349</v>
+        <v>367</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>55</v>
@@ -20892,13 +22401,13 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>349</v>
+        <v>367</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>53</v>
@@ -20921,7 +22430,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>349</v>
+        <v>367</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>62</v>
@@ -20933,7 +22442,7 @@
         <v>63</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="S41" s="3">
         <v>13277.0</v>
@@ -20981,7 +22490,7 @@
         <v>0.0</v>
       </c>
       <c r="AM41" s="1" t="s">
-        <v>350</v>
+        <v>368</v>
       </c>
       <c r="AN41" s="3">
         <v>1.0</v>
@@ -21013,13 +22522,13 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>351</v>
+        <v>369</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>51</v>
@@ -21033,13 +22542,13 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>351</v>
+        <v>369</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>53</v>
@@ -21062,13 +22571,13 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>351</v>
+        <v>369</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>55</v>
@@ -21082,7 +22591,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>351</v>
+        <v>369</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>69</v>
@@ -21091,10 +22600,10 @@
         <v>0.0</v>
       </c>
       <c r="Q45" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="R45" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="S45" s="3">
         <v>12722.0</v>
@@ -21142,7 +22651,7 @@
         <v>0.0</v>
       </c>
       <c r="AM45" s="1" t="s">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="AN45" s="3">
         <v>1.0</v>
@@ -21174,7 +22683,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>76</v>
@@ -21194,13 +22703,13 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>53</v>
@@ -21223,13 +22732,13 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>55</v>
@@ -21243,7 +22752,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>76</v>
@@ -21303,7 +22812,7 @@
         <v>0.0</v>
       </c>
       <c r="AM49" s="1" t="s">
-        <v>354</v>
+        <v>372</v>
       </c>
       <c r="AN49" s="3">
         <v>1.0</v>
@@ -21335,7 +22844,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>355</v>
+        <v>373</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>82</v>
@@ -21355,13 +22864,13 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>355</v>
+        <v>373</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>82</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>51</v>
@@ -21384,7 +22893,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>355</v>
+        <v>373</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>82</v>
@@ -21444,7 +22953,7 @@
         <v>0.0</v>
       </c>
       <c r="AM52" s="1" t="s">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="AN52" s="3">
         <v>1.0</v>
@@ -21476,13 +22985,13 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>357</v>
+        <v>375</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>55</v>
@@ -21496,7 +23005,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>357</v>
+        <v>375</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>86</v>
@@ -21529,7 +23038,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>357</v>
+        <v>375</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>86</v>
@@ -21539,7 +23048,7 @@
       <c r="E55" s="1"/>
       <c r="G55" s="1"/>
       <c r="H55" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>51</v>
@@ -21553,7 +23062,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>357</v>
+        <v>375</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>86</v>
@@ -21611,7 +23120,7 @@
         <v>0.0</v>
       </c>
       <c r="AM56" s="1" t="s">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="AN56" s="3">
         <v>1.0</v>
@@ -21643,13 +23152,13 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>359</v>
+        <v>377</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>90</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>51</v>
@@ -21663,13 +23172,13 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>359</v>
+        <v>377</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>90</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>53</v>
@@ -21692,13 +23201,13 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>359</v>
+        <v>377</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>90</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>51</v>
@@ -21712,7 +23221,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>359</v>
+        <v>377</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>90</v>
@@ -21721,10 +23230,10 @@
         <v>0.0</v>
       </c>
       <c r="Q60" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="R60" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="S60" s="3">
         <v>18556.619999999995</v>
@@ -21772,7 +23281,7 @@
         <v>0.0</v>
       </c>
       <c r="AM60" s="1" t="s">
-        <v>360</v>
+        <v>378</v>
       </c>
       <c r="AN60" s="3">
         <v>1.0</v>
@@ -21804,7 +23313,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>49</v>
@@ -21824,13 +23333,13 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>55</v>
@@ -21844,7 +23353,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>49</v>
@@ -21854,7 +23363,7 @@
       <c r="E63" s="1"/>
       <c r="G63" s="1"/>
       <c r="H63" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>53</v>
@@ -21877,7 +23386,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>49</v>
@@ -21893,7 +23402,7 @@
         <v>63</v>
       </c>
       <c r="R64" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="S64" s="3">
         <v>21825.50999999999</v>
@@ -21941,7 +23450,7 @@
         <v>0.0</v>
       </c>
       <c r="AM64" s="1" t="s">
-        <v>362</v>
+        <v>380</v>
       </c>
       <c r="AN64" s="3">
         <v>1.0</v>
@@ -21973,7 +23482,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>62</v>
@@ -21993,13 +23502,13 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>55</v>
@@ -22013,13 +23522,13 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="I67" s="2" t="s">
         <v>53</v>
@@ -22042,7 +23551,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>62</v>
@@ -22096,7 +23605,7 @@
         <v>0.0</v>
       </c>
       <c r="AM68" s="1" t="s">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="AN68" s="3">
         <v>1.0</v>
@@ -22128,13 +23637,13 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>365</v>
+        <v>383</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>51</v>
@@ -22148,13 +23657,13 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>365</v>
+        <v>383</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>53</v>
@@ -22177,7 +23686,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>365</v>
+        <v>383</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>69</v>
@@ -22231,7 +23740,7 @@
         <v>0.0</v>
       </c>
       <c r="AM71" s="1" t="s">
-        <v>366</v>
+        <v>384</v>
       </c>
       <c r="AN71" s="3">
         <v>1.0</v>
@@ -22263,7 +23772,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>367</v>
+        <v>385</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>76</v>
@@ -22283,13 +23792,13 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>367</v>
+        <v>385</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>53</v>
@@ -22312,7 +23821,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>367</v>
+        <v>385</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>76</v>
@@ -22375,7 +23884,7 @@
         <v>0.0</v>
       </c>
       <c r="AM74" s="1" t="s">
-        <v>368</v>
+        <v>386</v>
       </c>
       <c r="AN74" s="3">
         <v>1.0</v>
@@ -22407,7 +23916,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>82</v>
@@ -22427,13 +23936,13 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>82</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>53</v>
@@ -22456,13 +23965,13 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>82</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>55</v>
@@ -22485,7 +23994,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>82</v>
@@ -22545,7 +24054,7 @@
         <v>0.0</v>
       </c>
       <c r="AM78" s="1" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="AN78" s="3">
         <v>2.0</v>
@@ -22577,13 +24086,13 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>370</v>
+        <v>388</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>51</v>
@@ -22597,13 +24106,13 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>370</v>
+        <v>388</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>86</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="I80" s="2" t="s">
         <v>53</v>
@@ -22626,7 +24135,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>370</v>
+        <v>388</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>86</v>
@@ -22655,7 +24164,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>370</v>
+        <v>388</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>86</v>
@@ -22664,10 +24173,10 @@
         <v>0.0</v>
       </c>
       <c r="Q82" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="R82" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="S82" s="3">
         <v>12752.009999999998</v>
@@ -22712,7 +24221,7 @@
         <v>0.0</v>
       </c>
       <c r="AM82" s="1" t="s">
-        <v>371</v>
+        <v>389</v>
       </c>
       <c r="AN82" s="3">
         <v>2.0</v>
@@ -22744,13 +24253,13 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>372</v>
+        <v>390</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>90</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>55</v>
@@ -22764,7 +24273,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>372</v>
+        <v>390</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>90</v>
@@ -22793,13 +24302,13 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>372</v>
+        <v>390</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>90</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="I85" s="2" t="s">
         <v>51</v>
@@ -22816,7 +24325,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>372</v>
+        <v>390</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>90</v>
@@ -22825,7 +24334,7 @@
         <v>0.0</v>
       </c>
       <c r="R86" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="S86" s="3">
         <v>17035.32</v>
@@ -22873,7 +24382,7 @@
         <v>0.0</v>
       </c>
       <c r="AM86" s="1" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="AN86" s="3">
         <v>1.0</v>
@@ -22905,7 +24414,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>373</v>
+        <v>391</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>49</v>
@@ -22925,13 +24434,13 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>373</v>
+        <v>391</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>55</v>
@@ -22945,7 +24454,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>373</v>
+        <v>391</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>49</v>
@@ -22974,7 +24483,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>373</v>
+        <v>391</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>49</v>
@@ -22986,7 +24495,7 @@
         <v>63</v>
       </c>
       <c r="R90" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="S90" s="3">
         <v>25392.46</v>
@@ -23034,7 +24543,7 @@
         <v>0.0</v>
       </c>
       <c r="AM90" s="1" t="s">
-        <v>374</v>
+        <v>392</v>
       </c>
       <c r="AN90" s="3">
         <v>1.0</v>
@@ -23066,7 +24575,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>375</v>
+        <v>393</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>62</v>
@@ -23086,13 +24595,13 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>375</v>
+        <v>393</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>55</v>
@@ -23106,13 +24615,13 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>375</v>
+        <v>393</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="I93" s="2" t="s">
         <v>53</v>
@@ -23135,7 +24644,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>375</v>
+        <v>393</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>62</v>
@@ -23147,7 +24656,7 @@
         <v>63</v>
       </c>
       <c r="R94" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="S94" s="3">
         <v>23475.639999999996</v>
@@ -23227,13 +24736,13 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>376</v>
+        <v>394</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>51</v>
@@ -23247,22 +24756,22 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>376</v>
+        <v>394</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="I96" s="2" t="s">
         <v>53</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>210</v>
+        <v>136</v>
       </c>
       <c r="M96" s="3">
         <v>8.0</v>
@@ -23276,7 +24785,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>376</v>
+        <v>394</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>69</v>
@@ -23285,10 +24794,10 @@
         <v>0.0</v>
       </c>
       <c r="Q97" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="R97" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="S97" s="3">
         <v>19985.18999999999</v>
@@ -23336,7 +24845,7 @@
         <v>0.0</v>
       </c>
       <c r="AM97" s="1" t="s">
-        <v>377</v>
+        <v>395</v>
       </c>
       <c r="AN97" s="3">
         <v>1.0</v>
@@ -23368,7 +24877,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>378</v>
+        <v>396</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>76</v>
@@ -23388,13 +24897,13 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>378</v>
+        <v>396</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="I99" s="2" t="s">
         <v>51</v>
@@ -23411,13 +24920,13 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>378</v>
+        <v>396</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="I100" s="2" t="s">
         <v>53</v>
@@ -23440,7 +24949,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>378</v>
+        <v>396</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>76</v>
@@ -23497,7 +25006,7 @@
         <v>0.0</v>
       </c>
       <c r="AM101" s="1" t="s">
-        <v>379</v>
+        <v>397</v>
       </c>
       <c r="AN101" s="3">
         <v>1.0</v>
@@ -23529,13 +25038,13 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>380</v>
+        <v>398</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>82</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>55</v>
@@ -23549,13 +25058,13 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>380</v>
+        <v>398</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>82</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="I103" s="2" t="s">
         <v>51</v>
@@ -23572,7 +25081,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>380</v>
+        <v>398</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>82</v>
@@ -23601,7 +25110,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>380</v>
+        <v>398</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>82</v>
@@ -23610,7 +25119,7 @@
         <v>0.0</v>
       </c>
       <c r="R105" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="S105" s="3">
         <v>12356.0</v>
@@ -23658,7 +25167,7 @@
         <v>0.0</v>
       </c>
       <c r="AM105" s="1" t="s">
-        <v>381</v>
+        <v>399</v>
       </c>
       <c r="AN105" s="3">
         <v>1.0</v>
@@ -23690,13 +25199,13 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>382</v>
+        <v>400</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>55</v>
@@ -23710,13 +25219,13 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>382</v>
+        <v>400</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>86</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="I107" s="2" t="s">
         <v>51</v>
@@ -23733,7 +25242,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>382</v>
+        <v>400</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>86</v>
@@ -23762,7 +25271,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>382</v>
+        <v>400</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>86</v>
@@ -23771,7 +25280,7 @@
         <v>0.0</v>
       </c>
       <c r="R109" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="S109" s="3">
         <v>8748.0</v>
@@ -23819,7 +25328,7 @@
         <v>0.0</v>
       </c>
       <c r="AM109" s="1" t="s">
-        <v>383</v>
+        <v>401</v>
       </c>
       <c r="AN109" s="3">
         <v>1.0</v>
@@ -23851,13 +25360,13 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>384</v>
+        <v>402</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>90</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>55</v>
@@ -23871,7 +25380,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>384</v>
+        <v>402</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>90</v>
@@ -23900,13 +25409,13 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>384</v>
+        <v>402</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>90</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="I112" s="2" t="s">
         <v>51</v>
@@ -23929,7 +25438,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>384</v>
+        <v>402</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>90</v>
@@ -23983,7 +25492,7 @@
         <v>0.0</v>
       </c>
       <c r="AM113" s="1" t="s">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="AN113" s="3">
         <v>2.0</v>
@@ -24015,13 +25524,13 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>385</v>
+        <v>403</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>55</v>
@@ -24035,13 +25544,13 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>385</v>
+        <v>403</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>55</v>
@@ -24055,13 +25564,13 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>385</v>
+        <v>403</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="I116" s="2" t="s">
         <v>53</v>
@@ -24084,13 +25593,13 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>385</v>
+        <v>403</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="I117" s="2" t="s">
         <v>51</v>
@@ -24107,7 +25616,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>385</v>
+        <v>403</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>49</v>
@@ -24116,7 +25625,7 @@
         <v>1.0</v>
       </c>
       <c r="R118" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="S118" s="3">
         <v>22791.559999999998</v>
@@ -24164,7 +25673,7 @@
         <v>0.0</v>
       </c>
       <c r="AM118" s="1" t="s">
-        <v>362</v>
+        <v>380</v>
       </c>
       <c r="AN118" s="3">
         <v>1.0</v>
@@ -24196,13 +25705,13 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>51</v>
@@ -24216,13 +25725,13 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>55</v>
@@ -24236,7 +25745,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>62</v>
@@ -24265,7 +25774,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>62</v>
@@ -24319,7 +25828,7 @@
         <v>0.0</v>
       </c>
       <c r="AM122" s="1" t="s">
-        <v>304</v>
+        <v>322</v>
       </c>
       <c r="AN122" s="3">
         <v>1.0</v>
